--- a/docs/design-vi/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者情報登録画面_v1.0.xlsx
+++ b/docs/design-vi/ACSMS-SCR-011/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_テスト仕様書_購読者情報登録画面_v1.0.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="3.33" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1361,20 +1361,80 @@
       <c r="AG2" s="10" t="n"/>
       <c r="AH2" s="11" t="n"/>
     </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="20" t="inlineStr">
+        <is>
+          <t>Đồng bộ với bản tiếng Nhật (bổ sung 7 case còn thiếu): TC-011-015-2 kiểm tra họ tên cho phép Kanji/Hiragana/Katakana/Latin, TC-011-047 luồng chỉnh sửa của bản điện tử thuần, TC-011-048 dropdown cửa hàng liên động theo loại người đọc, TC-011-049 sửa phương thức thanh toán và 4 trường tài khoản trước khi duyệt (#56524), TC-011-050 4 trường phụ thuộc của thuộc tính người đọc, TC-011-051 kiểm tra trùng email xuyên JA (#56568), TC-011-052 vùng nơi giao báo hiển thị với loại kết hợp.</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="19" t="inlineStr"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="11" t="n"/>
+      <c r="AC3" s="19" t="inlineStr"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="18">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="AC2:AH2"/>
     <mergeCell ref="AC1:AH1"/>
+    <mergeCell ref="O3:V3"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="O2:V2"/>
     <mergeCell ref="W1:AB1"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="W3:AB3"/>
     <mergeCell ref="O1:V1"/>
     <mergeCell ref="I1:N1"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="I3:N3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="W2:AB2"/>
+    <mergeCell ref="AC3:AH3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6346,7 +6406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ63"/>
+  <dimension ref="A1:BQ70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -10868,188 +10928,48 @@
       <c r="BP29" s="10" t="n"/>
       <c r="BQ29" s="11" t="n"/>
     </row>
-    <row r="30" ht="384" customHeight="1">
+    <row r="30" ht="80" customHeight="1">
       <c r="A30" s="44" t="n">
         <v>16</v>
       </c>
       <c r="B30" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-016</t>
+          <t>ACSMS-TC-011-015-2</t>
         </is>
       </c>
       <c r="C30" s="10" t="n"/>
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="46" t="inlineStr">
         <is>
-          <t>Kiểm tra 7 chữ số mã bưu điện</t>
+          <t>Kiểm tra họ tên người đọc cho phép Kanji / Hiragana / Katakana (yêu cầu khách hàng 2026-07)</t>
         </is>
       </c>
       <c r="F30" s="10" t="n"/>
       <c r="G30" s="10" t="n"/>
       <c r="H30" s="10" t="n"/>
       <c r="I30" s="11" t="n"/>
-      <c r="J30" s="46" t="inlineStr">
-        <is>
-          <t>・role: JA_HONTEN（ja_id=100 所属）
-・Đang mở màn hình đăng ký thông tin độc giả (chế độ tạo mới)</t>
-        </is>
-      </c>
+      <c r="J30" s="46" t="inlineStr"/>
       <c r="K30" s="10" t="n"/>
       <c r="L30" s="10" t="n"/>
       <c r="M30" s="10" t="n"/>
       <c r="N30" s="10" t="n"/>
       <c r="O30" s="10" t="n"/>
       <c r="P30" s="11" t="n"/>
-      <c r="Q30" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Nhập「123」(dưới 6 chữ số) vào mã bưu điện (yubin_no), click button「承認・登録」
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Nhập「123-4567」(có dấu gạch ngang) vào mã bưu điện (yubin_no), click button「承認・登録」
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Nhập「1234567」(7 chữ số nửa角) vào mã bưu điện (yubin_no), click button「承認・登録」</t>
-          </r>
-        </is>
-      </c>
+      <c r="Q30" s="46" t="inlineStr"/>
       <c r="R30" s="10" t="n"/>
       <c r="S30" s="10" t="n"/>
       <c r="T30" s="10" t="n"/>
       <c r="U30" s="10" t="n"/>
       <c r="V30" s="10" t="n"/>
       <c r="W30" s="11" t="n"/>
-      <c r="X30" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Hiển thị lỗi format (message `郵便番号は7桁で入力してください。`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Hiển thị lỗi format (không cho nhập dấu gạch ngang, message `郵便番号は7桁で入力してください。`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Không hiển thị lỗi format mã bưu điện (7 chữ số nửa角 có thể nhập)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Mã bưu điện cố định 7 chữ số nửa角, không cho nhập dấu gạch ngang
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Khi số chữ số sai thì hiển thị message ACSMS-MSG-011-004 `郵便番号は7桁で入力してください。`</t>
-          </r>
-        </is>
-      </c>
+      <c r="X30" s="46" t="inlineStr"/>
       <c r="Y30" s="10" t="n"/>
       <c r="Z30" s="10" t="n"/>
       <c r="AA30" s="10" t="n"/>
       <c r="AB30" s="10" t="n"/>
       <c r="AC30" s="10" t="n"/>
       <c r="AD30" s="11" t="n"/>
-      <c r="AE30" s="45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="AE30" s="45" t="inlineStr"/>
       <c r="AF30" s="11" t="n"/>
       <c r="AG30" s="45" t="inlineStr"/>
       <c r="AH30" s="10" t="n"/>
@@ -11095,14 +11015,14 @@
       </c>
       <c r="B31" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-017</t>
+          <t>ACSMS-TC-011-016</t>
         </is>
       </c>
       <c r="C31" s="10" t="n"/>
       <c r="D31" s="11" t="n"/>
       <c r="E31" s="46" t="inlineStr">
         <is>
-          <t>Kiểm tra format email</t>
+          <t>Kiểm tra 7 chữ số mã bưu điện</t>
         </is>
       </c>
       <c r="F31" s="10" t="n"/>
@@ -11137,7 +11057,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Nhập「yamada」(không có @) vào email (email), click button「承認・登録」
+            <t xml:space="preserve">Nhập「123」(dưới 6 chữ số) vào mã bưu điện (yubin_no), click button「承認・登録」
 </t>
           </r>
           <r>
@@ -11154,7 +11074,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Nhập「yamada@」(không có domain) vào email (email), click button「承認・登録」
+            <t xml:space="preserve">Nhập「123-4567」(có dấu gạch ngang) vào mã bưu điện (yubin_no), click button「承認・登録」
 </t>
           </r>
           <r>
@@ -11171,7 +11091,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Nhập「yamada@example.com」(format đúng) vào email (email), click button「承認・登録」</t>
+            <t>Nhập「1234567」(7 chữ số nửa角) vào mã bưu điện (yubin_no), click button「承認・登録」</t>
           </r>
         </is>
       </c>
@@ -11197,7 +11117,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Hiển thị lỗi format (message `正しいメールアドレスを入力してください。`)
+            <t xml:space="preserve">Hiển thị lỗi format (message `郵便番号は7桁で入力してください。`)
 </t>
           </r>
           <r>
@@ -11214,7 +11134,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Hiển thị lỗi format (message `正しいメールアドレスを入力してください。`)
+            <t xml:space="preserve">Hiển thị lỗi format (không cho nhập dấu gạch ngang, message `郵便番号は7桁で入力してください。`)
 </t>
           </r>
           <r>
@@ -11231,7 +11151,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Không hiển thị lỗi format email
+            <t xml:space="preserve">Không hiển thị lỗi format mã bưu điện (7 chữ số nửa角 có thể nhập)
 </t>
           </r>
           <r>
@@ -11248,23 +11168,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Email kiểm tra format theo RFC 5322
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Khi format sai thì hiển thị message ACSMS-MSG-011-005 `正しいメールアドレスを入力してください。`
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・項目 email dùng `type="text"`, không dùng popup tiếng Anh mặc định của trình duyệt</t>
+            <t xml:space="preserve">・Mã bưu điện cố định 7 chữ số nửa角, không cho nhập dấu gạch ngang
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Khi số chữ số sai thì hiển thị message ACSMS-MSG-011-004 `郵便番号は7桁で入力してください。`</t>
           </r>
         </is>
       </c>
@@ -11318,20 +11230,20 @@
       <c r="BP31" s="10" t="n"/>
       <c r="BQ31" s="11" t="n"/>
     </row>
-    <row r="32" ht="336" customHeight="1">
+    <row r="32" ht="384" customHeight="1">
       <c r="A32" s="44" t="n">
         <v>18</v>
       </c>
       <c r="B32" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-018</t>
+          <t>ACSMS-TC-011-017</t>
         </is>
       </c>
       <c r="C32" s="10" t="n"/>
       <c r="D32" s="11" t="n"/>
       <c r="E32" s="46" t="inlineStr">
         <is>
-          <t>Email bắt buộc có điều kiện (電子版・併読)</t>
+          <t>Kiểm tra format email</t>
         </is>
       </c>
       <c r="F32" s="10" t="n"/>
@@ -11366,7 +11278,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chọn「電子版」ở loại độc giả (dokusya_shubetsu), để trống email (email) rồi click button「承認・登録」
+            <t xml:space="preserve">Nhập「yamada」(không có @) vào email (email), click button「承認・登録」
 </t>
           </r>
           <r>
@@ -11383,7 +11295,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chọn「併読」ở loại độc giả, để trống email rồi click button「承認・登録」
+            <t xml:space="preserve">Nhập「yamada@」(không có domain) vào email (email), click button「承認・登録」
 </t>
           </r>
           <r>
@@ -11400,7 +11312,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Chọn「紙版」ở loại độc giả, để trống email, nhập các項目 bắt buộc khác rồi click button「承認・登録」</t>
+            <t>Nhập「yamada@example.com」(format đúng) vào email (email), click button「承認・登録」</t>
           </r>
         </is>
       </c>
@@ -11426,7 +11338,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Lỗi required hiển thị dưới email (email) (message `必須項目です。`)
+            <t xml:space="preserve">Hiển thị lỗi format (message `正しいメールアドレスを入力してください。`)
 </t>
           </r>
           <r>
@@ -11443,7 +11355,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Lỗi required hiển thị dưới email (email) (message `必須項目です。`)
+            <t xml:space="preserve">Hiển thị lỗi format (message `正しいメールアドレスを入力してください。`)
 </t>
           </r>
           <r>
@@ -11460,7 +11372,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Lỗi required của email (email) không hiển thị (trường hợp 紙版 là tùy chọn)
+            <t xml:space="preserve">Không hiển thị lỗi format email
 </t>
           </r>
           <r>
@@ -11477,15 +11389,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Khi loại độc giả=電子版/併読 thì email bắt buộc (機能定義 §7.1)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Trường hợp 紙版 thì email là tùy chọn</t>
+            <t xml:space="preserve">・Email kiểm tra format theo RFC 5322
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Khi format sai thì hiển thị message ACSMS-MSG-011-005 `正しいメールアドレスを入力してください。`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・項目 email dùng `type="text"`, không dùng popup tiếng Anh mặc định của trình duyệt</t>
           </r>
         </is>
       </c>
@@ -11539,20 +11459,20 @@
       <c r="BP32" s="10" t="n"/>
       <c r="BQ32" s="11" t="n"/>
     </row>
-    <row r="33" ht="450" customHeight="1">
+    <row r="33" ht="336" customHeight="1">
       <c r="A33" s="44" t="n">
         <v>19</v>
       </c>
       <c r="B33" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-019</t>
+          <t>ACSMS-TC-011-018</t>
         </is>
       </c>
       <c r="C33" s="10" t="n"/>
       <c r="D33" s="11" t="n"/>
       <c r="E33" s="46" t="inlineStr">
         <is>
-          <t>Cụm ngân hàng bắt buộc có điều kiện khi 口座引落</t>
+          <t>Email bắt buộc có điều kiện (電子版・併読)</t>
         </is>
       </c>
       <c r="F33" s="10" t="n"/>
@@ -11562,8 +11482,7 @@
       <c r="J33" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・Loại độc giả=紙版
-・Đã chọn「口座引落」ở phương thức thanh toán (shiharai_hoho)</t>
+・Đang mở màn hình đăng ký thông tin độc giả (chế độ tạo mới)</t>
         </is>
       </c>
       <c r="K33" s="10" t="n"/>
@@ -11588,7 +11507,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Để trống 引落口座支店 (bank_shiten_id)・引落口座貯金種目 (hikiotoshi_yokin_shubetsu)・引落口座番号 (hikiotoshi_koza_no)・引落口座名義 (hikiotoshi_koza_meigi) rồi click button「承認・登録」
+            <t xml:space="preserve">Chọn「電子版」ở loại độc giả (dokusya_shubetsu), để trống email (email) rồi click button「承認・登録」
 </t>
           </r>
           <r>
@@ -11605,7 +11524,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Đổi phương thức thanh toán sang「現金集金」, để trống 4項目 trên rồi click button「承認・登録」
+            <t xml:space="preserve">Chọn「併読」ở loại độc giả, để trống email rồi click button「承認・登録」
 </t>
           </r>
           <r>
@@ -11622,7 +11541,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận lựa chọn của dropdown 引落口座支店</t>
+            <t>Chọn「紙版」ở loại độc giả, để trống email, nhập các項目 bắt buộc khác rồi click button「承認・登録」</t>
           </r>
         </is>
       </c>
@@ -11648,7 +11567,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Lỗi hiển thị dưới 引落口座支店・引落口座貯金種目・引落口座番号・引落口座名義 (message `口座引落の場合、〇〇は必須です。`)
+            <t xml:space="preserve">Lỗi required hiển thị dưới email (email) (message `必須項目です。`)
 </t>
           </r>
           <r>
@@ -11665,7 +11584,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Lỗi của 4項目 trên không hiển thị (phương thức thanh toán khác 口座引落 là tùy chọn)
+            <t xml:space="preserve">Lỗi required hiển thị dưới email (email) (message `必須項目です。`)
 </t>
           </r>
           <r>
@@ -11682,7 +11601,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chỉ chi nhánh có cờ chi nhánh tài chính (kinyu_shiten_flg=TRUE) được hiển thị trong lựa chọn
+            <t xml:space="preserve">Lỗi required của email (email) không hiển thị (trường hợp 紙版 là tùy chọn)
 </t>
           </r>
           <r>
@@ -11699,23 +11618,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Khi phương thức thanh toán=口座引落 (shiharai_hoho=1) thì cụm tài khoản rút 4項目 bắt buộc (機能定義 §10.1)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Lỗi bắt buộc 口座引落 hiển thị message ACSMS-MSG-011-006 `口座引落の場合、〇〇は必須です。`
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Dropdown 引落口座支店 chỉ hiển thị những cái có `m_shiten.kinyu_shiten_flg=TRUE`</t>
+            <t xml:space="preserve">・Khi loại độc giả=電子版/併読 thì email bắt buộc (機能定義 §7.1)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Trường hợp 紙版 thì email là tùy chọn</t>
           </r>
         </is>
       </c>
@@ -11775,14 +11686,14 @@
       </c>
       <c r="B34" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-020</t>
+          <t>ACSMS-TC-011-019</t>
         </is>
       </c>
       <c r="C34" s="10" t="n"/>
       <c r="D34" s="11" t="n"/>
       <c r="E34" s="46" t="inlineStr">
         <is>
-          <t>Địa chỉ giao bắt buộc có điều kiện (購読者情報と同じ chưa check)</t>
+          <t>Cụm ngân hàng bắt buộc có điều kiện khi 口座引落</t>
         </is>
       </c>
       <c r="F34" s="10" t="n"/>
@@ -11793,7 +11704,7 @@
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
 ・Loại độc giả=紙版
-・「購読者情報と同じ」(haitatsu_same_flg) ở trạng thái chưa check</t>
+・Đã chọn「口座引落」ở phương thức thanh toán (shiharai_hoho)</t>
         </is>
       </c>
       <c r="K34" s="10" t="n"/>
@@ -11818,7 +11729,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Để trống 配達先郵便番号 (haitatsu_yubin_no)・配達先都道府県 (haitatsu_todofuken_code)・配達先市町村郡 (haitatsu_shikuchoson)・配達先丁目番地 (haitatsu_chome_banchi) rồi click button「承認・登録」
+            <t xml:space="preserve">Để trống 引落口座支店 (bank_shiten_id)・引落口座貯金種目 (hikiotoshi_yokin_shubetsu)・引落口座番号 (hikiotoshi_koza_no)・引落口座名義 (hikiotoshi_koza_meigi) rồi click button「承認・登録」
 </t>
           </r>
           <r>
@@ -11835,7 +11746,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Để trống 配達先苗字漢字 (haitatsu_shimei_sei)・配達先名前漢字 (haitatsu_shimei_mei)・配達先苗字かな (haitatsu_shimei_kana_sei)・配達先名前かな (haitatsu_shimei_kana_mei) rồi click button「承認・登録」
+            <t xml:space="preserve">Đổi phương thức thanh toán sang「現金集金」, để trống 4項目 trên rồi click button「承認・登録」
 </t>
           </r>
           <r>
@@ -11852,7 +11763,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Check「購読者情報と同じ」, để trống các項目 địa chỉ giao rồi click button「承認・登録」</t>
+            <t>Xác nhận lựa chọn của dropdown 引落口座支店</t>
           </r>
         </is>
       </c>
@@ -11878,7 +11789,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Lỗi required hiển thị dưới 配達先郵便番号・配達先都道府県・配達先市町村郡・配達先丁目番地 (message `必須項目です。`)
+            <t xml:space="preserve">Lỗi hiển thị dưới 引落口座支店・引落口座貯金種目・引落口座番号・引落口座名義 (message `口座引落の場合、〇〇は必須です。`)
 </t>
           </r>
           <r>
@@ -11895,7 +11806,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Lỗi required hiển thị dưới 配達先苗字漢字・配達先名前漢字・配達先苗字かな・配達先名前かな (message `必須項目です。`)
+            <t xml:space="preserve">Lỗi của 4項目 trên không hiển thị (phương thức thanh toán khác 口座引落 là tùy chọn)
 </t>
           </r>
           <r>
@@ -11912,7 +11823,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Lỗi required của các項目 địa chỉ giao không hiển thị (khi check thì copy từ thông tin độc giả nên bỏ qua bắt buộc)
+            <t xml:space="preserve">Chỉ chi nhánh có cờ chi nhánh tài chính (kinyu_shiten_flg=TRUE) được hiển thị trong lựa chọn
 </t>
           </r>
           <r>
@@ -11929,15 +11840,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Khi「購読者情報と同じ」chưa check thì 配達先郵便番号〜丁目番地 và 配達先氏名 (漢字・かな) bắt buộc (機能定義 §9.2)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Khi check thì copy từ thông tin độc giả lúc lưu DB (機能定義 §9.1)</t>
+            <t xml:space="preserve">・Khi phương thức thanh toán=口座引落 (shiharai_hoho=1) thì cụm tài khoản rút 4項目 bắt buộc (機能定義 §10.1)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Lỗi bắt buộc 口座引落 hiển thị message ACSMS-MSG-011-006 `口座引落の場合、〇〇は必須です。`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Dropdown 引落口座支店 chỉ hiển thị những cái có `m_shiten.kinyu_shiten_flg=TRUE`</t>
           </r>
         </is>
       </c>
@@ -11991,20 +11910,20 @@
       <c r="BP34" s="10" t="n"/>
       <c r="BQ34" s="11" t="n"/>
     </row>
-    <row r="35" ht="384" customHeight="1">
+    <row r="35" ht="450" customHeight="1">
       <c r="A35" s="44" t="n">
         <v>21</v>
       </c>
       <c r="B35" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-021</t>
+          <t>ACSMS-TC-011-020</t>
         </is>
       </c>
       <c r="C35" s="10" t="n"/>
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="46" t="inlineStr">
         <is>
-          <t>Kiểm tra số ký tự tối đa 備考・kiểm tra ngày tương lai 読者情報変更適用日</t>
+          <t>Địa chỉ giao bắt buộc có điều kiện (購読者情報と同じ chưa check)</t>
         </is>
       </c>
       <c r="F35" s="10" t="n"/>
@@ -12014,8 +11933,8 @@
       <c r="J35" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・Đang mở màn hình đăng ký thông tin độc giả (chế độ tạo mới)
-・Hôm nay: 2026-06-03</t>
+・Loại độc giả=紙版
+・「購読者情報と同じ」(haitatsu_same_flg) ở trạng thái chưa check</t>
         </is>
       </c>
       <c r="K35" s="10" t="n"/>
@@ -12040,7 +11959,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Nhập 501 ký tự vào 備考 (biko), click button「承認・登録」
+            <t xml:space="preserve">Để trống 配達先郵便番号 (haitatsu_yubin_no)・配達先都道府県 (haitatsu_todofuken_code)・配達先市町村郡 (haitatsu_shikuchoson)・配達先丁目番地 (haitatsu_chome_banchi) rồi click button「承認・登録」
 </t>
           </r>
           <r>
@@ -12057,7 +11976,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Nhập 500 ký tự vào 備考 (biko), click button「承認・登録」
+            <t xml:space="preserve">Để trống 配達先苗字漢字 (haitatsu_shimei_sei)・配達先名前漢字 (haitatsu_shimei_mei)・配達先苗字かな (haitatsu_shimei_kana_sei)・配達先名前かな (haitatsu_shimei_kana_mei) rồi click button「承認・登録」
 </t>
           </r>
           <r>
@@ -12074,7 +11993,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Nhập ngày quá khứ (2026-06-02) vào 読者情報変更適用日 (joho_henko_tekiyo_date), click button「承認・登録」</t>
+            <t>Check「購読者情報と同じ」, để trống các項目 địa chỉ giao rồi click button「承認・登録」</t>
           </r>
         </is>
       </c>
@@ -12100,7 +12019,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Hiển thị lỗi vượt quá số ký tự (message `備考は500文字以内で入力してください。`)
+            <t xml:space="preserve">Lỗi required hiển thị dưới 配達先郵便番号・配達先都道府県・配達先市町村郡・配達先丁目番地 (message `必須項目です。`)
 </t>
           </r>
           <r>
@@ -12117,7 +12036,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Lỗi vượt quá số ký tự của 備考 không hiển thị (có thể đăng ký trong 500 ký tự)
+            <t xml:space="preserve">Lỗi required hiển thị dưới 配達先苗字漢字・配達先名前漢字・配達先苗字かな・配達先名前かな (message `必須項目です。`)
 </t>
           </r>
           <r>
@@ -12134,7 +12053,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Lỗi hiển thị dưới 読者情報変更適用日 (chỉ cho nhập ngày tương lai)
+            <t xml:space="preserve">Lỗi required của các項目 địa chỉ giao không hiển thị (khi check thì copy từ thông tin độc giả nên bỏ qua bắt buộc)
 </t>
           </r>
           <r>
@@ -12151,15 +12070,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・備考 trong 500 ký tự (ACSMS-MSG-011-010 message `備考は500文字以内で入力してください。`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・読者情報変更適用日 (joho_henko_tekiyo_date) khi nhập thì kiểm tra phải là ngày tương lai</t>
+            <t xml:space="preserve">・Khi「購読者情報と同じ」chưa check thì 配達先郵便番号〜丁目番地 và 配達先氏名 (漢字・かな) bắt buộc (機能定義 §9.2)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Khi check thì copy từ thông tin độc giả lúc lưu DB (機能定義 §9.1)</t>
           </r>
         </is>
       </c>
@@ -12213,20 +12132,20 @@
       <c r="BP35" s="10" t="n"/>
       <c r="BQ35" s="11" t="n"/>
     </row>
-    <row r="36" ht="400" customHeight="1">
+    <row r="36" ht="384" customHeight="1">
       <c r="A36" s="44" t="n">
         <v>22</v>
       </c>
       <c r="B36" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-022</t>
+          <t>ACSMS-TC-011-021</t>
         </is>
       </c>
       <c r="C36" s="10" t="n"/>
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="46" t="inlineStr">
         <is>
-          <t>Phân loại nông dân bắt buộc có điều kiện (tầng độc giả=農業者)</t>
+          <t>Kiểm tra số ký tự tối đa 備考・kiểm tra ngày tương lai 読者情報変更適用日</t>
         </is>
       </c>
       <c r="F36" s="10" t="n"/>
@@ -12236,7 +12155,8 @@
       <c r="J36" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・Đang mở màn hình đăng ký thông tin độc giả (chế độ tạo mới)</t>
+・Đang mở màn hình đăng ký thông tin độc giả (chế độ tạo mới)
+・Hôm nay: 2026-06-03</t>
         </is>
       </c>
       <c r="K36" s="10" t="n"/>
@@ -12261,7 +12181,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Check「農業者」ở phân loại tầng độc giả (dokusyaso_bunrui), để trống phân loại nông dân (nogyosya_bunrui) rồi click button「承認・登録」
+            <t xml:space="preserve">Nhập 501 ký tự vào 備考 (biko), click button「承認・登録」
 </t>
           </r>
           <r>
@@ -12278,7 +12198,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chọn「水稲」ở phân loại nông dân (nogyosya_bunrui), click button「承認・登録」
+            <t xml:space="preserve">Nhập 500 ký tự vào 備考 (biko), click button「承認・登録」
 </t>
           </r>
           <r>
@@ -12295,7 +12215,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Bỏ check「農業者」ở phân loại tầng độc giả, để trống phân loại nông dân rồi click button「承認・登録」</t>
+            <t>Nhập ngày quá khứ (2026-06-02) vào 読者情報変更適用日 (joho_henko_tekiyo_date), click button「承認・登録」</t>
           </r>
         </is>
       </c>
@@ -12321,7 +12241,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Lỗi required hiển thị dưới phân loại nông dân (nogyosya_bunrui) (message `必須項目です。`)
+            <t xml:space="preserve">Hiển thị lỗi vượt quá số ký tự (message `備考は500文字以内で入力してください。`)
 </t>
           </r>
           <r>
@@ -12338,7 +12258,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Lỗi required của phân loại nông dân không hiển thị
+            <t xml:space="preserve">Lỗi vượt quá số ký tự của 備考 không hiển thị (có thể đăng ký trong 500 ký tự)
 </t>
           </r>
           <r>
@@ -12355,7 +12275,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Lỗi required của phân loại nông dân không hiển thị (khi không chọn nông dân là tùy chọn)
+            <t xml:space="preserve">Lỗi hiển thị dưới 読者情報変更適用日 (chỉ cho nhập ngày tương lai)
 </t>
           </r>
           <r>
@@ -12372,15 +12292,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Khi chọn「農業者」ở phân loại tầng độc giả thì phân loại nông dân (nogyosya_bunrui) bắt buộc (đặc tả request parameter của API)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Khi không chọn nông dân thì phân loại nông dân là tùy chọn</t>
+            <t xml:space="preserve">・備考 trong 500 ký tự (ACSMS-MSG-011-010 message `備考は500文字以内で入力してください。`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・読者情報変更適用日 (joho_henko_tekiyo_date) khi nhập thì kiểm tra phải là ngày tương lai</t>
           </r>
         </is>
       </c>
@@ -12426,12 +12346,7 @@
       <c r="BH36" s="45" t="inlineStr"/>
       <c r="BI36" s="10" t="n"/>
       <c r="BJ36" s="11" t="n"/>
-      <c r="BK36" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BK36" s="46" t="inlineStr"/>
       <c r="BL36" s="10" t="n"/>
       <c r="BM36" s="10" t="n"/>
       <c r="BN36" s="10" t="n"/>
@@ -12439,74 +12354,225 @@
       <c r="BP36" s="10" t="n"/>
       <c r="BQ36" s="11" t="n"/>
     </row>
-    <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="32" t="inlineStr">
-        <is>
-          <t>Logic nghiệp vụ đăng ký (Function — Create)</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n"/>
+    <row r="37" ht="400" customHeight="1">
+      <c r="A37" s="44" t="n">
+        <v>23</v>
+      </c>
+      <c r="B37" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-022</t>
+        </is>
+      </c>
       <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="46" t="inlineStr">
+        <is>
+          <t>Phân loại nông dân bắt buộc có điều kiện (tầng độc giả=農業者)</t>
+        </is>
+      </c>
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="10" t="n"/>
       <c r="H37" s="10" t="n"/>
-      <c r="I37" s="10" t="n"/>
-      <c r="J37" s="10" t="n"/>
+      <c r="I37" s="11" t="n"/>
+      <c r="J37" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属）
+・Đang mở màn hình đăng ký thông tin độc giả (chế độ tạo mới)</t>
+        </is>
+      </c>
       <c r="K37" s="10" t="n"/>
       <c r="L37" s="10" t="n"/>
       <c r="M37" s="10" t="n"/>
       <c r="N37" s="10" t="n"/>
       <c r="O37" s="10" t="n"/>
-      <c r="P37" s="10" t="n"/>
-      <c r="Q37" s="10" t="n"/>
+      <c r="P37" s="11" t="n"/>
+      <c r="Q37" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Check「農業者」ở phân loại tầng độc giả (dokusyaso_bunrui), để trống phân loại nông dân (nogyosya_bunrui) rồi click button「承認・登録」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Chọn「水稲」ở phân loại nông dân (nogyosya_bunrui), click button「承認・登録」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Bỏ check「農業者」ở phân loại tầng độc giả, để trống phân loại nông dân rồi click button「承認・登録」</t>
+          </r>
+        </is>
+      </c>
       <c r="R37" s="10" t="n"/>
       <c r="S37" s="10" t="n"/>
       <c r="T37" s="10" t="n"/>
       <c r="U37" s="10" t="n"/>
       <c r="V37" s="10" t="n"/>
-      <c r="W37" s="10" t="n"/>
-      <c r="X37" s="10" t="n"/>
+      <c r="W37" s="11" t="n"/>
+      <c r="X37" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Lỗi required hiển thị dưới phân loại nông dân (nogyosya_bunrui) (message `必須項目です。`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Lỗi required của phân loại nông dân không hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Lỗi required của phân loại nông dân không hiển thị (khi không chọn nông dân là tùy chọn)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Khi chọn「農業者」ở phân loại tầng độc giả thì phân loại nông dân (nogyosya_bunrui) bắt buộc (đặc tả request parameter của API)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Khi không chọn nông dân thì phân loại nông dân là tùy chọn</t>
+          </r>
+        </is>
+      </c>
       <c r="Y37" s="10" t="n"/>
       <c r="Z37" s="10" t="n"/>
       <c r="AA37" s="10" t="n"/>
       <c r="AB37" s="10" t="n"/>
       <c r="AC37" s="10" t="n"/>
-      <c r="AD37" s="10" t="n"/>
-      <c r="AE37" s="10" t="n"/>
-      <c r="AF37" s="10" t="n"/>
-      <c r="AG37" s="10" t="n"/>
+      <c r="AD37" s="11" t="n"/>
+      <c r="AE37" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF37" s="11" t="n"/>
+      <c r="AG37" s="45" t="inlineStr"/>
       <c r="AH37" s="10" t="n"/>
-      <c r="AI37" s="10" t="n"/>
-      <c r="AJ37" s="10" t="n"/>
+      <c r="AI37" s="11" t="n"/>
+      <c r="AJ37" s="45" t="inlineStr"/>
       <c r="AK37" s="10" t="n"/>
-      <c r="AL37" s="10" t="n"/>
-      <c r="AM37" s="10" t="n"/>
+      <c r="AL37" s="11" t="n"/>
+      <c r="AM37" s="45" t="inlineStr"/>
       <c r="AN37" s="10" t="n"/>
-      <c r="AO37" s="10" t="n"/>
-      <c r="AP37" s="10" t="n"/>
+      <c r="AO37" s="11" t="n"/>
+      <c r="AP37" s="45" t="inlineStr"/>
       <c r="AQ37" s="10" t="n"/>
-      <c r="AR37" s="10" t="n"/>
-      <c r="AS37" s="10" t="n"/>
+      <c r="AR37" s="11" t="n"/>
+      <c r="AS37" s="45" t="inlineStr"/>
       <c r="AT37" s="10" t="n"/>
-      <c r="AU37" s="10" t="n"/>
-      <c r="AV37" s="10" t="n"/>
+      <c r="AU37" s="11" t="n"/>
+      <c r="AV37" s="45" t="inlineStr"/>
       <c r="AW37" s="10" t="n"/>
-      <c r="AX37" s="10" t="n"/>
-      <c r="AY37" s="10" t="n"/>
+      <c r="AX37" s="11" t="n"/>
+      <c r="AY37" s="45" t="inlineStr"/>
       <c r="AZ37" s="10" t="n"/>
-      <c r="BA37" s="10" t="n"/>
-      <c r="BB37" s="10" t="n"/>
+      <c r="BA37" s="11" t="n"/>
+      <c r="BB37" s="45" t="inlineStr"/>
       <c r="BC37" s="10" t="n"/>
-      <c r="BD37" s="10" t="n"/>
-      <c r="BE37" s="10" t="n"/>
+      <c r="BD37" s="11" t="n"/>
+      <c r="BE37" s="45" t="inlineStr"/>
       <c r="BF37" s="10" t="n"/>
-      <c r="BG37" s="10" t="n"/>
-      <c r="BH37" s="10" t="n"/>
+      <c r="BG37" s="11" t="n"/>
+      <c r="BH37" s="45" t="inlineStr"/>
       <c r="BI37" s="10" t="n"/>
-      <c r="BJ37" s="10" t="n"/>
-      <c r="BK37" s="10" t="n"/>
+      <c r="BJ37" s="11" t="n"/>
+      <c r="BK37" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL37" s="10" t="n"/>
       <c r="BM37" s="10" t="n"/>
       <c r="BN37" s="10" t="n"/>
@@ -12514,382 +12580,74 @@
       <c r="BP37" s="10" t="n"/>
       <c r="BQ37" s="11" t="n"/>
     </row>
-    <row r="38" ht="450" customHeight="1">
-      <c r="A38" s="44" t="n">
-        <v>23</v>
-      </c>
-      <c r="B38" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-011-023</t>
-        </is>
-      </c>
+    <row r="38" ht="22.5" customHeight="1">
+      <c r="A38" s="32" t="inlineStr">
+        <is>
+          <t>Logic nghiệp vụ đăng ký (Function — Create)</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n"/>
       <c r="C38" s="10" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="46" t="inlineStr">
-        <is>
-          <t>Đăng ký mới normal (lưu DB + tạo lịch sử + audit log)</t>
-        </is>
-      </c>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
       <c r="F38" s="10" t="n"/>
       <c r="G38" s="10" t="n"/>
       <c r="H38" s="10" t="n"/>
-      <c r="I38" s="11" t="n"/>
-      <c r="J38" s="46" t="inlineStr">
-        <is>
-          <t>・role: JA_HONTEN（ja_id=100 所属）
-・Đã nhập giá trị hợp lệ cho tất cả項目 bắt buộc (loại độc giả=紙版, loại thủ tục=新規, phương thức thanh toán=口座引落)</t>
-        </is>
-      </c>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="10" t="n"/>
       <c r="K38" s="10" t="n"/>
       <c r="L38" s="10" t="n"/>
       <c r="M38" s="10" t="n"/>
       <c r="N38" s="10" t="n"/>
       <c r="O38" s="10" t="n"/>
-      <c r="P38" s="11" t="n"/>
-      <c r="Q38" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Nhập tất cả項目 bắt buộc, click button「承認・登録」, click「はい」ở dialog xác nhận
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Xác nhận chuyển màn hình và message
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Chạy query sau trong DB, xác nhận record bản thể・lịch sử
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">```sql
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT dokusya_id, rireki_no, tetsuzuki_shurui, dokusya_busu
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_dokusya
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE dokusya_id = :new_dokusya_id;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT rireki_no, saishin_data_flg, shinki_flg, kaiyaku_flg, zougen_hokoku_flg
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_dokusya_rireki
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE dokusya_id = :new_dokusya_id;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">```
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Chạy query sau trong DB, xác nhận audit log
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">```sql
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT operation, result_status, target_table, ja_id
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_log
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE target_table = 't_dokusya' AND target_id = :new_dokusya_id
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ORDER BY log_datetime DESC
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">LIMIT 1;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>```</t>
-          </r>
-        </is>
-      </c>
+      <c r="P38" s="10" t="n"/>
+      <c r="Q38" s="10" t="n"/>
       <c r="R38" s="10" t="n"/>
       <c r="S38" s="10" t="n"/>
       <c r="T38" s="10" t="n"/>
       <c r="U38" s="10" t="n"/>
       <c r="V38" s="10" t="n"/>
-      <c r="W38" s="11" t="n"/>
-      <c r="X38" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Dialog xác nhận được hiển thị, click「はい」thì xử lý đăng ký được thực hiện
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Trả về HTTP 201, message đăng ký thành công `登録しました。`（ACSMS-MSG-011-011）được hiển thị, chuyển về màn hình 購読者明細検索
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Record mới được đăng ký vào t_dokusya, record lịch sử (rireki_no=1, saishin_data_flg=true, shinki_flg=true, kaiyaku_flg=false, zougen_hokoku_flg=true) được đăng ký vào t_dokusya_rireki
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Record với operation=`CREATE`, result_status=1, target_table=`t_dokusya`, ja_id=100 được ghi vào t_log
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Tạo t_dokusya + t_dokusya_rireki trong 1 transaction (機能定義 §2.6)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Khi phương thức thanh toán=口座引落 thì逆引き `m_shiten.jastem_toriatsukai_tenpo_code` / `jastem_tenpo_name` từ bank_shiten_id, lưu phi chuẩn hóa vào `t_dokusya.bank_branch_code` / `bank_branch_name`
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Đăng ký (ghi nghiệp vụ) và audit log được thực hiện trong một transaction duy nhất</t>
-          </r>
-        </is>
-      </c>
+      <c r="W38" s="10" t="n"/>
+      <c r="X38" s="10" t="n"/>
       <c r="Y38" s="10" t="n"/>
       <c r="Z38" s="10" t="n"/>
       <c r="AA38" s="10" t="n"/>
       <c r="AB38" s="10" t="n"/>
       <c r="AC38" s="10" t="n"/>
-      <c r="AD38" s="11" t="n"/>
-      <c r="AE38" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF38" s="11" t="n"/>
-      <c r="AG38" s="45" t="inlineStr"/>
+      <c r="AD38" s="10" t="n"/>
+      <c r="AE38" s="10" t="n"/>
+      <c r="AF38" s="10" t="n"/>
+      <c r="AG38" s="10" t="n"/>
       <c r="AH38" s="10" t="n"/>
-      <c r="AI38" s="11" t="n"/>
-      <c r="AJ38" s="45" t="inlineStr"/>
+      <c r="AI38" s="10" t="n"/>
+      <c r="AJ38" s="10" t="n"/>
       <c r="AK38" s="10" t="n"/>
-      <c r="AL38" s="11" t="n"/>
-      <c r="AM38" s="45" t="inlineStr"/>
+      <c r="AL38" s="10" t="n"/>
+      <c r="AM38" s="10" t="n"/>
       <c r="AN38" s="10" t="n"/>
-      <c r="AO38" s="11" t="n"/>
-      <c r="AP38" s="45" t="inlineStr"/>
+      <c r="AO38" s="10" t="n"/>
+      <c r="AP38" s="10" t="n"/>
       <c r="AQ38" s="10" t="n"/>
-      <c r="AR38" s="11" t="n"/>
-      <c r="AS38" s="45" t="inlineStr"/>
+      <c r="AR38" s="10" t="n"/>
+      <c r="AS38" s="10" t="n"/>
       <c r="AT38" s="10" t="n"/>
-      <c r="AU38" s="11" t="n"/>
-      <c r="AV38" s="45" t="inlineStr"/>
+      <c r="AU38" s="10" t="n"/>
+      <c r="AV38" s="10" t="n"/>
       <c r="AW38" s="10" t="n"/>
-      <c r="AX38" s="11" t="n"/>
-      <c r="AY38" s="45" t="inlineStr"/>
+      <c r="AX38" s="10" t="n"/>
+      <c r="AY38" s="10" t="n"/>
       <c r="AZ38" s="10" t="n"/>
-      <c r="BA38" s="11" t="n"/>
-      <c r="BB38" s="45" t="inlineStr"/>
+      <c r="BA38" s="10" t="n"/>
+      <c r="BB38" s="10" t="n"/>
       <c r="BC38" s="10" t="n"/>
-      <c r="BD38" s="11" t="n"/>
-      <c r="BE38" s="45" t="inlineStr"/>
+      <c r="BD38" s="10" t="n"/>
+      <c r="BE38" s="10" t="n"/>
       <c r="BF38" s="10" t="n"/>
-      <c r="BG38" s="11" t="n"/>
-      <c r="BH38" s="45" t="inlineStr"/>
+      <c r="BG38" s="10" t="n"/>
+      <c r="BH38" s="10" t="n"/>
       <c r="BI38" s="10" t="n"/>
-      <c r="BJ38" s="11" t="n"/>
-      <c r="BK38" s="46" t="inlineStr"/>
+      <c r="BJ38" s="10" t="n"/>
+      <c r="BK38" s="10" t="n"/>
       <c r="BL38" s="10" t="n"/>
       <c r="BM38" s="10" t="n"/>
       <c r="BN38" s="10" t="n"/>
@@ -12897,20 +12655,20 @@
       <c r="BP38" s="10" t="n"/>
       <c r="BQ38" s="11" t="n"/>
     </row>
-    <row r="39" ht="368" customHeight="1">
+    <row r="39" ht="450" customHeight="1">
       <c r="A39" s="44" t="n">
         <v>24</v>
       </c>
       <c r="B39" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-024</t>
+          <t>ACSMS-TC-011-023</t>
         </is>
       </c>
       <c r="C39" s="10" t="n"/>
       <c r="D39" s="11" t="n"/>
       <c r="E39" s="46" t="inlineStr">
         <is>
-          <t>Đăng ký mới — cố định số phần đăng ký 0 khi loại thủ tục「解約」</t>
+          <t>Đăng ký mới normal (lưu DB + tạo lịch sử + audit log)</t>
         </is>
       </c>
       <c r="F39" s="10" t="n"/>
@@ -12920,7 +12678,7 @@
       <c r="J39" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・Chọn loại thủ tục (tetsuzuki_shurui)=解約</t>
+・Đã nhập giá trị hợp lệ cho tất cả項目 bắt buộc (loại độc giả=紙版, loại thủ tục=新規, phương thức thanh toán=口座引落)</t>
         </is>
       </c>
       <c r="K39" s="10" t="n"/>
@@ -12945,7 +12703,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chọn「解約」ở loại thủ tục, ở trạng thái đã nhập「5」vào số phần đăng ký (dokusya_busu) rồi click button「承認・登録」
+            <t xml:space="preserve">Nhập tất cả項目 bắt buộc, click button「承認・登録」, click「はい」ở dialog xác nhận
 </t>
           </r>
           <r>
@@ -12962,7 +12720,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chạy query sau trong DB, xác nhận số phần đăng ký và cờ giải ước
+            <t xml:space="preserve">Xác nhận chuyển màn hình và message
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Chạy query sau trong DB, xác nhận record bản thể・lịch sử
 </t>
           </r>
           <r>
@@ -12978,15 +12753,31 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">SELECT dokusya_busu FROM t_dokusya WHERE dokusya_id = :new_dokusya_id;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT kaiyaku_flg, shinki_flg
+            <t xml:space="preserve">SELECT dokusya_id, rireki_no, tetsuzuki_shurui, dokusya_busu
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_dokusya
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE dokusya_id = :new_dokusya_id;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT rireki_no, saishin_data_flg, shinki_flg, kaiyaku_flg, zougen_hokoku_flg
 </t>
           </r>
           <r>
@@ -13002,7 +12793,80 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">WHERE dokusya_id = :new_dokusya_id AND saishin_data_flg = TRUE;
+            <t xml:space="preserve">WHERE dokusya_id = :new_dokusya_id;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Chạy query sau trong DB, xác nhận audit log
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT operation, result_status, target_table, ja_id
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_log
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE target_table = 't_dokusya' AND target_id = :new_dokusya_id
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ORDER BY log_datetime DESC
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">LIMIT 1;
 </t>
           </r>
           <r>
@@ -13036,7 +12900,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xử lý đăng ký được thực hiện, message đăng ký thành công `登録しました。` được hiển thị
+            <t xml:space="preserve">Dialog xác nhận được hiển thị, click「はい」thì xử lý đăng ký được thực hiện
 </t>
           </r>
           <r>
@@ -13053,7 +12917,41 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">dokusya_busu của t_dokusya được lưu là 0, kaiyaku_flg của t_dokusya_rireki là TRUE, shinki_flg là FALSE
+            <t xml:space="preserve">Trả về HTTP 201, message đăng ký thành công `登録しました。`（ACSMS-MSG-011-011）được hiển thị, chuyển về màn hình 購読者明細検索
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Record mới được đăng ký vào t_dokusya, record lịch sử (rireki_no=1, saishin_data_flg=true, shinki_flg=true, kaiyaku_flg=false, zougen_hokoku_flg=true) được đăng ký vào t_dokusya_rireki
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Record với operation=`CREATE`, result_status=1, target_table=`t_dokusya`, ja_id=100 được ghi vào t_log
 </t>
           </r>
           <r>
@@ -13070,15 +12968,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Khi đăng ký giải ước thì đặt số phần đăng ký là 0, kaiyaku_flg=TRUE (機能定義 §8.1)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Để chống tính phí hai lần, số phần đăng ký bị ép buộc về 0 khi giải ước</t>
+            <t xml:space="preserve">・Tạo t_dokusya + t_dokusya_rireki trong 1 transaction (機能定義 §2.6)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Khi phương thức thanh toán=口座引落 thì逆引き `m_shiten.jastem_toriatsukai_tenpo_code` / `jastem_tenpo_name` từ bank_shiten_id, lưu phi chuẩn hóa vào `t_dokusya.bank_branch_code` / `bank_branch_name`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Đăng ký (ghi nghiệp vụ) và audit log được thực hiện trong một transaction duy nhất</t>
           </r>
         </is>
       </c>
@@ -13132,20 +13038,20 @@
       <c r="BP39" s="10" t="n"/>
       <c r="BQ39" s="11" t="n"/>
     </row>
-    <row r="40" ht="304" customHeight="1">
+    <row r="40" ht="368" customHeight="1">
       <c r="A40" s="44" t="n">
         <v>25</v>
       </c>
       <c r="B40" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-025</t>
+          <t>ACSMS-TC-011-024</t>
         </is>
       </c>
       <c r="C40" s="10" t="n"/>
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="46" t="inlineStr">
         <is>
-          <t>Đăng ký mới — lưu copy khi địa chỉ giao「購読者情報と同じ」</t>
+          <t>Đăng ký mới — cố định số phần đăng ký 0 khi loại thủ tục「解約」</t>
         </is>
       </c>
       <c r="F40" s="10" t="n"/>
@@ -13155,8 +13061,7 @@
       <c r="J40" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・Loại độc giả=紙版
-・Check「購読者情報と同じ」(haitatsu_same_flg)</t>
+・Chọn loại thủ tục (tetsuzuki_shurui)=解約</t>
         </is>
       </c>
       <c r="K40" s="10" t="n"/>
@@ -13181,7 +13086,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Nhập họ tên độc giả・địa chỉ v.v., check「購読者情報と同じ」rồi click button「承認・登録」
+            <t xml:space="preserve">Chọn「解約」ở loại thủ tục, ở trạng thái đã nhập「5」vào số phần đăng ký (dokusya_busu) rồi click button「承認・登録」
 </t>
           </r>
           <r>
@@ -13198,7 +13103,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chạy query sau trong DB, xác nhận thông tin địa chỉ giao
+            <t xml:space="preserve">Chạy query sau trong DB, xác nhận số phần đăng ký và cờ giải ước
 </t>
           </r>
           <r>
@@ -13214,15 +13119,31 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">SELECT haitatsu_same_flg, haitatsu_yubin_no, haitatsu_shimei_sei
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_dokusya WHERE dokusya_id = :new_dokusya_id;
+            <t xml:space="preserve">SELECT dokusya_busu FROM t_dokusya WHERE dokusya_id = :new_dokusya_id;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT kaiyaku_flg, shinki_flg
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_dokusya_rireki
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE dokusya_id = :new_dokusya_id AND saishin_data_flg = TRUE;
 </t>
           </r>
           <r>
@@ -13273,7 +13194,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">haitatsu_same_flg được lưu là true, các項目 địa chỉ giao (haitatsu_yubin_no・haitatsu_shimei_sei v.v.) được lưu giá trị copy từ thông tin độc giả
+            <t xml:space="preserve">dokusya_busu của t_dokusya được lưu là 0, kaiyaku_flg của t_dokusya_rireki là TRUE, shinki_flg là FALSE
 </t>
           </r>
           <r>
@@ -13290,7 +13211,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・Khi check「購読者情報と同じ」thì copy từ thông tin độc giả lúc lưu DB (機能定義 §9.1)</t>
+            <t xml:space="preserve">・Khi đăng ký giải ước thì đặt số phần đăng ký là 0, kaiyaku_flg=TRUE (機能定義 §8.1)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Để chống tính phí hai lần, số phần đăng ký bị ép buộc về 0 khi giải ước</t>
           </r>
         </is>
       </c>
@@ -13344,20 +13273,20 @@
       <c r="BP40" s="10" t="n"/>
       <c r="BQ40" s="11" t="n"/>
     </row>
-    <row r="41" ht="384" customHeight="1">
+    <row r="41" ht="304" customHeight="1">
       <c r="A41" s="44" t="n">
         <v>26</v>
       </c>
       <c r="B41" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-026</t>
+          <t>ACSMS-TC-011-025</t>
         </is>
       </c>
       <c r="C41" s="10" t="n"/>
       <c r="D41" s="11" t="n"/>
       <c r="E41" s="46" t="inlineStr">
         <is>
-          <t>Đăng ký mới — validation tích hợp khi tất cả項目 chưa nhập</t>
+          <t>Đăng ký mới — lưu copy khi địa chỉ giao「購読者情報と同じ」</t>
         </is>
       </c>
       <c r="F41" s="10" t="n"/>
@@ -13367,7 +13296,8 @@
       <c r="J41" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・Đang mở màn hình đăng ký thông tin độc giả (chế độ tạo mới)</t>
+・Loại độc giả=紙版
+・Check「購読者情報と同じ」(haitatsu_same_flg)</t>
         </is>
       </c>
       <c r="K41" s="10" t="n"/>
@@ -13392,7 +13322,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Để trống tất cả項目 rồi click button「承認・登録」
+            <t xml:space="preserve">Nhập họ tên độc giả・địa chỉ v.v., check「購読者情報と同じ」rồi click button「承認・登録」
 </t>
           </r>
           <r>
@@ -13409,7 +13339,39 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận response của POST `/api/v1/dokusya` qua tab Network của DevTools</t>
+            <t xml:space="preserve">Chạy query sau trong DB, xác nhận thông tin địa chỉ giao
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT haitatsu_same_flg, haitatsu_yubin_no, haitatsu_shimei_sei
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_dokusya WHERE dokusya_id = :new_dokusya_id;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>```</t>
           </r>
         </is>
       </c>
@@ -13435,7 +13397,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Lỗi required `必須項目です。` hiển thị dưới từng項目 bắt buộc, xử lý đăng ký không được thực hiện
+            <t xml:space="preserve">Xử lý đăng ký được thực hiện, message đăng ký thành công `登録しました。` được hiển thị
 </t>
           </r>
           <r>
@@ -13452,7 +13414,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 400 (`error_code: VALIDATION_ERROR`, message `入力値が不正です。詳細はerrorsフィールドを確認してください。`, mảng `errors` chứa message từng項目 như shimei_sei・yubin_no)
+            <t xml:space="preserve">haitatsu_same_flg được lưu là true, các項目 địa chỉ giao (haitatsu_yubin_no・haitatsu_shimei_sei v.v.) được lưu giá trị copy từ thông tin độc giả
 </t>
           </r>
           <r>
@@ -13469,15 +13431,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Sau khi kiểm tra dữ liệu phía client (bắt buộc・format・tương quan), phía server cũng validation lại (機能定義 §2.1, §2.5)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Lỗi validation được trả về theo từng項目 trong mảng `errors`</t>
+            <t>・Khi check「購読者情報と同じ」thì copy từ thông tin độc giả lúc lưu DB (機能定義 §9.1)</t>
           </r>
         </is>
       </c>
@@ -13489,7 +13443,7 @@
       <c r="AD41" s="11" t="n"/>
       <c r="AE41" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF41" s="11" t="n"/>
@@ -13531,20 +13485,20 @@
       <c r="BP41" s="10" t="n"/>
       <c r="BQ41" s="11" t="n"/>
     </row>
-    <row r="42" ht="240" customHeight="1">
+    <row r="42" ht="384" customHeight="1">
       <c r="A42" s="44" t="n">
         <v>27</v>
       </c>
       <c r="B42" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-027</t>
+          <t>ACSMS-TC-011-026</t>
         </is>
       </c>
       <c r="C42" s="10" t="n"/>
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="46" t="inlineStr">
         <is>
-          <t>Đăng ký mới — hủy bằng button quay lại</t>
+          <t>Đăng ký mới — validation tích hợp khi tất cả項目 chưa nhập</t>
         </is>
       </c>
       <c r="F42" s="10" t="n"/>
@@ -13554,7 +13508,7 @@
       <c r="J42" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・Đã nhập một số項目 ở màn hình đăng ký thông tin độc giả (chế độ tạo mới)</t>
+・Đang mở màn hình đăng ký thông tin độc giả (chế độ tạo mới)</t>
         </is>
       </c>
       <c r="K42" s="10" t="n"/>
@@ -13579,7 +13533,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Click button「前の画面に戻る」
+            <t xml:space="preserve">Để trống tất cả項目 rồi click button「承認・登録」
 </t>
           </r>
           <r>
@@ -13596,7 +13550,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận màn hình đích đến và việc lưu dữ liệu đã nhập</t>
+            <t>Xác nhận response của POST `/api/v1/dokusya` qua tab Network của DevTools</t>
           </r>
         </is>
       </c>
@@ -13622,7 +13576,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chuyển về màn hình 購読者明細検索
+            <t xml:space="preserve">Lỗi required `必須項目です。` hiển thị dưới từng項目 bắt buộc, xử lý đăng ký không được thực hiện
 </t>
           </r>
           <r>
@@ -13639,7 +13593,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Dữ liệu đã nhập không được lưu (dữ liệu mới không được đăng ký vào t_dokusya)
+            <t xml:space="preserve">Trả về HTTP 400 (`error_code: VALIDATION_ERROR`, message `入力値が不正です。詳細はerrorsフィールドを確認してください。`, mảng `errors` chứa message từng項目 như shimei_sei・yubin_no)
 </t>
           </r>
           <r>
@@ -13656,15 +13610,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Click button「前の画面に戻る」thì chuyển về màn hình 購読者明細検索 (機能定義 §16)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Dữ liệu đã nhập vào form không được lưu</t>
+            <t xml:space="preserve">・Sau khi kiểm tra dữ liệu phía client (bắt buộc・format・tương quan), phía server cũng validation lại (機能定義 §2.1, §2.5)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Lỗi validation được trả về theo từng項目 trong mảng `errors`</t>
           </r>
         </is>
       </c>
@@ -13676,7 +13630,7 @@
       <c r="AD42" s="11" t="n"/>
       <c r="AE42" s="45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AF42" s="11" t="n"/>
@@ -13710,12 +13664,7 @@
       <c r="BH42" s="45" t="inlineStr"/>
       <c r="BI42" s="10" t="n"/>
       <c r="BJ42" s="11" t="n"/>
-      <c r="BK42" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BK42" s="46" t="inlineStr"/>
       <c r="BL42" s="10" t="n"/>
       <c r="BM42" s="10" t="n"/>
       <c r="BN42" s="10" t="n"/>
@@ -13723,74 +13672,191 @@
       <c r="BP42" s="10" t="n"/>
       <c r="BQ42" s="11" t="n"/>
     </row>
-    <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="32" t="inlineStr">
-        <is>
-          <t>Logic nghiệp vụ cập nhật (Sửa・Duyệt・Từ chối)</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="n"/>
+    <row r="43" ht="240" customHeight="1">
+      <c r="A43" s="44" t="n">
+        <v>28</v>
+      </c>
+      <c r="B43" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-027</t>
+        </is>
+      </c>
       <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="10" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="46" t="inlineStr">
+        <is>
+          <t>Đăng ký mới — hủy bằng button quay lại</t>
+        </is>
+      </c>
       <c r="F43" s="10" t="n"/>
       <c r="G43" s="10" t="n"/>
       <c r="H43" s="10" t="n"/>
-      <c r="I43" s="10" t="n"/>
-      <c r="J43" s="10" t="n"/>
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属）
+・Đã nhập một số項目 ở màn hình đăng ký thông tin độc giả (chế độ tạo mới)</t>
+        </is>
+      </c>
       <c r="K43" s="10" t="n"/>
       <c r="L43" s="10" t="n"/>
       <c r="M43" s="10" t="n"/>
       <c r="N43" s="10" t="n"/>
       <c r="O43" s="10" t="n"/>
-      <c r="P43" s="10" t="n"/>
-      <c r="Q43" s="10" t="n"/>
+      <c r="P43" s="11" t="n"/>
+      <c r="Q43" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Click button「前の画面に戻る」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Xác nhận màn hình đích đến và việc lưu dữ liệu đã nhập</t>
+          </r>
+        </is>
+      </c>
       <c r="R43" s="10" t="n"/>
       <c r="S43" s="10" t="n"/>
       <c r="T43" s="10" t="n"/>
       <c r="U43" s="10" t="n"/>
       <c r="V43" s="10" t="n"/>
-      <c r="W43" s="10" t="n"/>
-      <c r="X43" s="10" t="n"/>
+      <c r="W43" s="11" t="n"/>
+      <c r="X43" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Chuyển về màn hình 購読者明細検索
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Dữ liệu đã nhập không được lưu (dữ liệu mới không được đăng ký vào t_dokusya)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Click button「前の画面に戻る」thì chuyển về màn hình 購読者明細検索 (機能定義 §16)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Dữ liệu đã nhập vào form không được lưu</t>
+          </r>
+        </is>
+      </c>
       <c r="Y43" s="10" t="n"/>
       <c r="Z43" s="10" t="n"/>
       <c r="AA43" s="10" t="n"/>
       <c r="AB43" s="10" t="n"/>
       <c r="AC43" s="10" t="n"/>
-      <c r="AD43" s="10" t="n"/>
-      <c r="AE43" s="10" t="n"/>
-      <c r="AF43" s="10" t="n"/>
-      <c r="AG43" s="10" t="n"/>
+      <c r="AD43" s="11" t="n"/>
+      <c r="AE43" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF43" s="11" t="n"/>
+      <c r="AG43" s="45" t="inlineStr"/>
       <c r="AH43" s="10" t="n"/>
-      <c r="AI43" s="10" t="n"/>
-      <c r="AJ43" s="10" t="n"/>
+      <c r="AI43" s="11" t="n"/>
+      <c r="AJ43" s="45" t="inlineStr"/>
       <c r="AK43" s="10" t="n"/>
-      <c r="AL43" s="10" t="n"/>
-      <c r="AM43" s="10" t="n"/>
+      <c r="AL43" s="11" t="n"/>
+      <c r="AM43" s="45" t="inlineStr"/>
       <c r="AN43" s="10" t="n"/>
-      <c r="AO43" s="10" t="n"/>
-      <c r="AP43" s="10" t="n"/>
+      <c r="AO43" s="11" t="n"/>
+      <c r="AP43" s="45" t="inlineStr"/>
       <c r="AQ43" s="10" t="n"/>
-      <c r="AR43" s="10" t="n"/>
-      <c r="AS43" s="10" t="n"/>
+      <c r="AR43" s="11" t="n"/>
+      <c r="AS43" s="45" t="inlineStr"/>
       <c r="AT43" s="10" t="n"/>
-      <c r="AU43" s="10" t="n"/>
-      <c r="AV43" s="10" t="n"/>
+      <c r="AU43" s="11" t="n"/>
+      <c r="AV43" s="45" t="inlineStr"/>
       <c r="AW43" s="10" t="n"/>
-      <c r="AX43" s="10" t="n"/>
-      <c r="AY43" s="10" t="n"/>
+      <c r="AX43" s="11" t="n"/>
+      <c r="AY43" s="45" t="inlineStr"/>
       <c r="AZ43" s="10" t="n"/>
-      <c r="BA43" s="10" t="n"/>
-      <c r="BB43" s="10" t="n"/>
+      <c r="BA43" s="11" t="n"/>
+      <c r="BB43" s="45" t="inlineStr"/>
       <c r="BC43" s="10" t="n"/>
-      <c r="BD43" s="10" t="n"/>
-      <c r="BE43" s="10" t="n"/>
+      <c r="BD43" s="11" t="n"/>
+      <c r="BE43" s="45" t="inlineStr"/>
       <c r="BF43" s="10" t="n"/>
-      <c r="BG43" s="10" t="n"/>
-      <c r="BH43" s="10" t="n"/>
+      <c r="BG43" s="11" t="n"/>
+      <c r="BH43" s="45" t="inlineStr"/>
       <c r="BI43" s="10" t="n"/>
-      <c r="BJ43" s="10" t="n"/>
-      <c r="BK43" s="10" t="n"/>
+      <c r="BJ43" s="11" t="n"/>
+      <c r="BK43" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL43" s="10" t="n"/>
       <c r="BM43" s="10" t="n"/>
       <c r="BN43" s="10" t="n"/>
@@ -13798,228 +13864,74 @@
       <c r="BP43" s="10" t="n"/>
       <c r="BQ43" s="11" t="n"/>
     </row>
-    <row r="44" ht="448" customHeight="1">
-      <c r="A44" s="44" t="n">
-        <v>28</v>
-      </c>
-      <c r="B44" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-011-028</t>
-        </is>
-      </c>
+    <row r="44" ht="22.5" customHeight="1">
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t>Logic nghiệp vụ cập nhật (Sửa・Duyệt・Từ chối)</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n"/>
       <c r="C44" s="10" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="46" t="inlineStr">
-        <is>
-          <t>Chế độ sửa load form (phản ánh dữ liệu hiện có)</t>
-        </is>
-      </c>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
       <c r="F44" s="10" t="n"/>
       <c r="G44" s="10" t="n"/>
       <c r="H44" s="10" t="n"/>
-      <c r="I44" s="11" t="n"/>
-      <c r="J44" s="46" t="inlineStr">
-        <is>
-          <t>・role: JA_HONTEN（ja_id=100 所属）
-・Tồn tại độc giả có loại độc giả=紙版 (dokusya_id=100)</t>
-        </is>
-      </c>
+      <c r="I44" s="10" t="n"/>
+      <c r="J44" s="10" t="n"/>
       <c r="K44" s="10" t="n"/>
       <c r="L44" s="10" t="n"/>
       <c r="M44" s="10" t="n"/>
       <c r="N44" s="10" t="n"/>
       <c r="O44" s="10" t="n"/>
-      <c r="P44" s="11" t="n"/>
-      <c r="Q44" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Click dòng độc giả đối tượng từ danh sách màn hình 購読者明細検索, mở màn hình đăng ký thông tin độc giả ở chế độ sửa
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Xác nhận response của GET `/api/v1/dokusya/100` qua tab Network của DevTools
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Xác nhận giá trị từng項目 form và hiển thị của 購読者ID (dokusya_id)・履歴No (rireki_no)</t>
-          </r>
-        </is>
-      </c>
+      <c r="P44" s="10" t="n"/>
+      <c r="Q44" s="10" t="n"/>
       <c r="R44" s="10" t="n"/>
       <c r="S44" s="10" t="n"/>
       <c r="T44" s="10" t="n"/>
       <c r="U44" s="10" t="n"/>
       <c r="V44" s="10" t="n"/>
-      <c r="W44" s="11" t="n"/>
-      <c r="X44" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Màn hình đăng ký thông tin độc giả được hiển thị ở chế độ sửa
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Trả về HTTP 200 (tất cả項目 của độc giả đối tượng được chứa trong `data`, bank_shiten_id được trả về để re-hydration dropdown)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Dữ liệu hiện có được phản ánh vào từng項目 form, 購読者ID (dokusya_id) hiển thị không thể thay đổi
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Ở chế độ sửa thì lấy dữ liệu độc giả bằng ID và phản ánh vào form (機能定義 §15.1)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・購読者ID không thể thay đổi
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Khi lấy dữ liệu thất bại thì hiển thị ACSMS-MSG-011-016 `購読者ID #{id} が見つかりません。`</t>
-          </r>
-        </is>
-      </c>
+      <c r="W44" s="10" t="n"/>
+      <c r="X44" s="10" t="n"/>
       <c r="Y44" s="10" t="n"/>
       <c r="Z44" s="10" t="n"/>
       <c r="AA44" s="10" t="n"/>
       <c r="AB44" s="10" t="n"/>
       <c r="AC44" s="10" t="n"/>
-      <c r="AD44" s="11" t="n"/>
-      <c r="AE44" s="45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AF44" s="11" t="n"/>
-      <c r="AG44" s="45" t="inlineStr"/>
+      <c r="AD44" s="10" t="n"/>
+      <c r="AE44" s="10" t="n"/>
+      <c r="AF44" s="10" t="n"/>
+      <c r="AG44" s="10" t="n"/>
       <c r="AH44" s="10" t="n"/>
-      <c r="AI44" s="11" t="n"/>
-      <c r="AJ44" s="45" t="inlineStr"/>
+      <c r="AI44" s="10" t="n"/>
+      <c r="AJ44" s="10" t="n"/>
       <c r="AK44" s="10" t="n"/>
-      <c r="AL44" s="11" t="n"/>
-      <c r="AM44" s="45" t="inlineStr"/>
+      <c r="AL44" s="10" t="n"/>
+      <c r="AM44" s="10" t="n"/>
       <c r="AN44" s="10" t="n"/>
-      <c r="AO44" s="11" t="n"/>
-      <c r="AP44" s="45" t="inlineStr"/>
+      <c r="AO44" s="10" t="n"/>
+      <c r="AP44" s="10" t="n"/>
       <c r="AQ44" s="10" t="n"/>
-      <c r="AR44" s="11" t="n"/>
-      <c r="AS44" s="45" t="inlineStr"/>
+      <c r="AR44" s="10" t="n"/>
+      <c r="AS44" s="10" t="n"/>
       <c r="AT44" s="10" t="n"/>
-      <c r="AU44" s="11" t="n"/>
-      <c r="AV44" s="45" t="inlineStr"/>
+      <c r="AU44" s="10" t="n"/>
+      <c r="AV44" s="10" t="n"/>
       <c r="AW44" s="10" t="n"/>
-      <c r="AX44" s="11" t="n"/>
-      <c r="AY44" s="45" t="inlineStr"/>
+      <c r="AX44" s="10" t="n"/>
+      <c r="AY44" s="10" t="n"/>
       <c r="AZ44" s="10" t="n"/>
-      <c r="BA44" s="11" t="n"/>
-      <c r="BB44" s="45" t="inlineStr"/>
+      <c r="BA44" s="10" t="n"/>
+      <c r="BB44" s="10" t="n"/>
       <c r="BC44" s="10" t="n"/>
-      <c r="BD44" s="11" t="n"/>
-      <c r="BE44" s="45" t="inlineStr"/>
+      <c r="BD44" s="10" t="n"/>
+      <c r="BE44" s="10" t="n"/>
       <c r="BF44" s="10" t="n"/>
-      <c r="BG44" s="11" t="n"/>
-      <c r="BH44" s="45" t="inlineStr"/>
+      <c r="BG44" s="10" t="n"/>
+      <c r="BH44" s="10" t="n"/>
       <c r="BI44" s="10" t="n"/>
-      <c r="BJ44" s="11" t="n"/>
-      <c r="BK44" s="46" t="inlineStr"/>
+      <c r="BJ44" s="10" t="n"/>
+      <c r="BK44" s="10" t="n"/>
       <c r="BL44" s="10" t="n"/>
       <c r="BM44" s="10" t="n"/>
       <c r="BN44" s="10" t="n"/>
@@ -14027,20 +13939,20 @@
       <c r="BP44" s="10" t="n"/>
       <c r="BQ44" s="11" t="n"/>
     </row>
-    <row r="45" ht="450" customHeight="1">
+    <row r="45" ht="448" customHeight="1">
       <c r="A45" s="44" t="n">
         <v>29</v>
       </c>
       <c r="B45" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-029</t>
+          <t>ACSMS-TC-011-028</t>
         </is>
       </c>
       <c r="C45" s="10" t="n"/>
       <c r="D45" s="11" t="n"/>
       <c r="E45" s="46" t="inlineStr">
         <is>
-          <t>Cập nhật normal (phương thức追記 lịch sử + audit log)</t>
+          <t>Chế độ sửa load form (phản ánh dữ liệu hiện có)</t>
         </is>
       </c>
       <c r="F45" s="10" t="n"/>
@@ -14050,7 +13962,7 @@
       <c r="J45" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・Tồn tại độc giả có loại độc giả=紙版 (dokusya_id=100, rireki_no hiện tại=1)</t>
+・Tồn tại độc giả có loại độc giả=紙版 (dokusya_id=100)</t>
         </is>
       </c>
       <c r="K45" s="10" t="n"/>
@@ -14075,7 +13987,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Mở màn hình đăng ký thông tin độc giả ở chế độ sửa, đổi số phần đăng ký (dokusya_busu) từ 1 sang 2 rồi click button「承認・登録」
+            <t xml:space="preserve">Click dòng độc giả đối tượng từ danh sách màn hình 購読者明細検索, mở màn hình đăng ký thông tin độc giả ở chế độ sửa
 </t>
           </r>
           <r>
@@ -14092,7 +14004,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xác nhận chuyển màn hình và message
+            <t xml:space="preserve">Xác nhận response của GET `/api/v1/dokusya/100` qua tab Network của DevTools
 </t>
           </r>
           <r>
@@ -14109,136 +14021,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chạy query sau trong DB, xác nhận record bản thể・lịch sử
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">```sql
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT rireki_no, dokusya_busu FROM t_dokusya WHERE dokusya_id = 100;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT rireki_no, saishin_data_flg, zougen_hokoku_flg
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_dokusya_rireki
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE dokusya_id = 100
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ORDER BY rireki_no DESC;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">```
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Chạy query sau trong DB, xác nhận audit log
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">```sql
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT operation, result_status, before_value, after_value
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_log
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE target_table = 't_dokusya' AND target_id = 100
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ORDER BY log_datetime DESC
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">LIMIT 1;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>```</t>
+            <t>Xác nhận giá trị từng項目 form và hiển thị của 購読者ID (dokusya_id)・履歴No (rireki_no)</t>
           </r>
         </is>
       </c>
@@ -14264,7 +14047,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xử lý cập nhật được thực hiện
+            <t xml:space="preserve">Màn hình đăng ký thông tin độc giả được hiển thị ở chế độ sửa
 </t>
           </r>
           <r>
@@ -14281,7 +14064,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 200, message update thành công `更新しました。`（ACSMS-MSG-011-015）được hiển thị, quay về màn hình 購読者明細検索
+            <t xml:space="preserve">Trả về HTTP 200 (tất cả項目 của độc giả đối tượng được chứa trong `data`, bank_shiten_id được trả về để re-hydration dropdown)
 </t>
           </r>
           <r>
@@ -14298,24 +14081,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">rireki_no của t_dokusya được update thành 2 và dokusya_busu thành 2, lịch sử mới (rireki_no=2, saishin_data_flg=true, zougen_hokoku_flg=true) được追記 vào t_dokusya_rireki, saishin_data_flg của lịch sử cũ (rireki_no=1) được update thành false
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Record với operation=`UPDATE`, result_status=1 được ghi vào t_log, before_value lưu dữ liệu trước update, after_value lưu dữ liệu sau update
+            <t xml:space="preserve">Dữ liệu hiện có được phản ánh vào từng項目 form, 購読者ID (dokusya_id) hiển thị không thể thay đổi
 </t>
           </r>
           <r>
@@ -14332,23 +14098,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Cập nhật không phải update vật lý record hiện có mà là追記 record với số lịch sử mới (機能定義 §15.3)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Update cờ dữ liệu mới nhất của lịch sử cũ thành false, cờ dữ liệu mới nhất của lịch sử mới thành true
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Cập nhật (ghi nghiệp vụ) và audit log được thực hiện trong một transaction duy nhất</t>
+            <t xml:space="preserve">・Ở chế độ sửa thì lấy dữ liệu độc giả bằng ID và phản ánh vào form (機能定義 §15.1)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・購読者ID không thể thay đổi
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Khi lấy dữ liệu thất bại thì hiển thị ACSMS-MSG-011-016 `購読者ID #{id} が見つかりません。`</t>
           </r>
         </is>
       </c>
@@ -14408,14 +14174,14 @@
       </c>
       <c r="B46" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-030</t>
+          <t>ACSMS-TC-011-029</t>
         </is>
       </c>
       <c r="C46" s="10" t="n"/>
       <c r="D46" s="11" t="n"/>
       <c r="E46" s="46" t="inlineStr">
         <is>
-          <t>Kiểm soát read-only của độc giả 純電子版 (thanh toán thẻ tín dụng)・併読</t>
+          <t>Cập nhật normal (phương thức追記 lịch sử + audit log)</t>
         </is>
       </c>
       <c r="F46" s="10" t="n"/>
@@ -14425,7 +14191,7 @@
       <c r="J46" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・Tồn tại độc giả loại độc giả=電子版 (thanh toán thẻ tín dụng) (dokusya_id=300)</t>
+・Tồn tại độc giả có loại độc giả=紙版 (dokusya_id=100, rireki_no hiện tại=1)</t>
         </is>
       </c>
       <c r="K46" s="10" t="n"/>
@@ -14450,7 +14216,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Click dòng độc giả 電子版 thanh toán thẻ tín dụng từ danh sách màn hình 購読者明細検索, mở màn hình ở chế độ sửa
+            <t xml:space="preserve">Mở màn hình đăng ký thông tin độc giả ở chế độ sửa, đổi số phần đăng ký (dokusya_busu) từ 1 sang 2 rồi click button「承認・登録」
 </t>
           </r>
           <r>
@@ -14467,7 +14233,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xác nhận khả năng nhập của từng項目 form
+            <t xml:space="preserve">Xác nhận chuyển màn hình và message
 </t>
           </r>
           <r>
@@ -14484,7 +14250,136 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Gửi trực tiếp PUT `/api/v1/dokusya/300` kèm nội dung sửa qua tab Network của DevTools</t>
+            <t xml:space="preserve">Chạy query sau trong DB, xác nhận record bản thể・lịch sử
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT rireki_no, dokusya_busu FROM t_dokusya WHERE dokusya_id = 100;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT rireki_no, saishin_data_flg, zougen_hokoku_flg
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_dokusya_rireki
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE dokusya_id = 100
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ORDER BY rireki_no DESC;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Chạy query sau trong DB, xác nhận audit log
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT operation, result_status, before_value, after_value
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_log
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE target_table = 't_dokusya' AND target_id = 100
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ORDER BY log_datetime DESC
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">LIMIT 1;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>```</t>
           </r>
         </is>
       </c>
@@ -14510,7 +14405,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Màn hình đăng ký thông tin độc giả được hiển thị ở chế độ tham chiếu trong chế độ sửa
+            <t xml:space="preserve">Xử lý cập nhật được thực hiện
 </t>
           </r>
           <r>
@@ -14527,7 +14422,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">購読開始日 (dokusya_kaishi_date)・購読中止日 (dokusya_chushi_date) v.v. hiển thị read-only (dữ liệu liên kết từ hệ thống quản lý độc giả bản điện tử)
+            <t xml:space="preserve">Trả về HTTP 200, message update thành công `更新しました。`（ACSMS-MSG-011-015）được hiển thị, quay về màn hình 購読者明細検索
 </t>
           </r>
           <r>
@@ -14544,7 +14439,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Phía backend từ chối việc sửa độc giả 電子版 thanh toán thẻ tín dụng (không thể sửa theo quy tắc nghiệp vụ)
+            <t xml:space="preserve">rireki_no của t_dokusya được update thành 2 và dokusya_busu thành 2, lịch sử mới (rireki_no=2, saishin_data_flg=true, zougen_hokoku_flg=true) được追記 vào t_dokusya_rireki, saishin_data_flg của lịch sử cũ (rireki_no=1) được update thành false
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Record với operation=`UPDATE`, result_status=1 được ghi vào t_log, before_value lưu dữ liệu trước update, after_value lưu dữ liệu sau update
 </t>
           </r>
           <r>
@@ -14561,15 +14473,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Độc giả 電子版 thuần túy (thanh toán thẻ tín dụng) do quản lý độc giả được chủ đạo phía hệ thống Web bên ngoài nên màn hình này chỉ tham chiếu (read-only) (機能定義 §15.1)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Độc giả 電子版 thanh toán thẻ tín dụng・併読 không thể sửa・xóa (quy tắc nghiệp vụ, 機能定義 §1.2)</t>
+            <t xml:space="preserve">・Cập nhật không phải update vật lý record hiện có mà là追記 record với số lịch sử mới (機能定義 §15.3)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Update cờ dữ liệu mới nhất của lịch sử cũ thành false, cờ dữ liệu mới nhất của lịch sử mới thành true
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Cập nhật (ghi nghiệp vụ) và audit log được thực hiện trong một transaction duy nhất</t>
           </r>
         </is>
       </c>
@@ -14581,7 +14501,7 @@
       <c r="AD46" s="11" t="n"/>
       <c r="AE46" s="45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF46" s="11" t="n"/>
@@ -14623,20 +14543,20 @@
       <c r="BP46" s="10" t="n"/>
       <c r="BQ46" s="11" t="n"/>
     </row>
-    <row r="47" ht="432" customHeight="1">
+    <row r="47" ht="450" customHeight="1">
       <c r="A47" s="44" t="n">
         <v>31</v>
       </c>
       <c r="B47" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-031</t>
+          <t>ACSMS-TC-011-030</t>
         </is>
       </c>
       <c r="C47" s="10" t="n"/>
       <c r="D47" s="11" t="n"/>
       <c r="E47" s="46" t="inlineStr">
         <is>
-          <t>Xung đột sửa đồng thời (optimistic lock)</t>
+          <t>Kiểm soát read-only của độc giả 純電子版 (thanh toán thẻ tín dụng)・併読</t>
         </is>
       </c>
       <c r="F47" s="10" t="n"/>
@@ -14646,7 +14566,7 @@
       <c r="J47" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・Đang mở độc giả (dokusya_id=100) ở chế độ sửa trên 2 tab trình duyệt</t>
+・Tồn tại độc giả loại độc giả=電子版 (thanh toán thẻ tín dụng) (dokusya_id=300)</t>
         </is>
       </c>
       <c r="K47" s="10" t="n"/>
@@ -14671,7 +14591,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Ở tab A đổi số phần đăng ký (dokusya_busu) rồi click button「承認・登録」(update thành công)
+            <t xml:space="preserve">Click dòng độc giả 電子版 thanh toán thẻ tín dụng từ danh sách màn hình 購読者明細検索, mở màn hình ở chế độ sửa
 </t>
           </r>
           <r>
@@ -14688,7 +14608,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Ở tab B (giữ dữ liệu trước khi tab A update) đổi 市町村郡 (shikuchoson) rồi click button「承認・登録」
+            <t xml:space="preserve">Xác nhận khả năng nhập của từng項目 form
 </t>
           </r>
           <r>
@@ -14705,47 +14625,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chạy query sau trong DB, xác nhận nội dung lịch sử mới nhất
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">```sql
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT rireki_no, dokusya_busu, shikuchoson
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">FROM t_dokusya_rireki
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">WHERE dokusya_id = 100 AND saishin_data_flg = TRUE;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>```</t>
+            <t>Gửi trực tiếp PUT `/api/v1/dokusya/300` kèm nội dung sửa qua tab Network của DevTools</t>
           </r>
         </is>
       </c>
@@ -14771,7 +14651,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xử lý update của tab A được thực hiện, message update thành công `更新しました。` được hiển thị
+            <t xml:space="preserve">Màn hình đăng ký thông tin độc giả được hiển thị ở chế độ tham chiếu trong chế độ sửa
 </t>
           </r>
           <r>
@@ -14788,7 +14668,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xung đột được phát hiện khi update tab B (trường hợp update sau thắng thì thay đổi của tab A không bị mất)
+            <t xml:space="preserve">購読開始日 (dokusya_kaishi_date)・購読中止日 (dokusya_chushi_date) v.v. hiển thị read-only (dữ liệu liên kết từ hệ thống quản lý độc giả bản điện tử)
 </t>
           </r>
           <r>
@@ -14805,7 +14685,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Đảm bảo tính toàn vẹn dữ liệu, lịch sử có saishin_data_flg=TRUE chỉ có 1 record
+            <t xml:space="preserve">Phía backend từ chối việc sửa độc giả 電子版 thanh toán thẻ tín dụng (không thể sửa theo quy tắc nghiệp vụ)
 </t>
           </r>
           <r>
@@ -14822,15 +14702,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Bảng lịch sử là追記専用, record có cờ dữ liệu mới nhất (saishin_data_flg) TRUE chỉ có 1 record cho mỗi購読者ID (機能定義 §14.2)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Việc có/không hiện thực optimistic lock theo thiết kế, nếu chưa hiện thực thì lập bug ticket riêng</t>
+            <t xml:space="preserve">・Độc giả 電子版 thuần túy (thanh toán thẻ tín dụng) do quản lý độc giả được chủ đạo phía hệ thống Web bên ngoài nên màn hình này chỉ tham chiếu (read-only) (機能定義 §15.1)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Độc giả 電子版 thanh toán thẻ tín dụng・併読 không thể sửa・xóa (quy tắc nghiệp vụ, 機能定義 §1.2)</t>
           </r>
         </is>
       </c>
@@ -14876,11 +14756,7 @@
       <c r="BH47" s="45" t="inlineStr"/>
       <c r="BI47" s="10" t="n"/>
       <c r="BJ47" s="11" t="n"/>
-      <c r="BK47" s="46" t="inlineStr">
-        <is>
-          <t>Message chuyên dụng khi xung đột optimistic lock chưa được định nghĩa trong thiết kế, TC này chỉ kiểm chứng HTTP code và tính toàn vẹn dữ liệu (message chờ xác nhận thiết kế).</t>
-        </is>
-      </c>
+      <c r="BK47" s="46" t="inlineStr"/>
       <c r="BL47" s="10" t="n"/>
       <c r="BM47" s="10" t="n"/>
       <c r="BN47" s="10" t="n"/>
@@ -14888,20 +14764,20 @@
       <c r="BP47" s="10" t="n"/>
       <c r="BQ47" s="11" t="n"/>
     </row>
-    <row r="48" ht="448" customHeight="1">
+    <row r="48" ht="432" customHeight="1">
       <c r="A48" s="44" t="n">
         <v>32</v>
       </c>
       <c r="B48" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-032</t>
+          <t>ACSMS-TC-011-031</t>
         </is>
       </c>
       <c r="C48" s="10" t="n"/>
       <c r="D48" s="11" t="n"/>
       <c r="E48" s="46" t="inlineStr">
         <is>
-          <t>Duyệt bản điện tử normal (denshi_shonin_status 0→1)</t>
+          <t>Xung đột sửa đồng thời (optimistic lock)</t>
         </is>
       </c>
       <c r="F48" s="10" t="n"/>
@@ -14910,8 +14786,8 @@
       <c r="I48" s="11" t="n"/>
       <c r="J48" s="46" t="inlineStr">
         <is>
-          <t>・role: JA_HONTEN（ja_id=100 所属, có cờ xử lý bản điện tử）
-・Tồn tại độc giả loại độc giả=電子版 và denshi_shonin_status=0 (chờ duyệt) (dokusya_id=200, rireki_no hiện tại=1)</t>
+          <t>・role: JA_HONTEN（ja_id=100 所属）
+・Đang mở độc giả (dokusya_id=100) ở chế độ sửa trên 2 tab trình duyệt</t>
         </is>
       </c>
       <c r="K48" s="10" t="n"/>
@@ -14936,7 +14812,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Mở độc giả chờ duyệt ở chế độ sửa, click button「承認・登録」
+            <t xml:space="preserve">Ở tab A đổi số phần đăng ký (dokusya_busu) rồi click button「承認・登録」(update thành công)
 </t>
           </r>
           <r>
@@ -14953,7 +14829,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xác nhận chuyển màn hình và message
+            <t xml:space="preserve">Ở tab B (giữ dữ liệu trước khi tab A update) đổi 市町村郡 (shikuchoson) rồi click button「承認・登録」
 </t>
           </r>
           <r>
@@ -14970,7 +14846,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chạy query sau trong DB, xác nhận status và lịch sử
+            <t xml:space="preserve">Chạy query sau trong DB, xác nhận nội dung lịch sử mới nhất
 </t>
           </r>
           <r>
@@ -14986,15 +14862,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">SELECT denshi_shonin_status, rireki_no FROM t_dokusya WHERE dokusya_id = 200;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT rireki_no, denshi_shonin_status, saishin_data_flg, henko_riyu
+            <t xml:space="preserve">SELECT rireki_no, dokusya_busu, shikuchoson
 </t>
           </r>
           <r>
@@ -15010,15 +14878,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">WHERE dokusya_id = 200
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ORDER BY rireki_no DESC;
+            <t xml:space="preserve">WHERE dokusya_id = 100 AND saishin_data_flg = TRUE;
 </t>
           </r>
           <r>
@@ -15052,7 +14912,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xử lý duyệt được thực hiện
+            <t xml:space="preserve">Xử lý update của tab A được thực hiện, message update thành công `更新しました。` được hiển thị
 </t>
           </r>
           <r>
@@ -15069,7 +14929,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 200 (`data.denshi_shonin_status = 1`), message `承認しました。` được hiển thị
+            <t xml:space="preserve">Xung đột được phát hiện khi update tab B (trường hợp update sau thắng thì thay đổi của tab A không bị mất)
 </t>
           </r>
           <r>
@@ -15086,7 +14946,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">denshi_shonin_status của t_dokusya được update thành 1, lịch sử mới (denshi_shonin_status=1, saishin_data_flg=true, henko_riyu=`電子版承認`) được追記 vào t_dokusya_rireki
+            <t xml:space="preserve">Đảm bảo tính toàn vẹn dữ liệu, lịch sử có saishin_data_flg=TRUE chỉ có 1 record
 </t>
           </r>
           <r>
@@ -15103,23 +14963,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Click button「承認」thì API đặt denshi_shonin_status=1 (đã duyệt) và tạo record lịch sử mới (機能定義 §3.3)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Gọi PUT `/api/v1/dokusya/{dokusya_id}/approve`
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Duyệt (ghi nghiệp vụ) và audit log được thực hiện trong một transaction duy nhất</t>
+            <t xml:space="preserve">・Bảng lịch sử là追記専用, record có cờ dữ liệu mới nhất (saishin_data_flg) TRUE chỉ có 1 record cho mỗi購読者ID (機能定義 §14.2)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Việc có/không hiện thực optimistic lock theo thiết kế, nếu chưa hiện thực thì lập bug ticket riêng</t>
           </r>
         </is>
       </c>
@@ -15131,7 +14983,7 @@
       <c r="AD48" s="11" t="n"/>
       <c r="AE48" s="45" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AF48" s="11" t="n"/>
@@ -15165,7 +15017,11 @@
       <c r="BH48" s="45" t="inlineStr"/>
       <c r="BI48" s="10" t="n"/>
       <c r="BJ48" s="11" t="n"/>
-      <c r="BK48" s="46" t="inlineStr"/>
+      <c r="BK48" s="46" t="inlineStr">
+        <is>
+          <t>Message chuyên dụng khi xung đột optimistic lock chưa được định nghĩa trong thiết kế, TC này chỉ kiểm chứng HTTP code và tính toàn vẹn dữ liệu (message chờ xác nhận thiết kế).</t>
+        </is>
+      </c>
       <c r="BL48" s="10" t="n"/>
       <c r="BM48" s="10" t="n"/>
       <c r="BN48" s="10" t="n"/>
@@ -15173,20 +15029,20 @@
       <c r="BP48" s="10" t="n"/>
       <c r="BQ48" s="11" t="n"/>
     </row>
-    <row r="49" ht="450" customHeight="1">
+    <row r="49" ht="432" customHeight="1">
       <c r="A49" s="44" t="n">
         <v>33</v>
       </c>
       <c r="B49" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-033</t>
+          <t>ACSMS-TC-011-032</t>
         </is>
       </c>
       <c r="C49" s="10" t="n"/>
       <c r="D49" s="11" t="n"/>
       <c r="E49" s="46" t="inlineStr">
         <is>
-          <t>Từ chối bản điện tử normal (xác nhận từ chối + denshi_shonin_status 0→2)</t>
+          <t>Duyệt bản điện tử normal (denshi_shonin_status 0→1)</t>
         </is>
       </c>
       <c r="F49" s="10" t="n"/>
@@ -15196,7 +15052,7 @@
       <c r="J49" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属, có cờ xử lý bản điện tử）
-・Tồn tại độc giả loại độc giả=電子版 và denshi_shonin_status=0 (chờ duyệt) (dokusya_id=201)</t>
+・Tồn tại độc giả loại độc giả=電子版 và denshi_shonin_status=0 (chờ duyệt) (dokusya_id=200, rireki_no hiện tại=1)</t>
         </is>
       </c>
       <c r="K49" s="10" t="n"/>
@@ -15221,7 +15077,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Mở độc giả chờ duyệt ở chế độ sửa, xác nhận hiển thị của button「承認しない」
+            <t xml:space="preserve">Mở độc giả chờ duyệt ở chế độ sửa, click button「承認・登録」
 </t>
           </r>
           <r>
@@ -15238,7 +15094,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Click button「承認しない」, click「はい」ở dialog xác nhận từ chối
+            <t xml:space="preserve">Xác nhận chuyển màn hình và message
 </t>
           </r>
           <r>
@@ -15255,23 +15111,6 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xác nhận chuyển màn hình và message
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
             <t xml:space="preserve">Chạy query sau trong DB, xác nhận status và lịch sử
 </t>
           </r>
@@ -15288,15 +15127,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">SELECT denshi_shonin_status FROM t_dokusya WHERE dokusya_id = 201;
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">SELECT denshi_shonin_status, henko_riyu
+            <t xml:space="preserve">SELECT denshi_shonin_status, rireki_no FROM t_dokusya WHERE dokusya_id = 200;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT rireki_no, denshi_shonin_status, saishin_data_flg
 </t>
           </r>
           <r>
@@ -15312,7 +15151,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">WHERE dokusya_id = 201 AND saishin_data_flg = TRUE;
+            <t xml:space="preserve">WHERE dokusya_id = 200
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ORDER BY rireki_no DESC;
 </t>
           </r>
           <r>
@@ -15346,7 +15193,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Do denshi_shonin_status=0 (chờ duyệt) nên button「承認しない」được hiển thị
+            <t xml:space="preserve">Xử lý duyệt được thực hiện
 </t>
           </r>
           <r>
@@ -15363,7 +15210,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Dialog xác nhận từ chối được hiển thị (message `電子版読者の登録を否認します。よろしいですか？`), click「はい」thì xử lý từ chối được thực hiện
+            <t xml:space="preserve">Trả về HTTP 200 (`data.denshi_shonin_status = 1`), message `承認しました。` được hiển thị
 </t>
           </r>
           <r>
@@ -15380,24 +15227,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 200 (`data.denshi_shonin_status = 2`), message `否認しました。` được hiển thị, chuyển về màn hình 購読者明細検索
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ4：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">denshi_shonin_status của t_dokusya được update thành 2, lịch sử mới nhất của t_dokusya_rireki ghi denshi_shonin_status=2, henko_riyu=`電子版否認`
+            <t xml:space="preserve">denshi_shonin_status của t_dokusya được update thành 1, lịch sử mới (denshi_shonin_status=1, saishin_data_flg=true) được追記 vào t_dokusya_rireki
 </t>
           </r>
           <r>
@@ -15414,23 +15244,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Chỉ khi denshi_shonin_status=0 mới hiển thị button「承認しない」(機能定義 §4.1)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Click「承認しない」thì hiển thị dialog xác nhận từ chối (ACSMS-MSG-011-014 `電子版読者の登録を否認します。よろしいですか？`) (機能定義 §4.2)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Click「はい」thì gọi PUT `/api/v1/dokusya/{dokusya_id}/reject` và đặt denshi_shonin_status=2 (機能定義 §4.3)</t>
+            <t xml:space="preserve">・Click button「承認」thì API đặt denshi_shonin_status=1 (đã duyệt) và tạo record lịch sử mới (機能定義 §3.3)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Gọi PUT `/api/v1/dokusya/{dokusya_id}/approve`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Duyệt (ghi nghiệp vụ) và audit log được thực hiện trong một transaction duy nhất</t>
           </r>
         </is>
       </c>
@@ -15484,20 +15314,20 @@
       <c r="BP49" s="10" t="n"/>
       <c r="BQ49" s="11" t="n"/>
     </row>
-    <row r="50" ht="304" customHeight="1">
+    <row r="50" ht="450" customHeight="1">
       <c r="A50" s="44" t="n">
         <v>34</v>
       </c>
       <c r="B50" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-034</t>
+          <t>ACSMS-TC-011-033</t>
         </is>
       </c>
       <c r="C50" s="10" t="n"/>
       <c r="D50" s="11" t="n"/>
       <c r="E50" s="46" t="inlineStr">
         <is>
-          <t>Ngắt xử lý khi click「いいえ」ở dialog xác nhận từ chối</t>
+          <t>Từ chối bản điện tử normal (xác nhận từ chối + denshi_shonin_status 0→2)</t>
         </is>
       </c>
       <c r="F50" s="10" t="n"/>
@@ -15507,7 +15337,7 @@
       <c r="J50" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属, có cờ xử lý bản điện tử）
-・Tồn tại độc giả denshi_shonin_status=0 (chờ duyệt) (dokusya_id=202)</t>
+・Tồn tại độc giả loại độc giả=電子版 và denshi_shonin_status=0 (chờ duyệt) (dokusya_id=201)</t>
         </is>
       </c>
       <c r="K50" s="10" t="n"/>
@@ -15532,7 +15362,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Mở độc giả chờ duyệt ở chế độ sửa, click button「承認しない」
+            <t xml:space="preserve">Mở độc giả chờ duyệt ở chế độ sửa, xác nhận hiển thị của button「承認しない」
 </t>
           </r>
           <r>
@@ -15549,7 +15379,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Click「いいえ」ở dialog xác nhận từ chối
+            <t xml:space="preserve">Click button「承認しない」, click「はい」ở dialog xác nhận từ chối
 </t>
           </r>
           <r>
@@ -15566,7 +15396,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chạy query sau trong DB, xác nhận status
+            <t xml:space="preserve">Xác nhận chuyển màn hình và message
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Chạy query sau trong DB, xác nhận status và lịch sử
 </t>
           </r>
           <r>
@@ -15582,7 +15429,31 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">SELECT denshi_shonin_status FROM t_dokusya WHERE dokusya_id = 202;
+            <t xml:space="preserve">SELECT denshi_shonin_status FROM t_dokusya WHERE dokusya_id = 201;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT denshi_shonin_status
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">FROM t_dokusya_rireki
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">WHERE dokusya_id = 201 AND saishin_data_flg = TRUE;
 </t>
           </r>
           <r>
@@ -15616,7 +15487,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Dialog xác nhận từ chối được hiển thị
+            <t xml:space="preserve">Do denshi_shonin_status=0 (chờ duyệt) nên button「承認しない」được hiển thị
 </t>
           </r>
           <r>
@@ -15633,7 +15504,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xử lý từ chối không được thực hiện, màn hình hiện tại được giữ nguyên
+            <t xml:space="preserve">Dialog xác nhận từ chối được hiển thị (message `電子版読者の登録を否認します。よろしいですか？`), click「はい」thì xử lý từ chối được thực hiện
 </t>
           </r>
           <r>
@@ -15650,7 +15521,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">denshi_shonin_status của t_dokusya giữ nguyên 0 (chờ duyệt) không bị thay đổi
+            <t xml:space="preserve">Trả về HTTP 200 (`data.denshi_shonin_status = 2`), message `否認しました。` được hiển thị, chuyển về màn hình 購読者明細検索
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ4：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">denshi_shonin_status của t_dokusya được update thành 2, lịch sử mới nhất của t_dokusya_rireki ghi denshi_shonin_status=2
 </t>
           </r>
           <r>
@@ -15667,7 +15555,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・Khi click「いいえ」ở dialog xác nhận từ chối thì không làm gì và giữ nguyên màn hình hiện tại (機能定義 §4.4)</t>
+            <t xml:space="preserve">・Chỉ khi denshi_shonin_status=0 mới hiển thị button「承認しない」(機能定義 §4.1)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Click「承認しない」thì hiển thị dialog xác nhận từ chối (ACSMS-MSG-011-014 `電子版読者の登録を否認します。よろしいですか？`) (機能定義 §4.2)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Click「はい」thì gọi PUT `/api/v1/dokusya/{dokusya_id}/reject` và đặt denshi_shonin_status=2 (機能定義 §4.3)</t>
           </r>
         </is>
       </c>
@@ -15721,20 +15625,20 @@
       <c r="BP50" s="10" t="n"/>
       <c r="BQ50" s="11" t="n"/>
     </row>
-    <row r="51" ht="450" customHeight="1">
+    <row r="51" ht="304" customHeight="1">
       <c r="A51" s="44" t="n">
         <v>35</v>
       </c>
       <c r="B51" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-035</t>
+          <t>ACSMS-TC-011-034</t>
         </is>
       </c>
       <c r="C51" s="10" t="n"/>
       <c r="D51" s="11" t="n"/>
       <c r="E51" s="46" t="inlineStr">
         <is>
-          <t>Lấy・hiển thị danh sách lịch sử thay đổi</t>
+          <t>Ngắt xử lý khi click「いいえ」ở dialog xác nhận từ chối</t>
         </is>
       </c>
       <c r="F51" s="10" t="n"/>
@@ -15743,8 +15647,8 @@
       <c r="I51" s="11" t="n"/>
       <c r="J51" s="46" t="inlineStr">
         <is>
-          <t>・role: JA_HONTEN（ja_id=100 所属）
-・Tồn tại từ 2 lịch sử trở lên (rireki_no=1, 2) ở độc giả (dokusya_id=100)</t>
+          <t>・role: JA_HONTEN（ja_id=100 所属, có cờ xử lý bản điện tử）
+・Tồn tại độc giả denshi_shonin_status=0 (chờ duyệt) (dokusya_id=202)</t>
         </is>
       </c>
       <c r="K51" s="10" t="n"/>
@@ -15769,7 +15673,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Mở màn hình đăng ký thông tin độc giả ở chế độ sửa, click button「履歴表示」
+            <t xml:space="preserve">Mở độc giả chờ duyệt ở chế độ sửa, click button「承認しない」
 </t>
           </r>
           <r>
@@ -15786,7 +15690,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xác nhận response của GET `/api/v1/dokusya/100/history` qua tab Network của DevTools
+            <t xml:space="preserve">Click「いいえ」ở dialog xác nhận từ chối
 </t>
           </r>
           <r>
@@ -15803,7 +15707,31 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận thứ tự sắp xếp danh sách lịch sử và項目 từng dòng (rireki_no・tetsuzuki_shurui_label・henko_riyu・saishin_data_flg)</t>
+            <t xml:space="preserve">Chạy query sau trong DB, xác nhận status
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">```sql
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">SELECT denshi_shonin_status FROM t_dokusya WHERE dokusya_id = 202;
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>```</t>
           </r>
         </is>
       </c>
@@ -15829,7 +15757,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Màn hình thông tin lịch sử độc giả (danh sách lịch sử thay đổi) được hiển thị
+            <t xml:space="preserve">Dialog xác nhận từ chối được hiển thị
 </t>
           </r>
           <r>
@@ -15846,7 +15774,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 200 (mảng `data` chứa record lịch sử)
+            <t xml:space="preserve">Xử lý từ chối không được thực hiện, màn hình hiện tại được giữ nguyên
 </t>
           </r>
           <r>
@@ -15863,7 +15791,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Danh sách lịch sử hiển thị theo thứ tự giảm dần của rireki_no, từng dòng hiển thị label loại thủ tục (tetsuzuki_shurui_label)・lý do thay đổi (henko_riyu)・cờ dữ liệu mới nhất (saishin_data_flg)
+            <t xml:space="preserve">denshi_shonin_status của t_dokusya giữ nguyên 0 (chờ duyệt) không bị thay đổi
 </t>
           </r>
           <r>
@@ -15880,23 +15808,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Click button「履歴表示」thì chuyển về màn hình thông tin lịch sử độc giả (ACSMS-SCR-013) (機能定義 §5.1)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Danh sách lịch sử được lấy theo thứ tự giảm dần rireki_no
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Giá trị tetsuzuki_shurui được mapping sang label (m_code.code_category='TETSUZUKI_SHURUI')</t>
+            <t>・Khi click「いいえ」ở dialog xác nhận từ chối thì không làm gì và giữ nguyên màn hình hiện tại (機能定義 §4.4)</t>
           </r>
         </is>
       </c>
@@ -15942,12 +15854,7 @@
       <c r="BH51" s="45" t="inlineStr"/>
       <c r="BI51" s="10" t="n"/>
       <c r="BJ51" s="11" t="n"/>
-      <c r="BK51" s="46" t="inlineStr">
-        <is>
-          <t>(なし)
----</t>
-        </is>
-      </c>
+      <c r="BK51" s="46" t="inlineStr"/>
       <c r="BL51" s="10" t="n"/>
       <c r="BM51" s="10" t="n"/>
       <c r="BN51" s="10" t="n"/>
@@ -15955,74 +15862,233 @@
       <c r="BP51" s="10" t="n"/>
       <c r="BQ51" s="11" t="n"/>
     </row>
-    <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="32" t="inlineStr">
-        <is>
-          <t>Xử lý lỗi dùng chung (Common Error Handling)</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="n"/>
+    <row r="52" ht="450" customHeight="1">
+      <c r="A52" s="44" t="n">
+        <v>36</v>
+      </c>
+      <c r="B52" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-035</t>
+        </is>
+      </c>
       <c r="C52" s="10" t="n"/>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="46" t="inlineStr">
+        <is>
+          <t>Lấy・hiển thị danh sách lịch sử thay đổi</t>
+        </is>
+      </c>
       <c r="F52" s="10" t="n"/>
       <c r="G52" s="10" t="n"/>
       <c r="H52" s="10" t="n"/>
-      <c r="I52" s="10" t="n"/>
-      <c r="J52" s="10" t="n"/>
+      <c r="I52" s="11" t="n"/>
+      <c r="J52" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属）
+・Tồn tại từ 2 lịch sử trở lên (rireki_no=1, 2) ở độc giả (dokusya_id=100)</t>
+        </is>
+      </c>
       <c r="K52" s="10" t="n"/>
       <c r="L52" s="10" t="n"/>
       <c r="M52" s="10" t="n"/>
       <c r="N52" s="10" t="n"/>
       <c r="O52" s="10" t="n"/>
-      <c r="P52" s="10" t="n"/>
-      <c r="Q52" s="10" t="n"/>
+      <c r="P52" s="11" t="n"/>
+      <c r="Q52" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Mở màn hình đăng ký thông tin độc giả ở chế độ sửa, click button「履歴表示」
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Xác nhận response của GET `/api/v1/dokusya/100/history` qua tab Network của DevTools
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Xác nhận thứ tự sắp xếp danh sách lịch sử và項目 từng dòng (rireki_no・tetsuzuki_shurui・saishin_data_flg)</t>
+          </r>
+        </is>
+      </c>
       <c r="R52" s="10" t="n"/>
       <c r="S52" s="10" t="n"/>
       <c r="T52" s="10" t="n"/>
       <c r="U52" s="10" t="n"/>
       <c r="V52" s="10" t="n"/>
-      <c r="W52" s="10" t="n"/>
-      <c r="X52" s="10" t="n"/>
+      <c r="W52" s="11" t="n"/>
+      <c r="X52" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Màn hình thông tin lịch sử độc giả (danh sách lịch sử thay đổi) được hiển thị
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Trả về HTTP 200 (mảng `data` chứa record lịch sử)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Danh sách lịch sử hiển thị theo thứ tự giảm dần của rireki_no, từng dòng hiển thị loại thủ tục (label m_code của tetsuzuki_shurui)・cờ dữ liệu mới nhất (saishin_data_flg)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Click button「履歴表示」thì chuyển về màn hình thông tin lịch sử độc giả (ACSMS-SCR-013) (機能定義 §5.1)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Danh sách lịch sử được lấy theo thứ tự giảm dần rireki_no
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Giá trị tetsuzuki_shurui được mapping sang label (m_code.code_category='TETSUZUKI_SHURUI')</t>
+          </r>
+        </is>
+      </c>
       <c r="Y52" s="10" t="n"/>
       <c r="Z52" s="10" t="n"/>
       <c r="AA52" s="10" t="n"/>
       <c r="AB52" s="10" t="n"/>
       <c r="AC52" s="10" t="n"/>
-      <c r="AD52" s="10" t="n"/>
-      <c r="AE52" s="10" t="n"/>
-      <c r="AF52" s="10" t="n"/>
-      <c r="AG52" s="10" t="n"/>
+      <c r="AD52" s="11" t="n"/>
+      <c r="AE52" s="45" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="AF52" s="11" t="n"/>
+      <c r="AG52" s="45" t="inlineStr"/>
       <c r="AH52" s="10" t="n"/>
-      <c r="AI52" s="10" t="n"/>
-      <c r="AJ52" s="10" t="n"/>
+      <c r="AI52" s="11" t="n"/>
+      <c r="AJ52" s="45" t="inlineStr"/>
       <c r="AK52" s="10" t="n"/>
-      <c r="AL52" s="10" t="n"/>
-      <c r="AM52" s="10" t="n"/>
+      <c r="AL52" s="11" t="n"/>
+      <c r="AM52" s="45" t="inlineStr"/>
       <c r="AN52" s="10" t="n"/>
-      <c r="AO52" s="10" t="n"/>
-      <c r="AP52" s="10" t="n"/>
+      <c r="AO52" s="11" t="n"/>
+      <c r="AP52" s="45" t="inlineStr"/>
       <c r="AQ52" s="10" t="n"/>
-      <c r="AR52" s="10" t="n"/>
-      <c r="AS52" s="10" t="n"/>
+      <c r="AR52" s="11" t="n"/>
+      <c r="AS52" s="45" t="inlineStr"/>
       <c r="AT52" s="10" t="n"/>
-      <c r="AU52" s="10" t="n"/>
-      <c r="AV52" s="10" t="n"/>
+      <c r="AU52" s="11" t="n"/>
+      <c r="AV52" s="45" t="inlineStr"/>
       <c r="AW52" s="10" t="n"/>
-      <c r="AX52" s="10" t="n"/>
-      <c r="AY52" s="10" t="n"/>
+      <c r="AX52" s="11" t="n"/>
+      <c r="AY52" s="45" t="inlineStr"/>
       <c r="AZ52" s="10" t="n"/>
-      <c r="BA52" s="10" t="n"/>
-      <c r="BB52" s="10" t="n"/>
+      <c r="BA52" s="11" t="n"/>
+      <c r="BB52" s="45" t="inlineStr"/>
       <c r="BC52" s="10" t="n"/>
-      <c r="BD52" s="10" t="n"/>
-      <c r="BE52" s="10" t="n"/>
+      <c r="BD52" s="11" t="n"/>
+      <c r="BE52" s="45" t="inlineStr"/>
       <c r="BF52" s="10" t="n"/>
-      <c r="BG52" s="10" t="n"/>
-      <c r="BH52" s="10" t="n"/>
+      <c r="BG52" s="11" t="n"/>
+      <c r="BH52" s="45" t="inlineStr"/>
       <c r="BI52" s="10" t="n"/>
-      <c r="BJ52" s="10" t="n"/>
-      <c r="BK52" s="10" t="n"/>
+      <c r="BJ52" s="11" t="n"/>
+      <c r="BK52" s="46" t="inlineStr">
+        <is>
+          <t>(なし)
+---</t>
+        </is>
+      </c>
       <c r="BL52" s="10" t="n"/>
       <c r="BM52" s="10" t="n"/>
       <c r="BN52" s="10" t="n"/>
@@ -16030,179 +16096,74 @@
       <c r="BP52" s="10" t="n"/>
       <c r="BQ52" s="11" t="n"/>
     </row>
-    <row r="53" ht="288" customHeight="1">
-      <c r="A53" s="44" t="n">
-        <v>36</v>
-      </c>
-      <c r="B53" s="46" t="inlineStr">
-        <is>
-          <t>ACSMS-TC-011-036</t>
-        </is>
-      </c>
+    <row r="53" ht="22.5" customHeight="1">
+      <c r="A53" s="32" t="inlineStr">
+        <is>
+          <t>Xử lý lỗi dùng chung (Common Error Handling)</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="n"/>
       <c r="C53" s="10" t="n"/>
-      <c r="D53" s="11" t="n"/>
-      <c r="E53" s="46" t="inlineStr">
-        <is>
-          <t>Lỗi dùng chung — UNAUTHORIZED — xử lý khi session hết hạn</t>
-        </is>
-      </c>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
       <c r="F53" s="10" t="n"/>
       <c r="G53" s="10" t="n"/>
       <c r="H53" s="10" t="n"/>
-      <c r="I53" s="11" t="n"/>
-      <c r="J53" s="46" t="inlineStr">
-        <is>
-          <t>・role: JA_HONTEN（ja_id=100 所属）
-・Đang hiển thị màn hình đăng ký thông tin độc giả
-・Đã quá 24 giờ từ thao tác cuối, Redis session TTL đã hết hạn</t>
-        </is>
-      </c>
+      <c r="I53" s="10" t="n"/>
+      <c r="J53" s="10" t="n"/>
       <c r="K53" s="10" t="n"/>
       <c r="L53" s="10" t="n"/>
       <c r="M53" s="10" t="n"/>
       <c r="N53" s="10" t="n"/>
       <c r="O53" s="10" t="n"/>
-      <c r="P53" s="11" t="n"/>
-      <c r="Q53" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Click button「承認・登録」ở màn hình đăng ký thông tin độc giả, gửi request POST `/api/v1/dokusya`
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Xác nhận nội dung response và chuyển màn hình</t>
-          </r>
-        </is>
-      </c>
+      <c r="P53" s="10" t="n"/>
+      <c r="Q53" s="10" t="n"/>
       <c r="R53" s="10" t="n"/>
       <c r="S53" s="10" t="n"/>
       <c r="T53" s="10" t="n"/>
       <c r="U53" s="10" t="n"/>
       <c r="V53" s="10" t="n"/>
-      <c r="W53" s="11" t="n"/>
-      <c r="X53" s="46" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ1：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Trả về HTTP 401 (`error_code: UNAUTHORIZED`, message `セッションが切れました。再度ログインしてください。`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ2：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Phía frontend state user của Pinia auth store được clear, tự động chuyển về `/login?redirect=...`
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">補足：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Khi session hết hạn thì SessionAuthGuard phía backend trả về 401, axios interceptor phía frontend dẫn đồng nhất về màn hình đăng nhập</t>
-          </r>
-        </is>
-      </c>
+      <c r="W53" s="10" t="n"/>
+      <c r="X53" s="10" t="n"/>
       <c r="Y53" s="10" t="n"/>
       <c r="Z53" s="10" t="n"/>
       <c r="AA53" s="10" t="n"/>
       <c r="AB53" s="10" t="n"/>
       <c r="AC53" s="10" t="n"/>
-      <c r="AD53" s="11" t="n"/>
-      <c r="AE53" s="45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="AF53" s="11" t="n"/>
-      <c r="AG53" s="45" t="inlineStr"/>
+      <c r="AD53" s="10" t="n"/>
+      <c r="AE53" s="10" t="n"/>
+      <c r="AF53" s="10" t="n"/>
+      <c r="AG53" s="10" t="n"/>
       <c r="AH53" s="10" t="n"/>
-      <c r="AI53" s="11" t="n"/>
-      <c r="AJ53" s="45" t="inlineStr"/>
+      <c r="AI53" s="10" t="n"/>
+      <c r="AJ53" s="10" t="n"/>
       <c r="AK53" s="10" t="n"/>
-      <c r="AL53" s="11" t="n"/>
-      <c r="AM53" s="45" t="inlineStr"/>
+      <c r="AL53" s="10" t="n"/>
+      <c r="AM53" s="10" t="n"/>
       <c r="AN53" s="10" t="n"/>
-      <c r="AO53" s="11" t="n"/>
-      <c r="AP53" s="45" t="inlineStr"/>
+      <c r="AO53" s="10" t="n"/>
+      <c r="AP53" s="10" t="n"/>
       <c r="AQ53" s="10" t="n"/>
-      <c r="AR53" s="11" t="n"/>
-      <c r="AS53" s="45" t="inlineStr"/>
+      <c r="AR53" s="10" t="n"/>
+      <c r="AS53" s="10" t="n"/>
       <c r="AT53" s="10" t="n"/>
-      <c r="AU53" s="11" t="n"/>
-      <c r="AV53" s="45" t="inlineStr"/>
+      <c r="AU53" s="10" t="n"/>
+      <c r="AV53" s="10" t="n"/>
       <c r="AW53" s="10" t="n"/>
-      <c r="AX53" s="11" t="n"/>
-      <c r="AY53" s="45" t="inlineStr"/>
+      <c r="AX53" s="10" t="n"/>
+      <c r="AY53" s="10" t="n"/>
       <c r="AZ53" s="10" t="n"/>
-      <c r="BA53" s="11" t="n"/>
-      <c r="BB53" s="45" t="inlineStr"/>
+      <c r="BA53" s="10" t="n"/>
+      <c r="BB53" s="10" t="n"/>
       <c r="BC53" s="10" t="n"/>
-      <c r="BD53" s="11" t="n"/>
-      <c r="BE53" s="45" t="inlineStr"/>
+      <c r="BD53" s="10" t="n"/>
+      <c r="BE53" s="10" t="n"/>
       <c r="BF53" s="10" t="n"/>
-      <c r="BG53" s="11" t="n"/>
-      <c r="BH53" s="45" t="inlineStr"/>
+      <c r="BG53" s="10" t="n"/>
+      <c r="BH53" s="10" t="n"/>
       <c r="BI53" s="10" t="n"/>
-      <c r="BJ53" s="11" t="n"/>
-      <c r="BK53" s="46" t="inlineStr"/>
+      <c r="BJ53" s="10" t="n"/>
+      <c r="BK53" s="10" t="n"/>
       <c r="BL53" s="10" t="n"/>
       <c r="BM53" s="10" t="n"/>
       <c r="BN53" s="10" t="n"/>
@@ -16210,20 +16171,20 @@
       <c r="BP53" s="10" t="n"/>
       <c r="BQ53" s="11" t="n"/>
     </row>
-    <row r="54" ht="240" customHeight="1">
+    <row r="54" ht="288" customHeight="1">
       <c r="A54" s="44" t="n">
         <v>37</v>
       </c>
       <c r="B54" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-037</t>
+          <t>ACSMS-TC-011-036</t>
         </is>
       </c>
       <c r="C54" s="10" t="n"/>
       <c r="D54" s="11" t="n"/>
       <c r="E54" s="46" t="inlineStr">
         <is>
-          <t>Lỗi dùng chung — FORBIDDEN — gọi trực tiếp API đăng ký khi không có quyền</t>
+          <t>Lỗi dùng chung — UNAUTHORIZED — xử lý khi session hết hạn</t>
         </is>
       </c>
       <c r="F54" s="10" t="n"/>
@@ -16232,8 +16193,9 @@
       <c r="I54" s="11" t="n"/>
       <c r="J54" s="46" t="inlineStr">
         <is>
-          <t>・role: NICHINO_ADMIN
-・Không có quyền「dokusya.create」</t>
+          <t>・role: JA_HONTEN（ja_id=100 所属）
+・Đang hiển thị màn hình đăng ký thông tin độc giả
+・Đã quá 24 giờ từ thao tác cuối, Redis session TTL đã hết hạn</t>
         </is>
       </c>
       <c r="K54" s="10" t="n"/>
@@ -16258,7 +16220,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Từ Console của DevTools chạy `fetch('/api/v1/dokusya', { method: 'POST', credentials: 'include', headers: { 'Content-Type': 'application/json' }, body: '{}' })`
+            <t xml:space="preserve">Click button「承認・登録」ở màn hình đăng ký thông tin độc giả, gửi request POST `/api/v1/dokusya`
 </t>
           </r>
           <r>
@@ -16275,7 +16237,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận HTTP status và error_code của response</t>
+            <t>Xác nhận nội dung response và chuyển màn hình</t>
           </r>
         </is>
       </c>
@@ -16301,7 +16263,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Request bị từ chối ở kiểm tra quyền phía backend
+            <t xml:space="preserve">Trả về HTTP 401 (`error_code: UNAUTHORIZED`, message `セッションが切れました。再度ログインしてください。`)
 </t>
           </r>
           <r>
@@ -16318,7 +16280,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 403 (`error_code: FORBIDDEN`, message `この画面へのアクセス権限がありません。`)
+            <t xml:space="preserve">Phía frontend state user của Pinia auth store được clear, tự động chuyển về `/login?redirect=...`
 </t>
           </r>
           <r>
@@ -16335,7 +16297,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・Role không có quyền `dokusya.create` dù gọi trực tiếp API đăng ký thì phía backend cũng trả về 403</t>
+            <t>・Khi session hết hạn thì SessionAuthGuard phía backend trả về 401, axios interceptor phía frontend dẫn đồng nhất về màn hình đăng nhập</t>
           </r>
         </is>
       </c>
@@ -16389,20 +16351,20 @@
       <c r="BP54" s="10" t="n"/>
       <c r="BQ54" s="11" t="n"/>
     </row>
-    <row r="55" ht="400" customHeight="1">
+    <row r="55" ht="240" customHeight="1">
       <c r="A55" s="44" t="n">
         <v>38</v>
       </c>
       <c r="B55" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-038</t>
+          <t>ACSMS-TC-011-037</t>
         </is>
       </c>
       <c r="C55" s="10" t="n"/>
       <c r="D55" s="11" t="n"/>
       <c r="E55" s="46" t="inlineStr">
         <is>
-          <t>Lỗi dùng chung — DATA_SCOPE_VIOLATION — thử đăng ký với scope JA khác</t>
+          <t>Lỗi dùng chung — FORBIDDEN — gọi trực tiếp API đăng ký khi không có quyền</t>
         </is>
       </c>
       <c r="F55" s="10" t="n"/>
@@ -16411,8 +16373,8 @@
       <c r="I55" s="11" t="n"/>
       <c r="J55" s="46" t="inlineStr">
         <is>
-          <t>・role: JA_HONTEN（ja_id=100 所属）
-・Giữ管理支店ID・販売店ID thuộc JA khác (ja_id=200)</t>
+          <t>・role: NICHINO_ADMIN
+・Không có quyền「dokusya.create」</t>
         </is>
       </c>
       <c r="K55" s="10" t="n"/>
@@ -16437,7 +16399,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Từ Console của DevTools chạy POST `/api/v1/dokusya`, chỉ định kanri_shiten_id・hanbaiten_id thuộc JA khác (ja_id=200) trong request body để gửi
+            <t xml:space="preserve">Từ Console của DevTools chạy `fetch('/api/v1/dokusya', { method: 'POST', credentials: 'include', headers: { 'Content-Type': 'application/json' }, body: '{}' })`
 </t>
           </r>
           <r>
@@ -16480,7 +16442,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Request bị từ chối ở kiểm tra DataScope phía backend
+            <t xml:space="preserve">Request bị từ chối ở kiểm tra quyền phía backend
 </t>
           </r>
           <r>
@@ -16497,7 +16459,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 403 (`error_code: DATA_SCOPE_VIOLATION`, message `このデータへのアクセス権限がありません。`)
+            <t xml:space="preserve">Trả về HTTP 403 (`error_code: FORBIDDEN`, message `この画面へのアクセス権限がありません。`)
 </t>
           </r>
           <r>
@@ -16514,23 +16476,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・ja_id khi đăng ký được tự động thiết lập phía server, ja_id trong request body không được tin tưởng
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">・Đăng ký chỉ định tham chiếu FK (管理支店・販売店) thuộc JA khác bị từ chối bằng DATA_SCOPE_VIOLATION (403)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Vi phạm DataScope của hệ tham chiếu (lấy chi tiết・lịch sử) bị ẩn sự tồn tại bằng 404, nhưng hệ đăng ký・cập nhật minh thị từ chối truy cập bằng 403</t>
+            <t>・Role không có quyền `dokusya.create` dù gọi trực tiếp API đăng ký thì phía backend cũng trả về 403</t>
           </r>
         </is>
       </c>
@@ -16584,20 +16530,20 @@
       <c r="BP55" s="10" t="n"/>
       <c r="BQ55" s="11" t="n"/>
     </row>
-    <row r="56" ht="320" customHeight="1">
+    <row r="56" ht="400" customHeight="1">
       <c r="A56" s="44" t="n">
         <v>39</v>
       </c>
       <c r="B56" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-039</t>
+          <t>ACSMS-TC-011-038</t>
         </is>
       </c>
       <c r="C56" s="10" t="n"/>
       <c r="D56" s="11" t="n"/>
       <c r="E56" s="46" t="inlineStr">
         <is>
-          <t>Lỗi dùng chung — VALIDATION_ERROR — gửi tích hợp giá trị không hợp lệ</t>
+          <t>Lỗi dùng chung — DATA_SCOPE_VIOLATION — thử đăng ký với scope JA khác</t>
         </is>
       </c>
       <c r="F56" s="10" t="n"/>
@@ -16607,7 +16553,7 @@
       <c r="J56" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・Đang mở tab Network của DevTools</t>
+・Giữ管理支店ID・販売店ID thuộc JA khác (ja_id=200)</t>
         </is>
       </c>
       <c r="K56" s="10" t="n"/>
@@ -16632,7 +16578,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Từ Console của DevTools chạy POST `/api/v1/dokusya`, gửi shimei_sei rỗng・yubin_no là「123」(số chữ số sai)
+            <t xml:space="preserve">Từ Console của DevTools chạy POST `/api/v1/dokusya`, chỉ định kanri_shiten_id・hanbaiten_id thuộc JA khác (ja_id=200) trong request body để gửi
 </t>
           </r>
           <r>
@@ -16649,7 +16595,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận HTTP status・error_code・mảng errors của response</t>
+            <t>Xác nhận HTTP status và error_code của response</t>
           </r>
         </is>
       </c>
@@ -16675,7 +16621,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Request bị từ chối ở validation phía backend
+            <t xml:space="preserve">Request bị từ chối ở kiểm tra DataScope phía backend
 </t>
           </r>
           <r>
@@ -16692,7 +16638,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 400 (`error_code: VALIDATION_ERROR`, message `入力値が不正です。詳細はerrorsフィールドを確認してください。`, mảng `errors` chứa message từng項目 của shimei_sei・yubin_no)
+            <t xml:space="preserve">Trả về HTTP 403 (`error_code: DATA_SCOPE_VIOLATION`, message `このデータへのアクセス権限がありません。`)
 </t>
           </r>
           <r>
@@ -16709,15 +16655,23 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Lỗi validation được trả về theo dạng mảng `errors` (field + message)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Message từng項目 được hiển thị dưới từng項目 phía frontend</t>
+            <t xml:space="preserve">・ja_id khi đăng ký được tự động thiết lập phía server, ja_id trong request body không được tin tưởng
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Đăng ký chỉ định tham chiếu FK (管理支店・販売店) thuộc JA khác bị từ chối bằng DATA_SCOPE_VIOLATION (403)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Vi phạm DataScope của hệ tham chiếu (lấy chi tiết・lịch sử) bị ẩn sự tồn tại bằng 404, nhưng hệ đăng ký・cập nhật minh thị từ chối truy cập bằng 403</t>
           </r>
         </is>
       </c>
@@ -16771,20 +16725,20 @@
       <c r="BP56" s="10" t="n"/>
       <c r="BQ56" s="11" t="n"/>
     </row>
-    <row r="57" ht="352" customHeight="1">
+    <row r="57" ht="320" customHeight="1">
       <c r="A57" s="44" t="n">
         <v>40</v>
       </c>
       <c r="B57" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-040</t>
+          <t>ACSMS-TC-011-039</t>
         </is>
       </c>
       <c r="C57" s="10" t="n"/>
       <c r="D57" s="11" t="n"/>
       <c r="E57" s="46" t="inlineStr">
         <is>
-          <t>Lỗi dùng chung — NOT_FOUND — lấy độc giả đã xóa／không tồn tại</t>
+          <t>Lỗi dùng chung — VALIDATION_ERROR — gửi tích hợp giá trị không hợp lệ</t>
         </is>
       </c>
       <c r="F57" s="10" t="n"/>
@@ -16794,7 +16748,7 @@
       <c r="J57" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・ID độc giả không tồn tại (dokusya_id=999999)</t>
+・Đang mở tab Network của DevTools</t>
         </is>
       </c>
       <c r="K57" s="10" t="n"/>
@@ -16819,7 +16773,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Nhập `/dokusya/999999` vào thanh địa chỉ trình duyệt, truy cập trực tiếp ở chế độ sửa
+            <t xml:space="preserve">Từ Console của DevTools chạy POST `/api/v1/dokusya`, gửi shimei_sei rỗng・yubin_no là「123」(số chữ số sai)
 </t>
           </r>
           <r>
@@ -16836,24 +16790,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xác nhận response của GET `/api/v1/dokusya/999999` qua tab Network của DevTools
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Xác nhận hiển thị message phía màn hình</t>
+            <t>Xác nhận HTTP status・error_code・mảng errors của response</t>
           </r>
         </is>
       </c>
@@ -16879,7 +16816,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Màn hình đăng ký thông tin độc giả ở chế độ sửa được mở
+            <t xml:space="preserve">Request bị từ chối ở validation phía backend
 </t>
           </r>
           <r>
@@ -16896,24 +16833,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 404 (`error_code: NOT_FOUND`, message `指定された購読者が見つかりません。`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Message lấy dữ liệu thất bại ACSMS-MSG-011-016 `購読者ID #{id} が見つかりません。` được hiển thị
+            <t xml:space="preserve">Trả về HTTP 400 (`error_code: VALIDATION_ERROR`, message `入力値が不正です。詳細はerrorsフィールドを確認してください。`, mảng `errors` chứa message từng項目 của shimei_sei・yubin_no)
 </t>
           </r>
           <r>
@@ -16930,15 +16850,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Lấy ID độc giả không tồn tại trả về 404 (NOT_FOUND)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Khi lấy dữ liệu thất bại thì phía frontend hiển thị ACSMS-MSG-011-016</t>
+            <t xml:space="preserve">・Lỗi validation được trả về theo dạng mảng `errors` (field + message)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Message từng項目 được hiển thị dưới từng項目 phía frontend</t>
           </r>
         </is>
       </c>
@@ -16992,20 +16912,20 @@
       <c r="BP57" s="10" t="n"/>
       <c r="BQ57" s="11" t="n"/>
     </row>
-    <row r="58" ht="368" customHeight="1">
+    <row r="58" ht="352" customHeight="1">
       <c r="A58" s="44" t="n">
         <v>41</v>
       </c>
       <c r="B58" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-041</t>
+          <t>ACSMS-TC-011-040</t>
         </is>
       </c>
       <c r="C58" s="10" t="n"/>
       <c r="D58" s="11" t="n"/>
       <c r="E58" s="46" t="inlineStr">
         <is>
-          <t>Lỗi dùng chung — DUPLICATE_EMAIL — trùng địa chỉ email</t>
+          <t>Lỗi dùng chung — NOT_FOUND — lấy độc giả đã xóa／không tồn tại</t>
         </is>
       </c>
       <c r="F58" s="10" t="n"/>
@@ -17015,7 +16935,7 @@
       <c r="J58" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・Trong JA mình đã tồn tại độc giả có email=`existing@example.com`</t>
+・ID độc giả không tồn tại (dokusya_id=999999)</t>
         </is>
       </c>
       <c r="K58" s="10" t="n"/>
@@ -17040,7 +16960,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Chọn loại độc giả=電子版 ở chế độ tạo mới, nhập `existing@example.com` vào email (email), nhập tất cả項目 bắt buộc rồi click button「承認・登録」
+            <t xml:space="preserve">Nhập `/dokusya/999999` vào thanh địa chỉ trình duyệt, truy cập trực tiếp ở chế độ sửa
 </t>
           </r>
           <r>
@@ -17057,7 +16977,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xác nhận HTTP status và error_code của response
+            <t xml:space="preserve">Xác nhận response của GET `/api/v1/dokusya/999999` qua tab Network của DevTools
 </t>
           </r>
           <r>
@@ -17100,7 +17020,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xử lý đăng ký bị từ chối
+            <t xml:space="preserve">Màn hình đăng ký thông tin độc giả ở chế độ sửa được mở
 </t>
           </r>
           <r>
@@ -17117,7 +17037,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 400 (`error_code: DUPLICATE_EMAIL`, message `このメールアドレスは既に登録されています。`)
+            <t xml:space="preserve">Trả về HTTP 404 (`error_code: NOT_FOUND`, message `指定された購読者が見つかりません。`)
 </t>
           </r>
           <r>
@@ -17134,7 +17054,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Message `このメールアドレスは既に登録されています。`（ACSMS-MSG-011-009）được hiển thị, dữ liệu trùng không được đăng ký
+            <t xml:space="preserve">Message lấy dữ liệu thất bại ACSMS-MSG-011-016 `購読者ID #{id} が見つかりません。` được hiển thị
 </t>
           </r>
           <r>
@@ -17151,15 +17071,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Khi email được nhập thì kiểm tra trùng trong JA mình (`ja_id = :ja_id`, loại trừ chuỗi rỗng) (機能定義 §2.5)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Khi trùng thì trả về DUPLICATE_EMAIL (400)</t>
+            <t xml:space="preserve">・Lấy ID độc giả không tồn tại trả về 404 (NOT_FOUND)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Khi lấy dữ liệu thất bại thì phía frontend hiển thị ACSMS-MSG-011-016</t>
           </r>
         </is>
       </c>
@@ -17213,20 +17133,20 @@
       <c r="BP58" s="10" t="n"/>
       <c r="BQ58" s="11" t="n"/>
     </row>
-    <row r="59" ht="320" customHeight="1">
+    <row r="59" ht="368" customHeight="1">
       <c r="A59" s="44" t="n">
         <v>42</v>
       </c>
       <c r="B59" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-042</t>
+          <t>ACSMS-TC-011-041</t>
         </is>
       </c>
       <c r="C59" s="10" t="n"/>
       <c r="D59" s="11" t="n"/>
       <c r="E59" s="46" t="inlineStr">
         <is>
-          <t>Lỗi dùng chung — INVALID_STATUS — thử duyệt độc giả không phải chờ duyệt</t>
+          <t>Lỗi dùng chung — DUPLICATE_EMAIL — trùng địa chỉ email</t>
         </is>
       </c>
       <c r="F59" s="10" t="n"/>
@@ -17235,8 +17155,8 @@
       <c r="I59" s="11" t="n"/>
       <c r="J59" s="46" t="inlineStr">
         <is>
-          <t>・role: JA_HONTEN（ja_id=100 所属, có cờ xử lý bản điện tử）
-・Tồn tại độc giả denshi_shonin_status=1 (đã duyệt) (dokusya_id=210)</t>
+          <t>・role: JA_HONTEN（ja_id=100 所属）
+・Trong JA mình đã tồn tại độc giả có email=`existing@example.com`</t>
         </is>
       </c>
       <c r="K59" s="10" t="n"/>
@@ -17261,7 +17181,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Từ Console của DevTools chạy PUT `/api/v1/dokusya/210/approve`
+            <t xml:space="preserve">Chọn loại độc giả=電子版 ở chế độ tạo mới, nhập `existing@example.com` vào email (email), nhập tất cả項目 bắt buộc rồi click button「承認・登録」
 </t>
           </r>
           <r>
@@ -17295,7 +17215,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Từ Console của DevTools chạy PUT `/api/v1/dokusya/210/reject`, xác nhận response</t>
+            <t>Xác nhận hiển thị message phía màn hình</t>
           </r>
         </is>
       </c>
@@ -17321,7 +17241,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xử lý duyệt bị từ chối
+            <t xml:space="preserve">Xử lý đăng ký bị từ chối
 </t>
           </r>
           <r>
@@ -17338,7 +17258,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 400 (`error_code: INVALID_STATUS`, message `承認待ちの読者ではありません。`)
+            <t xml:space="preserve">Trả về HTTP 400 (`error_code: DUPLICATE_EMAIL`, message `このメールアドレスは既に登録されています。`)
 </t>
           </r>
           <r>
@@ -17355,7 +17275,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 400 (`error_code: INVALID_STATUS`, message `承認待ちの読者ではありません。`)
+            <t xml:space="preserve">Message `このメールアドレスは既に登録されています。`（ACSMS-MSG-011-009）được hiển thị, dữ liệu trùng không được đăng ký
 </t>
           </r>
           <r>
@@ -17372,7 +17292,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・Khi denshi_shonin_status khác 0 thì API duyệt・từ chối trả về INVALID_STATUS (400) (機能定義 §3.1, §4.1)</t>
+            <t xml:space="preserve">・Khi email được nhập thì kiểm tra trùng trong JA mình (`ja_id = :ja_id`, loại trừ chuỗi rỗng) (機能定義 §2.5)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Khi trùng thì trả về DUPLICATE_EMAIL (400)</t>
           </r>
         </is>
       </c>
@@ -17426,20 +17354,20 @@
       <c r="BP59" s="10" t="n"/>
       <c r="BQ59" s="11" t="n"/>
     </row>
-    <row r="60" ht="240" customHeight="1">
+    <row r="60" ht="320" customHeight="1">
       <c r="A60" s="44" t="n">
         <v>43</v>
       </c>
       <c r="B60" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-043</t>
+          <t>ACSMS-TC-011-042</t>
         </is>
       </c>
       <c r="C60" s="10" t="n"/>
       <c r="D60" s="11" t="n"/>
       <c r="E60" s="46" t="inlineStr">
         <is>
-          <t>Lỗi dùng chung — BAD_REQUEST — request parameter không hợp lệ</t>
+          <t>Lỗi dùng chung — INVALID_STATUS — thử duyệt độc giả không phải chờ duyệt</t>
         </is>
       </c>
       <c r="F60" s="10" t="n"/>
@@ -17448,8 +17376,8 @@
       <c r="I60" s="11" t="n"/>
       <c r="J60" s="46" t="inlineStr">
         <is>
-          <t>・role: JA_HONTEN（ja_id=100 所属）
-・Đang mở tab Network của DevTools</t>
+          <t>・role: JA_HONTEN（ja_id=100 所属, có cờ xử lý bản điện tử）
+・Tồn tại độc giả denshi_shonin_status=1 (đã duyệt) (dokusya_id=210)</t>
         </is>
       </c>
       <c r="K60" s="10" t="n"/>
@@ -17474,7 +17402,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Từ Console của DevTools chạy `fetch('/api/v1/dokusya/abc', { credentials: 'include' })` (chỉ định dokusya_id là phi số)
+            <t xml:space="preserve">Từ Console của DevTools chạy PUT `/api/v1/dokusya/210/approve`
 </t>
           </r>
           <r>
@@ -17491,7 +17419,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận HTTP status và error_code của response</t>
+            <t xml:space="preserve">Xác nhận HTTP status và error_code của response
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Từ Console của DevTools chạy PUT `/api/v1/dokusya/210/reject`, xác nhận response</t>
           </r>
         </is>
       </c>
@@ -17517,7 +17462,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Request bị từ chối ở validation phía backend
+            <t xml:space="preserve">Xử lý duyệt bị từ chối
 </t>
           </r>
           <r>
@@ -17534,7 +17479,24 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 400 (`error_code: BAD_REQUEST`, message `リクエストパラメータが不正です。`)
+            <t xml:space="preserve">Trả về HTTP 400 (`error_code: INVALID_STATUS`, message `承認待ちの読者ではありません。`)
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Trả về HTTP 400 (`error_code: INVALID_STATUS`, message `承認待ちの読者ではありません。`)
 </t>
           </r>
           <r>
@@ -17551,7 +17513,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>・dokusya_id path parameter được kiểm tra kiểu số, khi giá trị không hợp lệ thì được map sang BAD_REQUEST</t>
+            <t>・Khi denshi_shonin_status khác 0 thì API duyệt・từ chối trả về INVALID_STATUS (400) (機能定義 §3.1, §4.1)</t>
           </r>
         </is>
       </c>
@@ -17605,20 +17567,20 @@
       <c r="BP60" s="10" t="n"/>
       <c r="BQ60" s="11" t="n"/>
     </row>
-    <row r="61" ht="400" customHeight="1">
+    <row r="61" ht="240" customHeight="1">
       <c r="A61" s="44" t="n">
         <v>44</v>
       </c>
       <c r="B61" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-044</t>
+          <t>ACSMS-TC-011-043</t>
         </is>
       </c>
       <c r="C61" s="10" t="n"/>
       <c r="D61" s="11" t="n"/>
       <c r="E61" s="46" t="inlineStr">
         <is>
-          <t>Lỗi dùng chung — TOO_MANY_REQUESTS — vượt giới hạn rate</t>
+          <t>Lỗi dùng chung — BAD_REQUEST — request parameter không hợp lệ</t>
         </is>
       </c>
       <c r="F61" s="10" t="n"/>
@@ -17628,7 +17590,7 @@
       <c r="J61" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・Dùng script test gửi GET `/api/v1/dokusya/1` vượt giới hạn trong 1 phút</t>
+・Đang mở tab Network của DevTools</t>
         </is>
       </c>
       <c r="K61" s="10" t="n"/>
@@ -17653,7 +17615,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Khởi động script, gửi request tần suất cao tới API lấy độc giả
+            <t xml:space="preserve">Từ Console của DevTools chạy `fetch('/api/v1/dokusya/abc', { credentials: 'include' })` (chỉ định dokusya_id là phi số)
 </t>
           </r>
           <r>
@@ -17670,24 +17632,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xác nhận HTTP status và error_code của response
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>Xác nhận hiển thị toast phía màn hình</t>
+            <t>Xác nhận HTTP status và error_code của response</t>
           </r>
         </is>
       </c>
@@ -17713,7 +17658,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Đến số lượng giới hạn thì phản hồi bình thường, sau đó trả về 429
+            <t xml:space="preserve">Request bị từ chối ở validation phía backend
 </t>
           </r>
           <r>
@@ -17730,24 +17675,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 429 (`error_code: TOO_MANY_REQUESTS`, message `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。`)
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <b val="1"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">ステップ3：
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t xml:space="preserve">Toast `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。` được hiển thị
+            <t xml:space="preserve">Trả về HTTP 400 (`error_code: BAD_REQUEST`, message `リクエストパラメータが不正です。`)
 </t>
           </r>
           <r>
@@ -17764,15 +17692,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・NestJS @Throttle decorator + AWS WAF rate limit block ở cả 2 lớp hạ tầng／ứng dụng
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Tuân thủ quan điểm VP-A-08「レート制限・Throttling」(testcase-viewpoints.md v1.1)</t>
+            <t>・dokusya_id path parameter được kiểm tra kiểu số, khi giá trị không hợp lệ thì được map sang BAD_REQUEST</t>
           </r>
         </is>
       </c>
@@ -17826,20 +17746,20 @@
       <c r="BP61" s="10" t="n"/>
       <c r="BQ61" s="11" t="n"/>
     </row>
-    <row r="62" ht="448" customHeight="1">
+    <row r="62" ht="400" customHeight="1">
       <c r="A62" s="44" t="n">
         <v>45</v>
       </c>
       <c r="B62" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-045</t>
+          <t>ACSMS-TC-011-044</t>
         </is>
       </c>
       <c r="C62" s="10" t="n"/>
       <c r="D62" s="11" t="n"/>
       <c r="E62" s="46" t="inlineStr">
         <is>
-          <t>Lỗi dùng chung — INTERNAL_SERVER_ERROR — lỗi server</t>
+          <t>Lỗi dùng chung — TOO_MANY_REQUESTS — vượt giới hạn rate</t>
         </is>
       </c>
       <c r="F62" s="10" t="n"/>
@@ -17849,7 +17769,7 @@
       <c r="J62" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・Trạng thái có thể giả lập sự cố server như lỗi kết nối DB</t>
+・Dùng script test gửi GET `/api/v1/dokusya/1` vượt giới hạn trong 1 phút</t>
         </is>
       </c>
       <c r="K62" s="10" t="n"/>
@@ -17874,7 +17794,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Ở trạng thái giả lập sự cố server (lỗi kết nối DB v.v.) click button「承認・登録」
+            <t xml:space="preserve">Khởi động script, gửi request tần suất cao tới API lấy độc giả
 </t>
           </r>
           <r>
@@ -17891,7 +17811,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xác nhận HTTP status và error_code của response POST `/api/v1/dokusya`
+            <t xml:space="preserve">Xác nhận HTTP status và error_code của response
 </t>
           </r>
           <r>
@@ -17908,7 +17828,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận hiển thị message phía màn hình và việc ghi error log</t>
+            <t>Xác nhận hiển thị toast phía màn hình</t>
           </r>
         </is>
       </c>
@@ -17934,7 +17854,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Xử lý đăng ký thất bại
+            <t xml:space="preserve">Đến số lượng giới hạn thì phản hồi bình thường, sau đó trả về 429
 </t>
           </r>
           <r>
@@ -17951,7 +17871,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trả về HTTP 500 (`error_code: INTERNAL_SERVER_ERROR`, message `システムエラーが発生しました。しばらくしてから再度お試しください。`)
+            <t xml:space="preserve">Trả về HTTP 429 (`error_code: TOO_MANY_REQUESTS`, message `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。`)
 </t>
           </r>
           <r>
@@ -17968,7 +17888,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Message `システムエラーが発生しました。しばらくしてから再度お試しください。`（ACSMS-MSG-011-012）được hiển thị, error log (log_type=3, result_status=2) được ghi vào t_log, stack trace không hiển thị cho người dùng
+            <t xml:space="preserve">Toast `リクエスト回数が上限を超えました。しばらくしてから再度お試しください。` được hiển thị
 </t>
           </r>
           <r>
@@ -17985,15 +17905,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Sự cố server như lỗi kết nối DB được map sang INTERNAL_SERVER_ERROR
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Khi phát sinh lỗi thì ghi error log (log_type=3) ngoài transaction (ghi nghiệp vụ được rollback)</t>
+            <t xml:space="preserve">・NestJS @Throttle decorator + AWS WAF rate limit block ở cả 2 lớp hạ tầng／ứng dụng
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Tuân thủ quan điểm VP-A-08「レート制限・Throttling」(testcase-viewpoints.md v1.1)</t>
           </r>
         </is>
       </c>
@@ -18047,20 +17967,20 @@
       <c r="BP62" s="10" t="n"/>
       <c r="BQ62" s="11" t="n"/>
     </row>
-    <row r="63" ht="352" customHeight="1">
+    <row r="63" ht="448" customHeight="1">
       <c r="A63" s="44" t="n">
         <v>46</v>
       </c>
       <c r="B63" s="46" t="inlineStr">
         <is>
-          <t>ACSMS-TC-011-046</t>
+          <t>ACSMS-TC-011-045</t>
         </is>
       </c>
       <c r="C63" s="10" t="n"/>
       <c r="D63" s="11" t="n"/>
       <c r="E63" s="46" t="inlineStr">
         <is>
-          <t>Lỗi dùng chung — xử lý khi mất kết nối mạng</t>
+          <t>Lỗi dùng chung — INTERNAL_SERVER_ERROR — lỗi server</t>
         </is>
       </c>
       <c r="F63" s="10" t="n"/>
@@ -18070,7 +17990,7 @@
       <c r="J63" s="46" t="inlineStr">
         <is>
           <t>・role: JA_HONTEN（ja_id=100 所属）
-・Đang mở tab Network của DevTools</t>
+・Trạng thái có thể giả lập sự cố server như lỗi kết nối DB</t>
         </is>
       </c>
       <c r="K63" s="10" t="n"/>
@@ -18095,7 +18015,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Thiết lập ngắt mạng (offline) ở tab Network của DevTools
+            <t xml:space="preserve">Ở trạng thái giả lập sự cố server (lỗi kết nối DB v.v.) click button「承認・登録」
 </t>
           </r>
           <r>
@@ -18112,7 +18032,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Click button「承認・登録」, gửi POST `/api/v1/dokusya`
+            <t xml:space="preserve">Xác nhận HTTP status và error_code của response POST `/api/v1/dokusya`
 </t>
           </r>
           <r>
@@ -18129,7 +18049,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t>Xác nhận hiển thị toast phía màn hình</t>
+            <t>Xác nhận hiển thị message phía màn hình và việc ghi error log</t>
           </r>
         </is>
       </c>
@@ -18155,7 +18075,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Trở thành trạng thái ngắt mạng
+            <t xml:space="preserve">Xử lý đăng ký thất bại
 </t>
           </r>
           <r>
@@ -18172,7 +18092,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">API request trở thành lỗi mạng
+            <t xml:space="preserve">Trả về HTTP 500 (`error_code: INTERNAL_SERVER_ERROR`, message `システムエラーが発生しました。しばらくしてから再度お試しください。`)
 </t>
           </r>
           <r>
@@ -18189,7 +18109,7 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Toast `ネットワークエラーが発生しました。しばらくしてから再度お試しください。` được hiển thị, nội dung đã nhập được giữ lại
+            <t xml:space="preserve">Message `システムエラーが発生しました。しばらくしてから再度お試しください。`（ACSMS-MSG-011-012）được hiển thị, error log (log_type=3, result_status=2) được ghi vào t_log, stack trace không hiển thị cho người dùng
 </t>
           </r>
           <r>
@@ -18206,15 +18126,15 @@
               <rFont val="メイリオ"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">・Khi mất kết nối mạng thì axios interceptor phía frontend hiển thị toast lỗi mạng
-</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="メイリオ"/>
-              <sz val="10"/>
-            </rPr>
-            <t>・Không phát sinh lỗi ngoài dự kiến, nội dung đã nhập không bị mất</t>
+            <t xml:space="preserve">・Sự cố server như lỗi kết nối DB được map sang INTERNAL_SERVER_ERROR
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Khi phát sinh lỗi thì ghi error log (log_type=3) ngoài transaction (ghi nghiệp vụ được rollback)</t>
           </r>
         </is>
       </c>
@@ -18260,12 +18180,7 @@
       <c r="BH63" s="45" t="inlineStr"/>
       <c r="BI63" s="10" t="n"/>
       <c r="BJ63" s="11" t="n"/>
-      <c r="BK63" s="46" t="inlineStr">
-        <is>
-          <t>Văn bản toast lỗi mạng tuân theo hiện thực của axios interceptor phía frontend.
----</t>
-        </is>
-      </c>
+      <c r="BK63" s="46" t="inlineStr"/>
       <c r="BL63" s="10" t="n"/>
       <c r="BM63" s="10" t="n"/>
       <c r="BN63" s="10" t="n"/>
@@ -18273,101 +18188,831 @@
       <c r="BP63" s="10" t="n"/>
       <c r="BQ63" s="11" t="n"/>
     </row>
+    <row r="64" ht="352" customHeight="1">
+      <c r="A64" s="44" t="n">
+        <v>47</v>
+      </c>
+      <c r="B64" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-046</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="46" t="inlineStr">
+        <is>
+          <t>Lỗi dùng chung — xử lý khi mất kết nối mạng</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="11" t="n"/>
+      <c r="J64" s="46" t="inlineStr">
+        <is>
+          <t>・role: JA_HONTEN（ja_id=100 所属）
+・Đang mở tab Network của DevTools</t>
+        </is>
+      </c>
+      <c r="K64" s="10" t="n"/>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="10" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="11" t="n"/>
+      <c r="Q64" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Thiết lập ngắt mạng (offline) ở tab Network của DevTools
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Click button「承認・登録」, gửi POST `/api/v1/dokusya`
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>Xác nhận hiển thị toast phía màn hình</t>
+          </r>
+        </is>
+      </c>
+      <c r="R64" s="10" t="n"/>
+      <c r="S64" s="10" t="n"/>
+      <c r="T64" s="10" t="n"/>
+      <c r="U64" s="10" t="n"/>
+      <c r="V64" s="10" t="n"/>
+      <c r="W64" s="11" t="n"/>
+      <c r="X64" s="46" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ1：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Trở thành trạng thái ngắt mạng
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ2：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">API request trở thành lỗi mạng
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">ステップ3：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">Toast `ネットワークエラーが発生しました。しばらくしてから再度お試しください。` được hiển thị, nội dung đã nhập được giữ lại
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <b val="1"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">補足：
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t xml:space="preserve">・Khi mất kết nối mạng thì axios interceptor phía frontend hiển thị toast lỗi mạng
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="メイリオ"/>
+              <sz val="10"/>
+            </rPr>
+            <t>・Không phát sinh lỗi ngoài dự kiến, nội dung đã nhập không bị mất</t>
+          </r>
+        </is>
+      </c>
+      <c r="Y64" s="10" t="n"/>
+      <c r="Z64" s="10" t="n"/>
+      <c r="AA64" s="10" t="n"/>
+      <c r="AB64" s="10" t="n"/>
+      <c r="AC64" s="10" t="n"/>
+      <c r="AD64" s="11" t="n"/>
+      <c r="AE64" s="45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF64" s="11" t="n"/>
+      <c r="AG64" s="45" t="inlineStr"/>
+      <c r="AH64" s="10" t="n"/>
+      <c r="AI64" s="11" t="n"/>
+      <c r="AJ64" s="45" t="inlineStr"/>
+      <c r="AK64" s="10" t="n"/>
+      <c r="AL64" s="11" t="n"/>
+      <c r="AM64" s="45" t="inlineStr"/>
+      <c r="AN64" s="10" t="n"/>
+      <c r="AO64" s="11" t="n"/>
+      <c r="AP64" s="45" t="inlineStr"/>
+      <c r="AQ64" s="10" t="n"/>
+      <c r="AR64" s="11" t="n"/>
+      <c r="AS64" s="45" t="inlineStr"/>
+      <c r="AT64" s="10" t="n"/>
+      <c r="AU64" s="11" t="n"/>
+      <c r="AV64" s="45" t="inlineStr"/>
+      <c r="AW64" s="10" t="n"/>
+      <c r="AX64" s="11" t="n"/>
+      <c r="AY64" s="45" t="inlineStr"/>
+      <c r="AZ64" s="10" t="n"/>
+      <c r="BA64" s="11" t="n"/>
+      <c r="BB64" s="45" t="inlineStr"/>
+      <c r="BC64" s="10" t="n"/>
+      <c r="BD64" s="11" t="n"/>
+      <c r="BE64" s="45" t="inlineStr"/>
+      <c r="BF64" s="10" t="n"/>
+      <c r="BG64" s="11" t="n"/>
+      <c r="BH64" s="45" t="inlineStr"/>
+      <c r="BI64" s="10" t="n"/>
+      <c r="BJ64" s="11" t="n"/>
+      <c r="BK64" s="46" t="inlineStr">
+        <is>
+          <t>Văn bản toast lỗi mạng tuân theo hiện thực của axios interceptor phía frontend.
+---</t>
+        </is>
+      </c>
+      <c r="BL64" s="10" t="n"/>
+      <c r="BM64" s="10" t="n"/>
+      <c r="BN64" s="10" t="n"/>
+      <c r="BO64" s="10" t="n"/>
+      <c r="BP64" s="10" t="n"/>
+      <c r="BQ64" s="11" t="n"/>
+    </row>
+    <row r="65" ht="80" customHeight="1">
+      <c r="A65" s="44" t="n">
+        <v>48</v>
+      </c>
+      <c r="B65" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-047</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="11" t="n"/>
+      <c r="E65" s="46" t="inlineStr">
+        <is>
+          <t>Luồng chỉnh sửa của bản điện tử thuần (mở ở chế độ xem, "Thay đổi hẹn trước" bị vô hiệu)</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="46" t="inlineStr"/>
+      <c r="K65" s="10" t="n"/>
+      <c r="L65" s="10" t="n"/>
+      <c r="M65" s="10" t="n"/>
+      <c r="N65" s="10" t="n"/>
+      <c r="O65" s="10" t="n"/>
+      <c r="P65" s="11" t="n"/>
+      <c r="Q65" s="46" t="inlineStr"/>
+      <c r="R65" s="10" t="n"/>
+      <c r="S65" s="10" t="n"/>
+      <c r="T65" s="10" t="n"/>
+      <c r="U65" s="10" t="n"/>
+      <c r="V65" s="10" t="n"/>
+      <c r="W65" s="11" t="n"/>
+      <c r="X65" s="46" t="inlineStr"/>
+      <c r="Y65" s="10" t="n"/>
+      <c r="Z65" s="10" t="n"/>
+      <c r="AA65" s="10" t="n"/>
+      <c r="AB65" s="10" t="n"/>
+      <c r="AC65" s="10" t="n"/>
+      <c r="AD65" s="11" t="n"/>
+      <c r="AE65" s="45" t="inlineStr"/>
+      <c r="AF65" s="11" t="n"/>
+      <c r="AG65" s="45" t="inlineStr"/>
+      <c r="AH65" s="10" t="n"/>
+      <c r="AI65" s="11" t="n"/>
+      <c r="AJ65" s="45" t="inlineStr"/>
+      <c r="AK65" s="10" t="n"/>
+      <c r="AL65" s="11" t="n"/>
+      <c r="AM65" s="45" t="inlineStr"/>
+      <c r="AN65" s="10" t="n"/>
+      <c r="AO65" s="11" t="n"/>
+      <c r="AP65" s="45" t="inlineStr"/>
+      <c r="AQ65" s="10" t="n"/>
+      <c r="AR65" s="11" t="n"/>
+      <c r="AS65" s="45" t="inlineStr"/>
+      <c r="AT65" s="10" t="n"/>
+      <c r="AU65" s="11" t="n"/>
+      <c r="AV65" s="45" t="inlineStr"/>
+      <c r="AW65" s="10" t="n"/>
+      <c r="AX65" s="11" t="n"/>
+      <c r="AY65" s="45" t="inlineStr"/>
+      <c r="AZ65" s="10" t="n"/>
+      <c r="BA65" s="11" t="n"/>
+      <c r="BB65" s="45" t="inlineStr"/>
+      <c r="BC65" s="10" t="n"/>
+      <c r="BD65" s="11" t="n"/>
+      <c r="BE65" s="45" t="inlineStr"/>
+      <c r="BF65" s="10" t="n"/>
+      <c r="BG65" s="11" t="n"/>
+      <c r="BH65" s="45" t="inlineStr"/>
+      <c r="BI65" s="10" t="n"/>
+      <c r="BJ65" s="11" t="n"/>
+      <c r="BK65" s="46" t="inlineStr"/>
+      <c r="BL65" s="10" t="n"/>
+      <c r="BM65" s="10" t="n"/>
+      <c r="BN65" s="10" t="n"/>
+      <c r="BO65" s="10" t="n"/>
+      <c r="BP65" s="10" t="n"/>
+      <c r="BQ65" s="11" t="n"/>
+    </row>
+    <row r="66" ht="64" customHeight="1">
+      <c r="A66" s="44" t="n">
+        <v>49</v>
+      </c>
+      <c r="B66" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-048</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="n"/>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="46" t="inlineStr">
+        <is>
+          <t>Dropdown cửa hàng liên động theo loại người đọc (lọc cửa hàng dummy)</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="11" t="n"/>
+      <c r="J66" s="46" t="inlineStr"/>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="11" t="n"/>
+      <c r="Q66" s="46" t="inlineStr"/>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
+      <c r="U66" s="10" t="n"/>
+      <c r="V66" s="10" t="n"/>
+      <c r="W66" s="11" t="n"/>
+      <c r="X66" s="46" t="inlineStr"/>
+      <c r="Y66" s="10" t="n"/>
+      <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="10" t="n"/>
+      <c r="AB66" s="10" t="n"/>
+      <c r="AC66" s="10" t="n"/>
+      <c r="AD66" s="11" t="n"/>
+      <c r="AE66" s="45" t="inlineStr"/>
+      <c r="AF66" s="11" t="n"/>
+      <c r="AG66" s="45" t="inlineStr"/>
+      <c r="AH66" s="10" t="n"/>
+      <c r="AI66" s="11" t="n"/>
+      <c r="AJ66" s="45" t="inlineStr"/>
+      <c r="AK66" s="10" t="n"/>
+      <c r="AL66" s="11" t="n"/>
+      <c r="AM66" s="45" t="inlineStr"/>
+      <c r="AN66" s="10" t="n"/>
+      <c r="AO66" s="11" t="n"/>
+      <c r="AP66" s="45" t="inlineStr"/>
+      <c r="AQ66" s="10" t="n"/>
+      <c r="AR66" s="11" t="n"/>
+      <c r="AS66" s="45" t="inlineStr"/>
+      <c r="AT66" s="10" t="n"/>
+      <c r="AU66" s="11" t="n"/>
+      <c r="AV66" s="45" t="inlineStr"/>
+      <c r="AW66" s="10" t="n"/>
+      <c r="AX66" s="11" t="n"/>
+      <c r="AY66" s="45" t="inlineStr"/>
+      <c r="AZ66" s="10" t="n"/>
+      <c r="BA66" s="11" t="n"/>
+      <c r="BB66" s="45" t="inlineStr"/>
+      <c r="BC66" s="10" t="n"/>
+      <c r="BD66" s="11" t="n"/>
+      <c r="BE66" s="45" t="inlineStr"/>
+      <c r="BF66" s="10" t="n"/>
+      <c r="BG66" s="11" t="n"/>
+      <c r="BH66" s="45" t="inlineStr"/>
+      <c r="BI66" s="10" t="n"/>
+      <c r="BJ66" s="11" t="n"/>
+      <c r="BK66" s="46" t="inlineStr"/>
+      <c r="BL66" s="10" t="n"/>
+      <c r="BM66" s="10" t="n"/>
+      <c r="BN66" s="10" t="n"/>
+      <c r="BO66" s="10" t="n"/>
+      <c r="BP66" s="10" t="n"/>
+      <c r="BQ66" s="11" t="n"/>
+    </row>
+    <row r="67" ht="80" customHeight="1">
+      <c r="A67" s="44" t="n">
+        <v>50</v>
+      </c>
+      <c r="B67" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-049</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="11" t="n"/>
+      <c r="E67" s="46" t="inlineStr">
+        <is>
+          <t>Sửa phương thức thanh toán và 4 trường tài khoản rút tiền trước khi duyệt/từ chối (#56524)</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="11" t="n"/>
+      <c r="J67" s="46" t="inlineStr"/>
+      <c r="K67" s="10" t="n"/>
+      <c r="L67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n"/>
+      <c r="O67" s="10" t="n"/>
+      <c r="P67" s="11" t="n"/>
+      <c r="Q67" s="46" t="inlineStr"/>
+      <c r="R67" s="10" t="n"/>
+      <c r="S67" s="10" t="n"/>
+      <c r="T67" s="10" t="n"/>
+      <c r="U67" s="10" t="n"/>
+      <c r="V67" s="10" t="n"/>
+      <c r="W67" s="11" t="n"/>
+      <c r="X67" s="46" t="inlineStr"/>
+      <c r="Y67" s="10" t="n"/>
+      <c r="Z67" s="10" t="n"/>
+      <c r="AA67" s="10" t="n"/>
+      <c r="AB67" s="10" t="n"/>
+      <c r="AC67" s="10" t="n"/>
+      <c r="AD67" s="11" t="n"/>
+      <c r="AE67" s="45" t="inlineStr"/>
+      <c r="AF67" s="11" t="n"/>
+      <c r="AG67" s="45" t="inlineStr"/>
+      <c r="AH67" s="10" t="n"/>
+      <c r="AI67" s="11" t="n"/>
+      <c r="AJ67" s="45" t="inlineStr"/>
+      <c r="AK67" s="10" t="n"/>
+      <c r="AL67" s="11" t="n"/>
+      <c r="AM67" s="45" t="inlineStr"/>
+      <c r="AN67" s="10" t="n"/>
+      <c r="AO67" s="11" t="n"/>
+      <c r="AP67" s="45" t="inlineStr"/>
+      <c r="AQ67" s="10" t="n"/>
+      <c r="AR67" s="11" t="n"/>
+      <c r="AS67" s="45" t="inlineStr"/>
+      <c r="AT67" s="10" t="n"/>
+      <c r="AU67" s="11" t="n"/>
+      <c r="AV67" s="45" t="inlineStr"/>
+      <c r="AW67" s="10" t="n"/>
+      <c r="AX67" s="11" t="n"/>
+      <c r="AY67" s="45" t="inlineStr"/>
+      <c r="AZ67" s="10" t="n"/>
+      <c r="BA67" s="11" t="n"/>
+      <c r="BB67" s="45" t="inlineStr"/>
+      <c r="BC67" s="10" t="n"/>
+      <c r="BD67" s="11" t="n"/>
+      <c r="BE67" s="45" t="inlineStr"/>
+      <c r="BF67" s="10" t="n"/>
+      <c r="BG67" s="11" t="n"/>
+      <c r="BH67" s="45" t="inlineStr"/>
+      <c r="BI67" s="10" t="n"/>
+      <c r="BJ67" s="11" t="n"/>
+      <c r="BK67" s="46" t="inlineStr"/>
+      <c r="BL67" s="10" t="n"/>
+      <c r="BM67" s="10" t="n"/>
+      <c r="BN67" s="10" t="n"/>
+      <c r="BO67" s="10" t="n"/>
+      <c r="BP67" s="10" t="n"/>
+      <c r="BQ67" s="11" t="n"/>
+    </row>
+    <row r="68" ht="80" customHeight="1">
+      <c r="A68" s="44" t="n">
+        <v>51</v>
+      </c>
+      <c r="B68" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-050</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="11" t="n"/>
+      <c r="E68" s="46" t="inlineStr">
+        <is>
+          <t>4 trường phụ thuộc của thuộc tính người đọc (kiêm cán bộ JA / liên quan nông nghiệp / nội dung khác)</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="10" t="n"/>
+      <c r="I68" s="11" t="n"/>
+      <c r="J68" s="46" t="inlineStr"/>
+      <c r="K68" s="10" t="n"/>
+      <c r="L68" s="10" t="n"/>
+      <c r="M68" s="10" t="n"/>
+      <c r="N68" s="10" t="n"/>
+      <c r="O68" s="10" t="n"/>
+      <c r="P68" s="11" t="n"/>
+      <c r="Q68" s="46" t="inlineStr"/>
+      <c r="R68" s="10" t="n"/>
+      <c r="S68" s="10" t="n"/>
+      <c r="T68" s="10" t="n"/>
+      <c r="U68" s="10" t="n"/>
+      <c r="V68" s="10" t="n"/>
+      <c r="W68" s="11" t="n"/>
+      <c r="X68" s="46" t="inlineStr"/>
+      <c r="Y68" s="10" t="n"/>
+      <c r="Z68" s="10" t="n"/>
+      <c r="AA68" s="10" t="n"/>
+      <c r="AB68" s="10" t="n"/>
+      <c r="AC68" s="10" t="n"/>
+      <c r="AD68" s="11" t="n"/>
+      <c r="AE68" s="45" t="inlineStr"/>
+      <c r="AF68" s="11" t="n"/>
+      <c r="AG68" s="45" t="inlineStr"/>
+      <c r="AH68" s="10" t="n"/>
+      <c r="AI68" s="11" t="n"/>
+      <c r="AJ68" s="45" t="inlineStr"/>
+      <c r="AK68" s="10" t="n"/>
+      <c r="AL68" s="11" t="n"/>
+      <c r="AM68" s="45" t="inlineStr"/>
+      <c r="AN68" s="10" t="n"/>
+      <c r="AO68" s="11" t="n"/>
+      <c r="AP68" s="45" t="inlineStr"/>
+      <c r="AQ68" s="10" t="n"/>
+      <c r="AR68" s="11" t="n"/>
+      <c r="AS68" s="45" t="inlineStr"/>
+      <c r="AT68" s="10" t="n"/>
+      <c r="AU68" s="11" t="n"/>
+      <c r="AV68" s="45" t="inlineStr"/>
+      <c r="AW68" s="10" t="n"/>
+      <c r="AX68" s="11" t="n"/>
+      <c r="AY68" s="45" t="inlineStr"/>
+      <c r="AZ68" s="10" t="n"/>
+      <c r="BA68" s="11" t="n"/>
+      <c r="BB68" s="45" t="inlineStr"/>
+      <c r="BC68" s="10" t="n"/>
+      <c r="BD68" s="11" t="n"/>
+      <c r="BE68" s="45" t="inlineStr"/>
+      <c r="BF68" s="10" t="n"/>
+      <c r="BG68" s="11" t="n"/>
+      <c r="BH68" s="45" t="inlineStr"/>
+      <c r="BI68" s="10" t="n"/>
+      <c r="BJ68" s="11" t="n"/>
+      <c r="BK68" s="46" t="inlineStr"/>
+      <c r="BL68" s="10" t="n"/>
+      <c r="BM68" s="10" t="n"/>
+      <c r="BN68" s="10" t="n"/>
+      <c r="BO68" s="10" t="n"/>
+      <c r="BP68" s="10" t="n"/>
+      <c r="BQ68" s="11" t="n"/>
+    </row>
+    <row r="69" ht="48" customHeight="1">
+      <c r="A69" s="44" t="n">
+        <v>52</v>
+      </c>
+      <c r="B69" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-051</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="11" t="n"/>
+      <c r="E69" s="46" t="inlineStr">
+        <is>
+          <t>Kiểm tra trùng email của bản điện tử phải xuyên JA (#56568)</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="11" t="n"/>
+      <c r="J69" s="46" t="inlineStr"/>
+      <c r="K69" s="10" t="n"/>
+      <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="11" t="n"/>
+      <c r="Q69" s="46" t="inlineStr"/>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="10" t="n"/>
+      <c r="U69" s="10" t="n"/>
+      <c r="V69" s="10" t="n"/>
+      <c r="W69" s="11" t="n"/>
+      <c r="X69" s="46" t="inlineStr"/>
+      <c r="Y69" s="10" t="n"/>
+      <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="10" t="n"/>
+      <c r="AB69" s="10" t="n"/>
+      <c r="AC69" s="10" t="n"/>
+      <c r="AD69" s="11" t="n"/>
+      <c r="AE69" s="45" t="inlineStr"/>
+      <c r="AF69" s="11" t="n"/>
+      <c r="AG69" s="45" t="inlineStr"/>
+      <c r="AH69" s="10" t="n"/>
+      <c r="AI69" s="11" t="n"/>
+      <c r="AJ69" s="45" t="inlineStr"/>
+      <c r="AK69" s="10" t="n"/>
+      <c r="AL69" s="11" t="n"/>
+      <c r="AM69" s="45" t="inlineStr"/>
+      <c r="AN69" s="10" t="n"/>
+      <c r="AO69" s="11" t="n"/>
+      <c r="AP69" s="45" t="inlineStr"/>
+      <c r="AQ69" s="10" t="n"/>
+      <c r="AR69" s="11" t="n"/>
+      <c r="AS69" s="45" t="inlineStr"/>
+      <c r="AT69" s="10" t="n"/>
+      <c r="AU69" s="11" t="n"/>
+      <c r="AV69" s="45" t="inlineStr"/>
+      <c r="AW69" s="10" t="n"/>
+      <c r="AX69" s="11" t="n"/>
+      <c r="AY69" s="45" t="inlineStr"/>
+      <c r="AZ69" s="10" t="n"/>
+      <c r="BA69" s="11" t="n"/>
+      <c r="BB69" s="45" t="inlineStr"/>
+      <c r="BC69" s="10" t="n"/>
+      <c r="BD69" s="11" t="n"/>
+      <c r="BE69" s="45" t="inlineStr"/>
+      <c r="BF69" s="10" t="n"/>
+      <c r="BG69" s="11" t="n"/>
+      <c r="BH69" s="45" t="inlineStr"/>
+      <c r="BI69" s="10" t="n"/>
+      <c r="BJ69" s="11" t="n"/>
+      <c r="BK69" s="46" t="inlineStr"/>
+      <c r="BL69" s="10" t="n"/>
+      <c r="BM69" s="10" t="n"/>
+      <c r="BN69" s="10" t="n"/>
+      <c r="BO69" s="10" t="n"/>
+      <c r="BP69" s="10" t="n"/>
+      <c r="BQ69" s="11" t="n"/>
+    </row>
+    <row r="70" ht="80" customHeight="1">
+      <c r="A70" s="44" t="n">
+        <v>53</v>
+      </c>
+      <c r="B70" s="46" t="inlineStr">
+        <is>
+          <t>ACSMS-TC-011-052</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="11" t="n"/>
+      <c r="E70" s="46" t="inlineStr">
+        <is>
+          <t>Vùng thông tin nơi giao báo phải hiển thị với loại kết hợp (yêu cầu khách hàng 2026-08)</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="11" t="n"/>
+      <c r="J70" s="46" t="inlineStr"/>
+      <c r="K70" s="10" t="n"/>
+      <c r="L70" s="10" t="n"/>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="11" t="n"/>
+      <c r="Q70" s="46" t="inlineStr"/>
+      <c r="R70" s="10" t="n"/>
+      <c r="S70" s="10" t="n"/>
+      <c r="T70" s="10" t="n"/>
+      <c r="U70" s="10" t="n"/>
+      <c r="V70" s="10" t="n"/>
+      <c r="W70" s="11" t="n"/>
+      <c r="X70" s="46" t="inlineStr"/>
+      <c r="Y70" s="10" t="n"/>
+      <c r="Z70" s="10" t="n"/>
+      <c r="AA70" s="10" t="n"/>
+      <c r="AB70" s="10" t="n"/>
+      <c r="AC70" s="10" t="n"/>
+      <c r="AD70" s="11" t="n"/>
+      <c r="AE70" s="45" t="inlineStr"/>
+      <c r="AF70" s="11" t="n"/>
+      <c r="AG70" s="45" t="inlineStr"/>
+      <c r="AH70" s="10" t="n"/>
+      <c r="AI70" s="11" t="n"/>
+      <c r="AJ70" s="45" t="inlineStr"/>
+      <c r="AK70" s="10" t="n"/>
+      <c r="AL70" s="11" t="n"/>
+      <c r="AM70" s="45" t="inlineStr"/>
+      <c r="AN70" s="10" t="n"/>
+      <c r="AO70" s="11" t="n"/>
+      <c r="AP70" s="45" t="inlineStr"/>
+      <c r="AQ70" s="10" t="n"/>
+      <c r="AR70" s="11" t="n"/>
+      <c r="AS70" s="45" t="inlineStr"/>
+      <c r="AT70" s="10" t="n"/>
+      <c r="AU70" s="11" t="n"/>
+      <c r="AV70" s="45" t="inlineStr"/>
+      <c r="AW70" s="10" t="n"/>
+      <c r="AX70" s="11" t="n"/>
+      <c r="AY70" s="45" t="inlineStr"/>
+      <c r="AZ70" s="10" t="n"/>
+      <c r="BA70" s="11" t="n"/>
+      <c r="BB70" s="45" t="inlineStr"/>
+      <c r="BC70" s="10" t="n"/>
+      <c r="BD70" s="11" t="n"/>
+      <c r="BE70" s="45" t="inlineStr"/>
+      <c r="BF70" s="10" t="n"/>
+      <c r="BG70" s="11" t="n"/>
+      <c r="BH70" s="45" t="inlineStr"/>
+      <c r="BI70" s="10" t="n"/>
+      <c r="BJ70" s="11" t="n"/>
+      <c r="BK70" s="46" t="inlineStr"/>
+      <c r="BL70" s="10" t="n"/>
+      <c r="BM70" s="10" t="n"/>
+      <c r="BN70" s="10" t="n"/>
+      <c r="BO70" s="10" t="n"/>
+      <c r="BP70" s="10" t="n"/>
+      <c r="BQ70" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="854">
+  <mergeCells count="973">
     <mergeCell ref="AS59:AU59"/>
     <mergeCell ref="J31:P31"/>
     <mergeCell ref="B60:D60"/>
     <mergeCell ref="AS46:AU46"/>
     <mergeCell ref="BK58:BQ58"/>
+    <mergeCell ref="BB68:BD68"/>
     <mergeCell ref="AP50:AR50"/>
     <mergeCell ref="AE54:AF54"/>
     <mergeCell ref="BH33:BJ33"/>
     <mergeCell ref="BK50:BQ50"/>
     <mergeCell ref="AE41:AF41"/>
+    <mergeCell ref="E52:I52"/>
     <mergeCell ref="AV57:AX57"/>
-    <mergeCell ref="B53:D53"/>
     <mergeCell ref="AP60:AR60"/>
     <mergeCell ref="E39:I39"/>
     <mergeCell ref="E14:I14"/>
     <mergeCell ref="AS61:AU61"/>
     <mergeCell ref="W7:Y7"/>
+    <mergeCell ref="AM64:AO64"/>
     <mergeCell ref="AS48:AU48"/>
     <mergeCell ref="J62:P62"/>
     <mergeCell ref="BK16:BQ16"/>
     <mergeCell ref="AE56:AF56"/>
+    <mergeCell ref="AE43:AF43"/>
     <mergeCell ref="AM30:AO30"/>
     <mergeCell ref="AP45:AR45"/>
+    <mergeCell ref="J64:P64"/>
     <mergeCell ref="BE13:BG13"/>
     <mergeCell ref="W8:Y8"/>
+    <mergeCell ref="Q37:W37"/>
     <mergeCell ref="AJ20:AL20"/>
     <mergeCell ref="AM21:AO21"/>
+    <mergeCell ref="AM65:AO65"/>
     <mergeCell ref="AG24:AI24"/>
     <mergeCell ref="BH39:BJ39"/>
     <mergeCell ref="J57:P57"/>
     <mergeCell ref="W2:AH2"/>
     <mergeCell ref="X10:AD11"/>
     <mergeCell ref="AG42:AI42"/>
+    <mergeCell ref="BK70:BQ70"/>
     <mergeCell ref="AJ22:AL22"/>
     <mergeCell ref="AG26:AI26"/>
     <mergeCell ref="AP13:AR13"/>
     <mergeCell ref="BK42:BQ42"/>
-    <mergeCell ref="Q38:W38"/>
     <mergeCell ref="AE34:AF34"/>
     <mergeCell ref="AJ51:AL51"/>
     <mergeCell ref="BK47:BQ47"/>
     <mergeCell ref="E25:I25"/>
+    <mergeCell ref="X68:AD68"/>
     <mergeCell ref="Q40:W40"/>
     <mergeCell ref="AE36:AF36"/>
     <mergeCell ref="AS51:AU51"/>
     <mergeCell ref="Q15:W15"/>
     <mergeCell ref="AV39:AX39"/>
+    <mergeCell ref="AV70:AX70"/>
     <mergeCell ref="E58:I58"/>
     <mergeCell ref="BE20:BG20"/>
     <mergeCell ref="BH21:BJ21"/>
     <mergeCell ref="AM34:AO34"/>
-    <mergeCell ref="AJ38:AL38"/>
     <mergeCell ref="BE35:BG35"/>
     <mergeCell ref="BK48:BQ48"/>
     <mergeCell ref="AM49:AO49"/>
     <mergeCell ref="AE50:AF50"/>
+    <mergeCell ref="AG52:AI52"/>
+    <mergeCell ref="X69:AD69"/>
     <mergeCell ref="BE22:BG22"/>
     <mergeCell ref="BH23:BJ23"/>
     <mergeCell ref="BB26:BD26"/>
     <mergeCell ref="AE31:AF31"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="AG45:AI45"/>
+    <mergeCell ref="AS67:AU67"/>
     <mergeCell ref="AY29:BA29"/>
     <mergeCell ref="E20:I20"/>
     <mergeCell ref="AJ33:AL33"/>
+    <mergeCell ref="AG37:AI37"/>
     <mergeCell ref="J39:P39"/>
     <mergeCell ref="X21:AD21"/>
     <mergeCell ref="AE62:AF62"/>
     <mergeCell ref="AG47:AI47"/>
+    <mergeCell ref="B68:D68"/>
     <mergeCell ref="AF8:AH8"/>
     <mergeCell ref="AY31:BA31"/>
     <mergeCell ref="AJ35:AL35"/>
+    <mergeCell ref="BK37:BQ37"/>
     <mergeCell ref="AM55:AO55"/>
     <mergeCell ref="BH34:BJ34"/>
     <mergeCell ref="X23:AD23"/>
-    <mergeCell ref="BE38:BG38"/>
+    <mergeCell ref="AE64:AF64"/>
     <mergeCell ref="AS62:AU62"/>
     <mergeCell ref="AV63:AX63"/>
+    <mergeCell ref="AP66:AR66"/>
     <mergeCell ref="BH49:BJ49"/>
     <mergeCell ref="R3:V3"/>
-    <mergeCell ref="AP53:AR53"/>
+    <mergeCell ref="BK66:BQ66"/>
     <mergeCell ref="X16:AD16"/>
     <mergeCell ref="AP28:AR28"/>
     <mergeCell ref="AE57:AF57"/>
-    <mergeCell ref="BK53:BQ53"/>
     <mergeCell ref="BH60:BJ60"/>
     <mergeCell ref="AC7:AE7"/>
     <mergeCell ref="AY26:BA26"/>
     <mergeCell ref="BE15:BG15"/>
+    <mergeCell ref="AS64:AU64"/>
+    <mergeCell ref="AP68:AR68"/>
+    <mergeCell ref="J65:P65"/>
     <mergeCell ref="AG63:AI63"/>
     <mergeCell ref="X18:AD18"/>
     <mergeCell ref="BE33:BG33"/>
+    <mergeCell ref="BB37:BD37"/>
     <mergeCell ref="AG50:AI50"/>
+    <mergeCell ref="AP67:AR67"/>
     <mergeCell ref="BK13:BQ13"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="AY57:BA57"/>
@@ -18380,7 +19025,6 @@
     <mergeCell ref="AM24:AO24"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="AM60:AO60"/>
-    <mergeCell ref="BB38:BD38"/>
     <mergeCell ref="AV14:AX14"/>
     <mergeCell ref="Q61:W61"/>
     <mergeCell ref="W3:AH3"/>
@@ -18394,10 +19038,9 @@
     <mergeCell ref="BH29:BJ29"/>
     <mergeCell ref="Q41:W41"/>
     <mergeCell ref="E35:I35"/>
-    <mergeCell ref="AY44:BA44"/>
-    <mergeCell ref="AV53:AX53"/>
-    <mergeCell ref="BH44:BJ44"/>
     <mergeCell ref="Q56:W56"/>
+    <mergeCell ref="AE52:AF52"/>
+    <mergeCell ref="Q43:W43"/>
     <mergeCell ref="J14:P14"/>
     <mergeCell ref="AE39:AF39"/>
     <mergeCell ref="B51:D51"/>
@@ -18412,15 +19055,14 @@
     <mergeCell ref="AJ41:AL41"/>
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="BK10:BQ11"/>
-    <mergeCell ref="J53:P53"/>
     <mergeCell ref="AS14:AU14"/>
-    <mergeCell ref="AE53:AF53"/>
     <mergeCell ref="AG55:AI55"/>
     <mergeCell ref="AP18:AR18"/>
     <mergeCell ref="AJ56:AL56"/>
     <mergeCell ref="BH26:BJ26"/>
-    <mergeCell ref="AG38:AI38"/>
     <mergeCell ref="BE30:BG30"/>
+    <mergeCell ref="AJ43:AL43"/>
+    <mergeCell ref="AY70:BA70"/>
     <mergeCell ref="AV25:AX25"/>
     <mergeCell ref="W6:Y6"/>
     <mergeCell ref="J55:P55"/>
@@ -18432,24 +19074,35 @@
     <mergeCell ref="Q34:W34"/>
     <mergeCell ref="AG40:AI40"/>
     <mergeCell ref="X24:AD24"/>
+    <mergeCell ref="BB43:BD43"/>
+    <mergeCell ref="BK68:BQ68"/>
+    <mergeCell ref="A44:BQ44"/>
     <mergeCell ref="AY47:BA47"/>
     <mergeCell ref="E21:I21"/>
     <mergeCell ref="BH50:BJ50"/>
     <mergeCell ref="Q36:W36"/>
     <mergeCell ref="BE54:BG54"/>
+    <mergeCell ref="AJ67:AL67"/>
     <mergeCell ref="Q30:W30"/>
+    <mergeCell ref="BK67:BQ67"/>
     <mergeCell ref="AE63:AF63"/>
     <mergeCell ref="X26:AD26"/>
     <mergeCell ref="W1:AH1"/>
     <mergeCell ref="AC8:AE8"/>
-    <mergeCell ref="AP44:AR44"/>
+    <mergeCell ref="AP69:AR69"/>
     <mergeCell ref="E23:I23"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="BE56:BG56"/>
+    <mergeCell ref="AJ69:AL69"/>
+    <mergeCell ref="BK69:BQ69"/>
+    <mergeCell ref="AM70:AO70"/>
+    <mergeCell ref="BE43:BG43"/>
     <mergeCell ref="J33:P33"/>
     <mergeCell ref="AE58:AF58"/>
+    <mergeCell ref="AV68:AX68"/>
     <mergeCell ref="BB59:BD59"/>
     <mergeCell ref="AM63:AO63"/>
+    <mergeCell ref="AG66:AI66"/>
     <mergeCell ref="BB46:BD46"/>
     <mergeCell ref="BE57:BG57"/>
     <mergeCell ref="B24:D24"/>
@@ -18460,16 +19113,24 @@
     <mergeCell ref="Q62:W62"/>
     <mergeCell ref="E34:I34"/>
     <mergeCell ref="BB48:BD48"/>
+    <mergeCell ref="AG68:AI68"/>
+    <mergeCell ref="AG43:AI43"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E49:I49"/>
+    <mergeCell ref="J68:P68"/>
     <mergeCell ref="AY18:BA18"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="AY45:BA45"/>
     <mergeCell ref="E36:I36"/>
+    <mergeCell ref="Q64:W64"/>
     <mergeCell ref="Q51:W51"/>
+    <mergeCell ref="BH70:BJ70"/>
+    <mergeCell ref="X37:AD37"/>
+    <mergeCell ref="AV65:AX65"/>
     <mergeCell ref="BH45:BJ45"/>
     <mergeCell ref="AS20:AU20"/>
+    <mergeCell ref="A53:BQ53"/>
     <mergeCell ref="AP24:AR24"/>
     <mergeCell ref="BH32:BJ32"/>
     <mergeCell ref="BK18:BQ18"/>
@@ -18483,11 +19144,9 @@
     <mergeCell ref="AY42:BA42"/>
     <mergeCell ref="AE55:AF55"/>
     <mergeCell ref="AG21:AI21"/>
-    <mergeCell ref="X38:AD38"/>
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="BH46:BJ46"/>
     <mergeCell ref="BE50:BG50"/>
-    <mergeCell ref="BE44:BG44"/>
     <mergeCell ref="AJ57:AL57"/>
     <mergeCell ref="AG61:AI61"/>
     <mergeCell ref="BE31:BG31"/>
@@ -18495,66 +19154,72 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="AG48:AI48"/>
     <mergeCell ref="Q17:W17"/>
-    <mergeCell ref="B44:D44"/>
     <mergeCell ref="BB34:BD34"/>
     <mergeCell ref="E29:I29"/>
     <mergeCell ref="J23:P23"/>
     <mergeCell ref="AV34:AX34"/>
+    <mergeCell ref="B37:D37"/>
     <mergeCell ref="BH58:BJ58"/>
     <mergeCell ref="AV28:AX28"/>
-    <mergeCell ref="BK44:BQ44"/>
     <mergeCell ref="AY48:BA48"/>
     <mergeCell ref="BB49:BD49"/>
     <mergeCell ref="AG62:AI62"/>
     <mergeCell ref="AE33:AF33"/>
     <mergeCell ref="BB36:BD36"/>
-    <mergeCell ref="A37:BQ37"/>
     <mergeCell ref="X40:AD40"/>
     <mergeCell ref="E31:I31"/>
     <mergeCell ref="AV36:AX36"/>
     <mergeCell ref="T6:V6"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="AV30:AX30"/>
+    <mergeCell ref="Q52:W52"/>
     <mergeCell ref="Q39:W39"/>
     <mergeCell ref="AS33:AU33"/>
     <mergeCell ref="AM36:AO36"/>
     <mergeCell ref="F1:Q1"/>
+    <mergeCell ref="AP37:AR37"/>
     <mergeCell ref="J34:P34"/>
     <mergeCell ref="E26:I26"/>
+    <mergeCell ref="AY37:BA37"/>
+    <mergeCell ref="BE65:BG65"/>
     <mergeCell ref="AS35:AU35"/>
     <mergeCell ref="J49:P49"/>
+    <mergeCell ref="AE68:AF68"/>
     <mergeCell ref="J36:P36"/>
-    <mergeCell ref="A43:BQ43"/>
     <mergeCell ref="BB62:BD62"/>
     <mergeCell ref="AJ14:AL14"/>
     <mergeCell ref="AY17:BA17"/>
+    <mergeCell ref="AY66:BA66"/>
+    <mergeCell ref="AJ70:AL70"/>
     <mergeCell ref="AV21:AX21"/>
-    <mergeCell ref="AY53:BA53"/>
     <mergeCell ref="BK24:BQ24"/>
     <mergeCell ref="X45:AD45"/>
     <mergeCell ref="E50:I50"/>
     <mergeCell ref="AG11:AI11"/>
-    <mergeCell ref="BH53:BJ53"/>
+    <mergeCell ref="BB64:BD64"/>
     <mergeCell ref="AV29:AX29"/>
     <mergeCell ref="A8:G8"/>
+    <mergeCell ref="Q65:W65"/>
     <mergeCell ref="AV23:AX23"/>
     <mergeCell ref="BB51:BD51"/>
     <mergeCell ref="AP63:AR63"/>
     <mergeCell ref="E42:I42"/>
     <mergeCell ref="AY55:BA55"/>
+    <mergeCell ref="AY68:BA68"/>
     <mergeCell ref="X59:AD59"/>
     <mergeCell ref="K8:M8"/>
-    <mergeCell ref="E44:I44"/>
     <mergeCell ref="X46:AD46"/>
     <mergeCell ref="AE21:AF21"/>
     <mergeCell ref="BH48:BJ48"/>
     <mergeCell ref="AV24:AX24"/>
     <mergeCell ref="BE58:BG58"/>
+    <mergeCell ref="AJ65:AL65"/>
     <mergeCell ref="T8:V8"/>
     <mergeCell ref="AS28:AU28"/>
     <mergeCell ref="AM31:AO31"/>
     <mergeCell ref="BE39:BG39"/>
     <mergeCell ref="J29:P29"/>
+    <mergeCell ref="BE70:BG70"/>
     <mergeCell ref="X48:AD48"/>
     <mergeCell ref="AE23:AF23"/>
     <mergeCell ref="AC6:AE6"/>
@@ -18564,56 +19229,70 @@
     <mergeCell ref="BB11:BD11"/>
     <mergeCell ref="AJ25:AL25"/>
     <mergeCell ref="B45:D45"/>
-    <mergeCell ref="BE53:BG53"/>
     <mergeCell ref="AJ60:AL60"/>
     <mergeCell ref="AM32:AO32"/>
+    <mergeCell ref="AG64:AI64"/>
     <mergeCell ref="Q7:S7"/>
     <mergeCell ref="AM26:AO26"/>
     <mergeCell ref="J24:P24"/>
     <mergeCell ref="AG51:AI51"/>
     <mergeCell ref="Q20:W20"/>
     <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E70:I70"/>
     <mergeCell ref="Q14:W14"/>
     <mergeCell ref="B59:D59"/>
     <mergeCell ref="E57:I57"/>
     <mergeCell ref="AV50:AX50"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="Q60:W60"/>
+    <mergeCell ref="A38:BQ38"/>
     <mergeCell ref="AS54:AU54"/>
     <mergeCell ref="E32:I32"/>
     <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q60:W60"/>
+    <mergeCell ref="BH66:BJ66"/>
     <mergeCell ref="AS41:AU41"/>
     <mergeCell ref="AE49:AF49"/>
     <mergeCell ref="AY13:BA13"/>
     <mergeCell ref="Q8:S8"/>
+    <mergeCell ref="AG65:AI65"/>
     <mergeCell ref="AV55:AX55"/>
     <mergeCell ref="E47:I47"/>
     <mergeCell ref="BB39:BD39"/>
     <mergeCell ref="B48:D48"/>
+    <mergeCell ref="AV52:AX52"/>
     <mergeCell ref="AP55:AR55"/>
     <mergeCell ref="AS56:AU56"/>
-    <mergeCell ref="AP38:AR38"/>
+    <mergeCell ref="BH68:BJ68"/>
     <mergeCell ref="X41:AD41"/>
+    <mergeCell ref="AS43:AU43"/>
     <mergeCell ref="AY63:BA63"/>
     <mergeCell ref="BE25:BG25"/>
-    <mergeCell ref="BK38:BQ38"/>
     <mergeCell ref="F4:AH4"/>
     <mergeCell ref="X51:AD51"/>
     <mergeCell ref="AJ13:AL13"/>
+    <mergeCell ref="AM52:AO52"/>
     <mergeCell ref="BH61:BJ61"/>
     <mergeCell ref="AG17:AI17"/>
     <mergeCell ref="AS36:AU36"/>
     <mergeCell ref="J50:P50"/>
     <mergeCell ref="AM39:AO39"/>
     <mergeCell ref="AP40:AR40"/>
+    <mergeCell ref="BH67:BJ67"/>
     <mergeCell ref="J42:P42"/>
     <mergeCell ref="BK63:BQ63"/>
     <mergeCell ref="AJ15:AL15"/>
+    <mergeCell ref="AY67:BA67"/>
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="X36:AD36"/>
-    <mergeCell ref="J44:P44"/>
+    <mergeCell ref="J52:P52"/>
     <mergeCell ref="Q25:W25"/>
+    <mergeCell ref="AV37:AX37"/>
+    <mergeCell ref="BB65:BD65"/>
+    <mergeCell ref="BE66:BG66"/>
+    <mergeCell ref="AY69:BA69"/>
     <mergeCell ref="E60:I60"/>
+    <mergeCell ref="X67:AD67"/>
+    <mergeCell ref="J37:P37"/>
     <mergeCell ref="AV60:AX60"/>
     <mergeCell ref="Q33:W33"/>
     <mergeCell ref="X61:AD61"/>
@@ -18629,20 +19308,23 @@
     <mergeCell ref="AS29:AU29"/>
     <mergeCell ref="AM42:AO42"/>
     <mergeCell ref="X62:AD62"/>
+    <mergeCell ref="AE37:AF37"/>
+    <mergeCell ref="B66:D66"/>
     <mergeCell ref="BH16:BJ16"/>
     <mergeCell ref="AM29:AO29"/>
     <mergeCell ref="AM23:AO23"/>
     <mergeCell ref="AE24:AF24"/>
-    <mergeCell ref="AS44:AU44"/>
+    <mergeCell ref="J70:P70"/>
     <mergeCell ref="BE55:BG55"/>
     <mergeCell ref="AS31:AU31"/>
+    <mergeCell ref="X64:AD64"/>
     <mergeCell ref="BH18:BJ18"/>
     <mergeCell ref="J32:P32"/>
     <mergeCell ref="J63:P63"/>
     <mergeCell ref="AE26:AF26"/>
-    <mergeCell ref="AY38:BA38"/>
     <mergeCell ref="Q22:W22"/>
     <mergeCell ref="BB58:BD58"/>
+    <mergeCell ref="B67:D67"/>
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="J47:P47"/>
     <mergeCell ref="AV58:AX58"/>
@@ -18653,6 +19335,7 @@
     <mergeCell ref="BK17:BQ17"/>
     <mergeCell ref="BK55:BQ55"/>
     <mergeCell ref="BB60:BD60"/>
+    <mergeCell ref="B69:D69"/>
     <mergeCell ref="AP30:AR30"/>
     <mergeCell ref="AP59:AR59"/>
     <mergeCell ref="AJ30:AL30"/>
@@ -18667,8 +19350,8 @@
     <mergeCell ref="AP61:AR61"/>
     <mergeCell ref="AM16:AO16"/>
     <mergeCell ref="AP48:AR48"/>
+    <mergeCell ref="B64:D64"/>
     <mergeCell ref="A27:BQ27"/>
-    <mergeCell ref="AE44:AF44"/>
     <mergeCell ref="X57:AD57"/>
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="AP41:AR41"/>
@@ -18680,7 +19363,8 @@
     <mergeCell ref="AP56:AR56"/>
     <mergeCell ref="AG20:AI20"/>
     <mergeCell ref="B16:D16"/>
-    <mergeCell ref="AM53:AO53"/>
+    <mergeCell ref="BE68:BG68"/>
+    <mergeCell ref="AP43:AR43"/>
     <mergeCell ref="AM47:AO47"/>
     <mergeCell ref="B10:D11"/>
     <mergeCell ref="J45:P45"/>
@@ -18689,15 +19373,18 @@
     <mergeCell ref="AG22:AI22"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="AJ23:AL23"/>
-    <mergeCell ref="E53:I53"/>
+    <mergeCell ref="E66:I66"/>
+    <mergeCell ref="AE70:AF70"/>
     <mergeCell ref="AM48:AO48"/>
     <mergeCell ref="Q49:W49"/>
-    <mergeCell ref="AM44:AO44"/>
+    <mergeCell ref="E68:I68"/>
+    <mergeCell ref="BK43:BQ43"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="AF6:AH6"/>
     <mergeCell ref="E55:I55"/>
     <mergeCell ref="AE32:AF32"/>
     <mergeCell ref="AV48:AX48"/>
+    <mergeCell ref="E67:I67"/>
     <mergeCell ref="AY14:BA14"/>
     <mergeCell ref="AJ18:AL18"/>
     <mergeCell ref="J51:P51"/>
@@ -18711,11 +19398,13 @@
     <mergeCell ref="AJ34:AL34"/>
     <mergeCell ref="BK34:BQ34"/>
     <mergeCell ref="AY59:BA59"/>
+    <mergeCell ref="AS70:AU70"/>
     <mergeCell ref="J58:P58"/>
     <mergeCell ref="AS32:AU32"/>
     <mergeCell ref="AM45:AO45"/>
     <mergeCell ref="AJ49:AL49"/>
     <mergeCell ref="AP11:AR11"/>
+    <mergeCell ref="X70:AD70"/>
     <mergeCell ref="BB22:BD22"/>
     <mergeCell ref="BE23:BG23"/>
     <mergeCell ref="AJ36:AL36"/>
@@ -18727,8 +19416,8 @@
     <mergeCell ref="AG33:AI33"/>
     <mergeCell ref="X17:AD17"/>
     <mergeCell ref="BK61:BQ61"/>
-    <mergeCell ref="AJ44:AL44"/>
     <mergeCell ref="Q54:W54"/>
+    <mergeCell ref="AS65:AU65"/>
     <mergeCell ref="BE18:BG18"/>
     <mergeCell ref="AJ31:AL31"/>
     <mergeCell ref="B62:D62"/>
@@ -18736,6 +19425,7 @@
     <mergeCell ref="AG35:AI35"/>
     <mergeCell ref="AM51:AO51"/>
     <mergeCell ref="Q23:W23"/>
+    <mergeCell ref="AV66:AX66"/>
     <mergeCell ref="AE60:AF60"/>
     <mergeCell ref="AS58:AU58"/>
     <mergeCell ref="AG34:AI34"/>
@@ -18750,16 +19440,22 @@
     <mergeCell ref="BK56:BQ56"/>
     <mergeCell ref="BK62:BQ62"/>
     <mergeCell ref="BE36:BG36"/>
+    <mergeCell ref="BH37:BJ37"/>
+    <mergeCell ref="B70:D70"/>
     <mergeCell ref="AE45:AF45"/>
     <mergeCell ref="X58:AD58"/>
     <mergeCell ref="AS60:AU60"/>
     <mergeCell ref="AV61:AX61"/>
+    <mergeCell ref="AP64:AR64"/>
     <mergeCell ref="Z7:AB7"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="AP51:AR51"/>
     <mergeCell ref="AG59:AI59"/>
+    <mergeCell ref="BK64:BQ64"/>
+    <mergeCell ref="J66:P66"/>
     <mergeCell ref="BK51:BQ51"/>
+    <mergeCell ref="AM67:AO67"/>
     <mergeCell ref="X60:AD60"/>
     <mergeCell ref="AM61:AO61"/>
     <mergeCell ref="B17:D17"/>
@@ -18772,7 +19468,9 @@
     <mergeCell ref="BB35:BD35"/>
     <mergeCell ref="BH51:BJ51"/>
     <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="AP65:AR65"/>
     <mergeCell ref="AM20:AO20"/>
+    <mergeCell ref="AM69:AO69"/>
     <mergeCell ref="AJ24:AL24"/>
     <mergeCell ref="J61:P61"/>
     <mergeCell ref="AY11:BA11"/>
@@ -18781,31 +19479,34 @@
     <mergeCell ref="AM35:AO35"/>
     <mergeCell ref="AJ26:AL26"/>
     <mergeCell ref="AS13:AU13"/>
+    <mergeCell ref="E69:I69"/>
     <mergeCell ref="AP17:AR17"/>
     <mergeCell ref="AY40:BA40"/>
     <mergeCell ref="Q42:W42"/>
     <mergeCell ref="A12:BQ12"/>
     <mergeCell ref="AY15:BA15"/>
-    <mergeCell ref="AS53:AU53"/>
     <mergeCell ref="AG23:AI23"/>
     <mergeCell ref="BH40:BJ40"/>
     <mergeCell ref="X13:AD13"/>
     <mergeCell ref="AS15:AU15"/>
     <mergeCell ref="AE48:AF48"/>
     <mergeCell ref="AS55:AU55"/>
+    <mergeCell ref="BE37:BG37"/>
     <mergeCell ref="AJ50:AL50"/>
     <mergeCell ref="BH20:BJ20"/>
     <mergeCell ref="AG54:AI54"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="BE24:BG24"/>
     <mergeCell ref="BH25:BJ25"/>
-    <mergeCell ref="AM38:AO38"/>
+    <mergeCell ref="BH69:BJ69"/>
     <mergeCell ref="BB28:BD28"/>
     <mergeCell ref="AG41:AI41"/>
     <mergeCell ref="BH35:BJ35"/>
     <mergeCell ref="AP39:AR39"/>
     <mergeCell ref="AP14:AR14"/>
+    <mergeCell ref="AJ52:AL52"/>
     <mergeCell ref="BH22:BJ22"/>
+    <mergeCell ref="BK52:BQ52"/>
     <mergeCell ref="AG56:AI56"/>
     <mergeCell ref="BE26:BG26"/>
     <mergeCell ref="J16:P16"/>
@@ -18820,30 +19521,41 @@
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="AG49:AI49"/>
     <mergeCell ref="AE51:AF51"/>
+    <mergeCell ref="AV67:AX67"/>
     <mergeCell ref="BB29:BD29"/>
     <mergeCell ref="BB23:BD23"/>
     <mergeCell ref="E24:I24"/>
     <mergeCell ref="AG36:AI36"/>
     <mergeCell ref="B13:D13"/>
+    <mergeCell ref="Q70:W70"/>
+    <mergeCell ref="AE66:AF66"/>
     <mergeCell ref="Q45:W45"/>
+    <mergeCell ref="AV69:AX69"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="BB31:BD31"/>
     <mergeCell ref="Q32:W32"/>
     <mergeCell ref="AY35:BA35"/>
     <mergeCell ref="X22:AD22"/>
-    <mergeCell ref="BH38:BJ38"/>
     <mergeCell ref="BE42:BG42"/>
     <mergeCell ref="Q47:W47"/>
     <mergeCell ref="BH13:BJ13"/>
+    <mergeCell ref="AS66:AU66"/>
+    <mergeCell ref="BE52:BG52"/>
+    <mergeCell ref="BK65:BQ65"/>
+    <mergeCell ref="J67:P67"/>
     <mergeCell ref="BK21:BQ21"/>
     <mergeCell ref="BB56:BD56"/>
     <mergeCell ref="AE61:AF61"/>
+    <mergeCell ref="AE67:AF67"/>
+    <mergeCell ref="AV64:AX64"/>
     <mergeCell ref="AF7:AH7"/>
     <mergeCell ref="BH15:BJ15"/>
     <mergeCell ref="AY30:BA30"/>
+    <mergeCell ref="AS68:AU68"/>
     <mergeCell ref="AJ32:AL32"/>
     <mergeCell ref="AJ63:AL63"/>
     <mergeCell ref="AP25:AR25"/>
+    <mergeCell ref="J69:P69"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="AY46:BA46"/>
     <mergeCell ref="BB57:BD57"/>
@@ -18858,6 +19570,7 @@
     <mergeCell ref="AY41:BA41"/>
     <mergeCell ref="X15:AD15"/>
     <mergeCell ref="AV18:AX18"/>
+    <mergeCell ref="E37:I37"/>
     <mergeCell ref="X33:AD33"/>
     <mergeCell ref="AV17:AX17"/>
     <mergeCell ref="AY56:BA56"/>
@@ -18865,6 +19578,7 @@
     <mergeCell ref="AV11:AX11"/>
     <mergeCell ref="AP20:AR20"/>
     <mergeCell ref="AS21:AU21"/>
+    <mergeCell ref="AY43:BA43"/>
     <mergeCell ref="BE32:BG32"/>
     <mergeCell ref="BE63:BG63"/>
     <mergeCell ref="BK14:BQ14"/>
@@ -18872,30 +19586,29 @@
     <mergeCell ref="AG32:AI32"/>
     <mergeCell ref="X35:AD35"/>
     <mergeCell ref="AE10:AF11"/>
+    <mergeCell ref="BH43:BJ43"/>
     <mergeCell ref="BE47:BG47"/>
     <mergeCell ref="AP22:AR22"/>
     <mergeCell ref="BK60:BQ60"/>
-    <mergeCell ref="B38:D38"/>
     <mergeCell ref="J18:P18"/>
     <mergeCell ref="AE18:AF18"/>
     <mergeCell ref="BE40:BG40"/>
     <mergeCell ref="AP15:AR15"/>
     <mergeCell ref="AS16:AU16"/>
-    <mergeCell ref="BB44:BD44"/>
-    <mergeCell ref="AJ53:AL53"/>
+    <mergeCell ref="AM54:AO54"/>
+    <mergeCell ref="AG57:AI57"/>
     <mergeCell ref="AV10:BJ10"/>
     <mergeCell ref="BH28:BJ28"/>
     <mergeCell ref="J17:P17"/>
-    <mergeCell ref="AM54:AO54"/>
-    <mergeCell ref="AV44:AX44"/>
+    <mergeCell ref="AJ45:AL45"/>
     <mergeCell ref="B40:D40"/>
-    <mergeCell ref="AJ45:AL45"/>
-    <mergeCell ref="AG57:AI57"/>
     <mergeCell ref="E63:I63"/>
     <mergeCell ref="B15:D15"/>
+    <mergeCell ref="BB52:BD52"/>
     <mergeCell ref="AJ55:AL55"/>
     <mergeCell ref="AY34:BA34"/>
     <mergeCell ref="B33:D33"/>
+    <mergeCell ref="BB70:BD70"/>
     <mergeCell ref="BH59:BJ59"/>
     <mergeCell ref="AY25:BA25"/>
     <mergeCell ref="AS34:AU34"/>
@@ -18910,6 +19623,7 @@
     <mergeCell ref="AS30:AU30"/>
     <mergeCell ref="BB47:BD47"/>
     <mergeCell ref="AG60:AI60"/>
+    <mergeCell ref="AE69:AF69"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="AS42:AU42"/>
     <mergeCell ref="BH54:BJ54"/>
@@ -18918,8 +19632,10 @@
     <mergeCell ref="X30:AD30"/>
     <mergeCell ref="BE45:BG45"/>
     <mergeCell ref="AJ58:AL58"/>
+    <mergeCell ref="BH65:BJ65"/>
     <mergeCell ref="X42:AD42"/>
     <mergeCell ref="E22:I22"/>
+    <mergeCell ref="AS69:AU69"/>
     <mergeCell ref="BH56:BJ56"/>
     <mergeCell ref="X29:AD29"/>
     <mergeCell ref="AP35:AR35"/>
@@ -18929,21 +19645,26 @@
     <mergeCell ref="BE59:BG59"/>
     <mergeCell ref="AY62:BA62"/>
     <mergeCell ref="BB63:BD63"/>
+    <mergeCell ref="AJ66:AL66"/>
     <mergeCell ref="BE46:BG46"/>
+    <mergeCell ref="AG70:AI70"/>
     <mergeCell ref="BB50:BD50"/>
     <mergeCell ref="X54:AD54"/>
     <mergeCell ref="BK20:BQ20"/>
     <mergeCell ref="AY28:BA28"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B28:D28"/>
+    <mergeCell ref="AY64:BA64"/>
+    <mergeCell ref="AJ68:AL68"/>
+    <mergeCell ref="Q66:W66"/>
     <mergeCell ref="AS23:AU23"/>
-    <mergeCell ref="E38:I38"/>
     <mergeCell ref="AY51:BA51"/>
-    <mergeCell ref="Q53:W53"/>
     <mergeCell ref="X56:AD56"/>
     <mergeCell ref="BK22:BQ22"/>
     <mergeCell ref="E13:I13"/>
+    <mergeCell ref="X43:AD43"/>
     <mergeCell ref="B30:D30"/>
+    <mergeCell ref="Q68:W68"/>
     <mergeCell ref="E40:I40"/>
     <mergeCell ref="BK15:BQ15"/>
     <mergeCell ref="AE17:AF17"/>
@@ -18959,12 +19680,11 @@
     <mergeCell ref="AP21:AR21"/>
     <mergeCell ref="AS26:AU26"/>
     <mergeCell ref="B54:D54"/>
+    <mergeCell ref="AE65:AF65"/>
     <mergeCell ref="AJ46:AL46"/>
     <mergeCell ref="AJ21:AL21"/>
     <mergeCell ref="AG25:AI25"/>
     <mergeCell ref="AY33:BA33"/>
-    <mergeCell ref="A52:BQ52"/>
-    <mergeCell ref="BB53:BD53"/>
     <mergeCell ref="T5:AH5"/>
     <mergeCell ref="AM22:AO22"/>
     <mergeCell ref="AP23:AR23"/>
@@ -18972,6 +19692,7 @@
     <mergeCell ref="J20:P20"/>
     <mergeCell ref="AJ61:AL61"/>
     <mergeCell ref="AV47:AX47"/>
+    <mergeCell ref="B43:D43"/>
     <mergeCell ref="BE51:BG51"/>
     <mergeCell ref="AY50:BA50"/>
     <mergeCell ref="BB55:BD55"/>
@@ -18979,12 +19700,11 @@
     <mergeCell ref="A5:S5"/>
     <mergeCell ref="J22:P22"/>
     <mergeCell ref="BH62:BJ62"/>
-    <mergeCell ref="AV38:AX38"/>
+    <mergeCell ref="AY52:BA52"/>
     <mergeCell ref="N8:P8"/>
     <mergeCell ref="BK35:BQ35"/>
     <mergeCell ref="AY39:BA39"/>
-    <mergeCell ref="AG53:AI53"/>
-    <mergeCell ref="X44:AD44"/>
+    <mergeCell ref="AS52:AU52"/>
     <mergeCell ref="AP34:AR34"/>
     <mergeCell ref="AM11:AO11"/>
     <mergeCell ref="X31:AD31"/>
@@ -18997,13 +19717,15 @@
     <mergeCell ref="AV33:AX33"/>
     <mergeCell ref="BE61:BG61"/>
     <mergeCell ref="AP36:AR36"/>
+    <mergeCell ref="AS37:AU37"/>
+    <mergeCell ref="AE14:AF14"/>
     <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="AE14:AF14"/>
-    <mergeCell ref="J38:P38"/>
+    <mergeCell ref="BE67:BG67"/>
     <mergeCell ref="K7:M7"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="Q28:W28"/>
     <mergeCell ref="E30:I30"/>
+    <mergeCell ref="BE69:BG69"/>
     <mergeCell ref="AG15:AI15"/>
     <mergeCell ref="AJ16:AL16"/>
     <mergeCell ref="X32:AD32"/>
@@ -19013,26 +19735,34 @@
     <mergeCell ref="J40:P40"/>
     <mergeCell ref="BE62:BG62"/>
     <mergeCell ref="J15:P15"/>
+    <mergeCell ref="AY65:BA65"/>
     <mergeCell ref="AM41:AO41"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="AY21:BA21"/>
     <mergeCell ref="E61:I61"/>
+    <mergeCell ref="BB66:BD66"/>
+    <mergeCell ref="Q67:W67"/>
     <mergeCell ref="AV35:AX35"/>
     <mergeCell ref="AJ11:AL11"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="X49:AD49"/>
     <mergeCell ref="E54:I54"/>
+    <mergeCell ref="BE64:BG64"/>
     <mergeCell ref="AV22:AX22"/>
     <mergeCell ref="AY23:BA23"/>
     <mergeCell ref="AS63:AU63"/>
     <mergeCell ref="E41:I41"/>
     <mergeCell ref="J35:P35"/>
+    <mergeCell ref="X65:AD65"/>
+    <mergeCell ref="AM66:AO66"/>
+    <mergeCell ref="Q69:W69"/>
     <mergeCell ref="AP54:AR54"/>
     <mergeCell ref="B39:D39"/>
     <mergeCell ref="F3:Q3"/>
     <mergeCell ref="E56:I56"/>
     <mergeCell ref="AP29:AR29"/>
     <mergeCell ref="AV51:AX51"/>
+    <mergeCell ref="E43:I43"/>
     <mergeCell ref="X63:AD63"/>
     <mergeCell ref="BB15:BD15"/>
     <mergeCell ref="BE16:BG16"/>
@@ -19042,11 +19772,14 @@
     <mergeCell ref="BK29:BQ29"/>
     <mergeCell ref="AS40:AU40"/>
     <mergeCell ref="X50:AD50"/>
+    <mergeCell ref="AM68:AO68"/>
+    <mergeCell ref="BH52:BJ52"/>
     <mergeCell ref="AP31:AR31"/>
     <mergeCell ref="AE35:AF35"/>
     <mergeCell ref="BH14:BJ14"/>
     <mergeCell ref="BK54:BQ54"/>
     <mergeCell ref="AJ62:AL62"/>
+    <mergeCell ref="AJ37:AL37"/>
     <mergeCell ref="AY49:BA49"/>
     <mergeCell ref="BE11:BG11"/>
     <mergeCell ref="AY20:BA20"/>
@@ -19054,14 +19787,18 @@
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="Q16:W16"/>
     <mergeCell ref="AV40:AX40"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="AJ64:AL64"/>
     <mergeCell ref="T7:V7"/>
     <mergeCell ref="J28:P28"/>
+    <mergeCell ref="X52:AD52"/>
     <mergeCell ref="Q24:W24"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="Q18:W18"/>
     <mergeCell ref="BK49:BQ49"/>
+    <mergeCell ref="AG67:AI67"/>
     <mergeCell ref="B63:D63"/>
-    <mergeCell ref="AE38:AF38"/>
+    <mergeCell ref="AM37:AO37"/>
     <mergeCell ref="AV54:AX54"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="AP57:AR57"/>
@@ -19070,11 +19807,10 @@
     <mergeCell ref="AE13:AF13"/>
     <mergeCell ref="AS45:AU45"/>
     <mergeCell ref="BK57:BQ57"/>
+    <mergeCell ref="AG69:AI69"/>
     <mergeCell ref="AE40:AF40"/>
-    <mergeCell ref="X53:AD53"/>
     <mergeCell ref="X47:AD47"/>
     <mergeCell ref="BH63:BJ63"/>
-    <mergeCell ref="AS38:AU38"/>
     <mergeCell ref="AM14:AO14"/>
     <mergeCell ref="AE15:AF15"/>
     <mergeCell ref="AP42:AR42"/>
@@ -19082,30 +19818,40 @@
     <mergeCell ref="AP58:AR58"/>
     <mergeCell ref="R2:V2"/>
     <mergeCell ref="AM13:AO13"/>
+    <mergeCell ref="AP52:AR52"/>
     <mergeCell ref="X55:AD55"/>
-    <mergeCell ref="AM62:AO62"/>
     <mergeCell ref="AJ17:AL17"/>
     <mergeCell ref="AM56:AO56"/>
+    <mergeCell ref="AM62:AO62"/>
     <mergeCell ref="J54:P54"/>
+    <mergeCell ref="AM43:AO43"/>
     <mergeCell ref="J41:P41"/>
-    <mergeCell ref="Q44:W44"/>
+    <mergeCell ref="BB67:BD67"/>
+    <mergeCell ref="AV43:AX43"/>
     <mergeCell ref="E62:I62"/>
     <mergeCell ref="J56:P56"/>
     <mergeCell ref="AY58:BA58"/>
+    <mergeCell ref="J43:P43"/>
     <mergeCell ref="AM57:AO57"/>
     <mergeCell ref="X25:AD25"/>
+    <mergeCell ref="BB69:BD69"/>
     <mergeCell ref="AG16:AI16"/>
+    <mergeCell ref="E64:I64"/>
     <mergeCell ref="E51:I51"/>
     <mergeCell ref="BK31:BQ31"/>
     <mergeCell ref="AG18:AI18"/>
     <mergeCell ref="BE17:BG17"/>
     <mergeCell ref="B55:D55"/>
+    <mergeCell ref="AP70:AR70"/>
     <mergeCell ref="BB21:BD21"/>
     <mergeCell ref="N6:P6"/>
     <mergeCell ref="AM25:AO25"/>
+    <mergeCell ref="E65:I65"/>
     <mergeCell ref="J59:P59"/>
     <mergeCell ref="AP32:AR32"/>
     <mergeCell ref="BK45:BQ45"/>
+    <mergeCell ref="BH64:BJ64"/>
+    <mergeCell ref="X66:AD66"/>
     <mergeCell ref="BK32:BQ32"/>
     <mergeCell ref="AM33:AO33"/>
     <mergeCell ref="BK26:BQ26"/>
@@ -19119,25 +19865,25 @@
     <mergeCell ref="AE30:AF30"/>
     <mergeCell ref="Q26:W26"/>
     <mergeCell ref="AG10:AU10"/>
-    <mergeCell ref="AG44:AI44"/>
     <mergeCell ref="AV62:AX62"/>
     <mergeCell ref="AM28:AO28"/>
     <mergeCell ref="BE14:BG14"/>
     <mergeCell ref="BB24:BD24"/>
     <mergeCell ref="BB18:BD18"/>
     <mergeCell ref="AG31:AI31"/>
+    <mergeCell ref="B52:D52"/>
     <mergeCell ref="AV56:AX56"/>
     <mergeCell ref="B58:D58"/>
     <mergeCell ref="BE60:BG60"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="AE13:AE18 AE20:AE26 AE28:AE36 AE38:AE42 AE44:AE51 AE53:AE63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AE13:AE18 AE20:AE26 AE28:AE37 AE39:AE43 AE45:AE52 AE54:AE70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"N,A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG13:AG18 AG20:AG26 AG28:AG36 AG38:AG42 AG44:AG51 AG53:AG63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AG13:AG18 AG20:AG26 AG28:AG37 AG39:AG43 AG45:AG52 AG54:AG70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="AV13:AV18 AV20:AV26 AV28:AV36 AV38:AV42 AV44:AV51 AV53:AV63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AV13:AV18 AV20:AV26 AV28:AV37 AV39:AV43 AV45:AV52 AV54:AV70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未テスト,N/A"</formula1>
     </dataValidation>
     <dataValidation sqref="F1" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
